--- a/住宅改修_現地調査アセスメントシート.xlsx
+++ b/住宅改修_現地調査アセスメントシート.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,13 +92,6 @@
       <color rgb="00262626"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="BIZ UDPゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <color rgb="00595959"/>
-      <sz val="8.5"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -120,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -387,28 +380,6 @@
       </top>
       <bottom style="medium">
         <color rgb="00404040"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00A6A6A6"/>
-      </left>
-      <top style="medium">
-        <color rgb="00404040"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00595959"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="00A6A6A6"/>
-      </right>
-      <top style="medium">
-        <color rgb="00404040"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00595959"/>
       </bottom>
     </border>
     <border>
@@ -457,40 +428,40 @@
       <left style="medium">
         <color rgb="00404040"/>
       </left>
-      <top style="thin">
-        <color rgb="00595959"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00404040"/>
-      </left>
-      <bottom style="medium">
-        <color rgb="00404040"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="00595959"/>
-      </top>
-    </border>
-    <border>
-      <bottom style="medium">
-        <color rgb="00404040"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="00404040"/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="00595959"/>
-      </top>
-    </border>
-    <border>
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00404040"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00404040"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
       <right style="medium">
         <color rgb="00404040"/>
       </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
       <bottom style="medium">
         <color rgb="00404040"/>
       </bottom>
@@ -499,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -529,29 +500,17 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -613,10 +572,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -627,11 +582,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -644,11 +594,9 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1191,25 +1139,17 @@
       <c r="AF4" s="17" t="n"/>
       <c r="AG4" s="17" t="n"/>
       <c r="AH4" s="17" t="n"/>
-      <c r="AI4" s="18" t="inlineStr">
-        <is>
-          <t>1マス＝</t>
-        </is>
-      </c>
-      <c r="AJ4" s="19" t="n"/>
-      <c r="AK4" s="19" t="n"/>
-      <c r="AL4" s="20" t="n"/>
-      <c r="AM4" s="21" t="n"/>
-      <c r="AN4" s="22" t="n"/>
-      <c r="AO4" s="23" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="AP4" s="24" t="n"/>
+      <c r="AI4" s="17" t="n"/>
+      <c r="AJ4" s="17" t="n"/>
+      <c r="AK4" s="17" t="n"/>
+      <c r="AL4" s="17" t="n"/>
+      <c r="AM4" s="17" t="n"/>
+      <c r="AN4" s="17" t="n"/>
+      <c r="AO4" s="17" t="n"/>
+      <c r="AP4" s="18" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
@@ -1232,31 +1172,31 @@
       <c r="Q5" s="8" t="n"/>
       <c r="R5" s="8" t="n"/>
       <c r="S5" s="8" t="n"/>
-      <c r="T5" s="26" t="n"/>
-      <c r="V5" s="27" t="n"/>
-      <c r="W5" s="28" t="n"/>
-      <c r="X5" s="28" t="n"/>
-      <c r="Y5" s="28" t="n"/>
-      <c r="Z5" s="28" t="n"/>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="28" t="n"/>
-      <c r="AD5" s="28" t="n"/>
-      <c r="AE5" s="28" t="n"/>
-      <c r="AF5" s="28" t="n"/>
-      <c r="AG5" s="28" t="n"/>
-      <c r="AH5" s="28" t="n"/>
-      <c r="AI5" s="28" t="n"/>
-      <c r="AJ5" s="28" t="n"/>
-      <c r="AK5" s="28" t="n"/>
-      <c r="AL5" s="28" t="n"/>
-      <c r="AM5" s="28" t="n"/>
-      <c r="AN5" s="28" t="n"/>
-      <c r="AO5" s="28" t="n"/>
-      <c r="AP5" s="29" t="n"/>
+      <c r="T5" s="20" t="n"/>
+      <c r="V5" s="21" t="n"/>
+      <c r="W5" s="22" t="n"/>
+      <c r="X5" s="22" t="n"/>
+      <c r="Y5" s="22" t="n"/>
+      <c r="Z5" s="22" t="n"/>
+      <c r="AA5" s="22" t="n"/>
+      <c r="AB5" s="22" t="n"/>
+      <c r="AC5" s="22" t="n"/>
+      <c r="AD5" s="22" t="n"/>
+      <c r="AE5" s="22" t="n"/>
+      <c r="AF5" s="22" t="n"/>
+      <c r="AG5" s="22" t="n"/>
+      <c r="AH5" s="22" t="n"/>
+      <c r="AI5" s="22" t="n"/>
+      <c r="AJ5" s="22" t="n"/>
+      <c r="AK5" s="22" t="n"/>
+      <c r="AL5" s="22" t="n"/>
+      <c r="AM5" s="22" t="n"/>
+      <c r="AN5" s="22" t="n"/>
+      <c r="AO5" s="22" t="n"/>
+      <c r="AP5" s="23" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>電話番号</t>
         </is>
@@ -1264,67 +1204,67 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>自宅</t>
         </is>
       </c>
-      <c r="F6" s="31" t="n"/>
+      <c r="F6" s="25" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="8" t="n"/>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="9" t="n"/>
-      <c r="M6" s="30" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t>携帯</t>
         </is>
       </c>
-      <c r="N6" s="31" t="n"/>
+      <c r="N6" s="25" t="n"/>
       <c r="O6" s="7" t="n"/>
       <c r="P6" s="8" t="n"/>
       <c r="Q6" s="8" t="n"/>
       <c r="R6" s="8" t="n"/>
       <c r="S6" s="8" t="n"/>
-      <c r="T6" s="26" t="n"/>
-      <c r="V6" s="27" t="n"/>
-      <c r="W6" s="28" t="n"/>
-      <c r="X6" s="28" t="n"/>
-      <c r="Y6" s="28" t="n"/>
-      <c r="Z6" s="28" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="28" t="n"/>
-      <c r="AD6" s="28" t="n"/>
-      <c r="AE6" s="28" t="n"/>
-      <c r="AF6" s="28" t="n"/>
-      <c r="AG6" s="28" t="n"/>
-      <c r="AH6" s="28" t="n"/>
-      <c r="AI6" s="28" t="n"/>
-      <c r="AJ6" s="28" t="n"/>
-      <c r="AK6" s="28" t="n"/>
-      <c r="AL6" s="28" t="n"/>
-      <c r="AM6" s="28" t="n"/>
-      <c r="AN6" s="28" t="n"/>
-      <c r="AO6" s="28" t="n"/>
-      <c r="AP6" s="29" t="n"/>
+      <c r="T6" s="20" t="n"/>
+      <c r="V6" s="21" t="n"/>
+      <c r="W6" s="22" t="n"/>
+      <c r="X6" s="22" t="n"/>
+      <c r="Y6" s="22" t="n"/>
+      <c r="Z6" s="22" t="n"/>
+      <c r="AA6" s="22" t="n"/>
+      <c r="AB6" s="22" t="n"/>
+      <c r="AC6" s="22" t="n"/>
+      <c r="AD6" s="22" t="n"/>
+      <c r="AE6" s="22" t="n"/>
+      <c r="AF6" s="22" t="n"/>
+      <c r="AG6" s="22" t="n"/>
+      <c r="AH6" s="22" t="n"/>
+      <c r="AI6" s="22" t="n"/>
+      <c r="AJ6" s="22" t="n"/>
+      <c r="AK6" s="22" t="n"/>
+      <c r="AL6" s="22" t="n"/>
+      <c r="AM6" s="22" t="n"/>
+      <c r="AN6" s="22" t="n"/>
+      <c r="AO6" s="22" t="n"/>
+      <c r="AP6" s="23" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>キーパーソン</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="F7" s="31" t="n"/>
+      <c r="F7" s="25" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="8" t="n"/>
@@ -1333,49 +1273,49 @@
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="9" t="n"/>
-      <c r="O7" s="30" t="inlineStr">
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t>続柄</t>
         </is>
       </c>
-      <c r="P7" s="31" t="n"/>
+      <c r="P7" s="25" t="n"/>
       <c r="Q7" s="7" t="n"/>
       <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="n"/>
-      <c r="T7" s="26" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="28" t="n"/>
-      <c r="X7" s="28" t="n"/>
-      <c r="Y7" s="28" t="n"/>
-      <c r="Z7" s="28" t="n"/>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="28" t="n"/>
-      <c r="AD7" s="28" t="n"/>
-      <c r="AE7" s="28" t="n"/>
-      <c r="AF7" s="28" t="n"/>
-      <c r="AG7" s="28" t="n"/>
-      <c r="AH7" s="28" t="n"/>
-      <c r="AI7" s="28" t="n"/>
-      <c r="AJ7" s="28" t="n"/>
-      <c r="AK7" s="28" t="n"/>
-      <c r="AL7" s="28" t="n"/>
-      <c r="AM7" s="28" t="n"/>
-      <c r="AN7" s="28" t="n"/>
-      <c r="AO7" s="28" t="n"/>
-      <c r="AP7" s="29" t="n"/>
+      <c r="T7" s="20" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="22" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="22" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="22" t="n"/>
+      <c r="AF7" s="22" t="n"/>
+      <c r="AG7" s="22" t="n"/>
+      <c r="AH7" s="22" t="n"/>
+      <c r="AI7" s="22" t="n"/>
+      <c r="AJ7" s="22" t="n"/>
+      <c r="AK7" s="22" t="n"/>
+      <c r="AL7" s="22" t="n"/>
+      <c r="AM7" s="22" t="n"/>
+      <c r="AN7" s="22" t="n"/>
+      <c r="AO7" s="22" t="n"/>
+      <c r="AP7" s="23" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="37" t="n"/>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="30" t="n"/>
+      <c r="C8" s="30" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="F8" s="31" t="n"/>
+      <c r="F8" s="25" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
@@ -1389,146 +1329,146 @@
       <c r="Q8" s="8" t="n"/>
       <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="n"/>
-      <c r="T8" s="26" t="n"/>
-      <c r="V8" s="27" t="n"/>
-      <c r="W8" s="28" t="n"/>
-      <c r="X8" s="28" t="n"/>
-      <c r="Y8" s="28" t="n"/>
-      <c r="Z8" s="28" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="28" t="n"/>
-      <c r="AD8" s="28" t="n"/>
-      <c r="AE8" s="28" t="n"/>
-      <c r="AF8" s="28" t="n"/>
-      <c r="AG8" s="28" t="n"/>
-      <c r="AH8" s="28" t="n"/>
-      <c r="AI8" s="28" t="n"/>
-      <c r="AJ8" s="28" t="n"/>
-      <c r="AK8" s="28" t="n"/>
-      <c r="AL8" s="28" t="n"/>
-      <c r="AM8" s="28" t="n"/>
-      <c r="AN8" s="28" t="n"/>
-      <c r="AO8" s="28" t="n"/>
-      <c r="AP8" s="29" t="n"/>
+      <c r="T8" s="20" t="n"/>
+      <c r="V8" s="21" t="n"/>
+      <c r="W8" s="22" t="n"/>
+      <c r="X8" s="22" t="n"/>
+      <c r="Y8" s="22" t="n"/>
+      <c r="Z8" s="22" t="n"/>
+      <c r="AA8" s="22" t="n"/>
+      <c r="AB8" s="22" t="n"/>
+      <c r="AC8" s="22" t="n"/>
+      <c r="AD8" s="22" t="n"/>
+      <c r="AE8" s="22" t="n"/>
+      <c r="AF8" s="22" t="n"/>
+      <c r="AG8" s="22" t="n"/>
+      <c r="AH8" s="22" t="n"/>
+      <c r="AI8" s="22" t="n"/>
+      <c r="AJ8" s="22" t="n"/>
+      <c r="AK8" s="22" t="n"/>
+      <c r="AL8" s="22" t="n"/>
+      <c r="AM8" s="22" t="n"/>
+      <c r="AN8" s="22" t="n"/>
+      <c r="AO8" s="22" t="n"/>
+      <c r="AP8" s="23" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>連絡がつきやすい
 曜日・時間帯</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n"/>
-      <c r="C9" s="39" t="n"/>
-      <c r="D9" s="40" t="n"/>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="B9" s="33" t="n"/>
+      <c r="C9" s="33" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>本人</t>
         </is>
       </c>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="31" t="n"/>
-      <c r="H9" s="42" t="inlineStr">
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="36" t="inlineStr">
         <is>
           <t>月　火　水　木　金　土　日</t>
         </is>
       </c>
-      <c r="I9" s="43" t="n"/>
-      <c r="J9" s="43" t="n"/>
-      <c r="K9" s="43" t="n"/>
-      <c r="L9" s="43" t="n"/>
-      <c r="M9" s="43" t="n"/>
-      <c r="N9" s="44" t="n"/>
-      <c r="O9" s="45" t="inlineStr">
+      <c r="I9" s="37" t="n"/>
+      <c r="J9" s="37" t="n"/>
+      <c r="K9" s="37" t="n"/>
+      <c r="L9" s="37" t="n"/>
+      <c r="M9" s="37" t="n"/>
+      <c r="N9" s="38" t="n"/>
+      <c r="O9" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">　　時 ～ 　　時</t>
         </is>
       </c>
-      <c r="P9" s="43" t="n"/>
-      <c r="Q9" s="43" t="n"/>
-      <c r="R9" s="43" t="n"/>
-      <c r="S9" s="43" t="n"/>
-      <c r="T9" s="46" t="n"/>
-      <c r="V9" s="27" t="n"/>
-      <c r="W9" s="28" t="n"/>
-      <c r="X9" s="28" t="n"/>
-      <c r="Y9" s="28" t="n"/>
-      <c r="Z9" s="28" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="28" t="n"/>
-      <c r="AD9" s="28" t="n"/>
-      <c r="AE9" s="28" t="n"/>
-      <c r="AF9" s="28" t="n"/>
-      <c r="AG9" s="28" t="n"/>
-      <c r="AH9" s="28" t="n"/>
-      <c r="AI9" s="28" t="n"/>
-      <c r="AJ9" s="28" t="n"/>
-      <c r="AK9" s="28" t="n"/>
-      <c r="AL9" s="28" t="n"/>
-      <c r="AM9" s="28" t="n"/>
-      <c r="AN9" s="28" t="n"/>
-      <c r="AO9" s="28" t="n"/>
-      <c r="AP9" s="29" t="n"/>
+      <c r="P9" s="37" t="n"/>
+      <c r="Q9" s="37" t="n"/>
+      <c r="R9" s="37" t="n"/>
+      <c r="S9" s="37" t="n"/>
+      <c r="T9" s="40" t="n"/>
+      <c r="V9" s="21" t="n"/>
+      <c r="W9" s="22" t="n"/>
+      <c r="X9" s="22" t="n"/>
+      <c r="Y9" s="22" t="n"/>
+      <c r="Z9" s="22" t="n"/>
+      <c r="AA9" s="22" t="n"/>
+      <c r="AB9" s="22" t="n"/>
+      <c r="AC9" s="22" t="n"/>
+      <c r="AD9" s="22" t="n"/>
+      <c r="AE9" s="22" t="n"/>
+      <c r="AF9" s="22" t="n"/>
+      <c r="AG9" s="22" t="n"/>
+      <c r="AH9" s="22" t="n"/>
+      <c r="AI9" s="22" t="n"/>
+      <c r="AJ9" s="22" t="n"/>
+      <c r="AK9" s="22" t="n"/>
+      <c r="AL9" s="22" t="n"/>
+      <c r="AM9" s="22" t="n"/>
+      <c r="AN9" s="22" t="n"/>
+      <c r="AO9" s="22" t="n"/>
+      <c r="AP9" s="23" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="47" t="n"/>
-      <c r="B10" s="48" t="n"/>
-      <c r="C10" s="48" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="50" t="inlineStr">
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="43" t="n"/>
+      <c r="E10" s="44" t="inlineStr">
         <is>
           <t>キーパーソン</t>
         </is>
       </c>
-      <c r="F10" s="51" t="n"/>
-      <c r="G10" s="52" t="n"/>
-      <c r="H10" s="42" t="inlineStr">
+      <c r="F10" s="45" t="n"/>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>月　火　水　木　金　土　日</t>
         </is>
       </c>
-      <c r="I10" s="43" t="n"/>
-      <c r="J10" s="43" t="n"/>
-      <c r="K10" s="43" t="n"/>
-      <c r="L10" s="43" t="n"/>
-      <c r="M10" s="43" t="n"/>
-      <c r="N10" s="44" t="n"/>
-      <c r="O10" s="45" t="inlineStr">
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="37" t="n"/>
+      <c r="K10" s="37" t="n"/>
+      <c r="L10" s="37" t="n"/>
+      <c r="M10" s="37" t="n"/>
+      <c r="N10" s="38" t="n"/>
+      <c r="O10" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">　　時 ～ 　　時</t>
         </is>
       </c>
-      <c r="P10" s="43" t="n"/>
-      <c r="Q10" s="43" t="n"/>
-      <c r="R10" s="43" t="n"/>
-      <c r="S10" s="43" t="n"/>
-      <c r="T10" s="46" t="n"/>
-      <c r="V10" s="27" t="n"/>
-      <c r="W10" s="28" t="n"/>
-      <c r="X10" s="28" t="n"/>
-      <c r="Y10" s="28" t="n"/>
-      <c r="Z10" s="28" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="28" t="n"/>
-      <c r="AD10" s="28" t="n"/>
-      <c r="AE10" s="28" t="n"/>
-      <c r="AF10" s="28" t="n"/>
-      <c r="AG10" s="28" t="n"/>
-      <c r="AH10" s="28" t="n"/>
-      <c r="AI10" s="28" t="n"/>
-      <c r="AJ10" s="28" t="n"/>
-      <c r="AK10" s="28" t="n"/>
-      <c r="AL10" s="28" t="n"/>
-      <c r="AM10" s="28" t="n"/>
-      <c r="AN10" s="28" t="n"/>
-      <c r="AO10" s="28" t="n"/>
-      <c r="AP10" s="29" t="n"/>
+      <c r="P10" s="37" t="n"/>
+      <c r="Q10" s="37" t="n"/>
+      <c r="R10" s="37" t="n"/>
+      <c r="S10" s="37" t="n"/>
+      <c r="T10" s="40" t="n"/>
+      <c r="V10" s="21" t="n"/>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="22" t="n"/>
+      <c r="Y10" s="22" t="n"/>
+      <c r="Z10" s="22" t="n"/>
+      <c r="AA10" s="22" t="n"/>
+      <c r="AB10" s="22" t="n"/>
+      <c r="AC10" s="22" t="n"/>
+      <c r="AD10" s="22" t="n"/>
+      <c r="AE10" s="22" t="n"/>
+      <c r="AF10" s="22" t="n"/>
+      <c r="AG10" s="22" t="n"/>
+      <c r="AH10" s="22" t="n"/>
+      <c r="AI10" s="22" t="n"/>
+      <c r="AJ10" s="22" t="n"/>
+      <c r="AK10" s="22" t="n"/>
+      <c r="AL10" s="22" t="n"/>
+      <c r="AM10" s="22" t="n"/>
+      <c r="AN10" s="22" t="n"/>
+      <c r="AO10" s="22" t="n"/>
+      <c r="AP10" s="23" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>担当ケアマネ</t>
         </is>
@@ -1536,13 +1476,13 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="F11" s="41" t="n"/>
-      <c r="G11" s="31" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="25" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
@@ -1550,40 +1490,40 @@
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="9" t="n"/>
-      <c r="O11" s="30" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="P11" s="31" t="n"/>
+      <c r="P11" s="25" t="n"/>
       <c r="Q11" s="7" t="n"/>
       <c r="R11" s="8" t="n"/>
       <c r="S11" s="8" t="n"/>
-      <c r="T11" s="26" t="n"/>
-      <c r="V11" s="27" t="n"/>
-      <c r="W11" s="28" t="n"/>
-      <c r="X11" s="28" t="n"/>
-      <c r="Y11" s="28" t="n"/>
-      <c r="Z11" s="28" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="28" t="n"/>
-      <c r="AD11" s="28" t="n"/>
-      <c r="AE11" s="28" t="n"/>
-      <c r="AF11" s="28" t="n"/>
-      <c r="AG11" s="28" t="n"/>
-      <c r="AH11" s="28" t="n"/>
-      <c r="AI11" s="28" t="n"/>
-      <c r="AJ11" s="28" t="n"/>
-      <c r="AK11" s="28" t="n"/>
-      <c r="AL11" s="28" t="n"/>
-      <c r="AM11" s="28" t="n"/>
-      <c r="AN11" s="28" t="n"/>
-      <c r="AO11" s="28" t="n"/>
-      <c r="AP11" s="29" t="n"/>
+      <c r="T11" s="20" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="22" t="n"/>
+      <c r="Y11" s="22" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="22" t="n"/>
+      <c r="AB11" s="22" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AD11" s="22" t="n"/>
+      <c r="AE11" s="22" t="n"/>
+      <c r="AF11" s="22" t="n"/>
+      <c r="AG11" s="22" t="n"/>
+      <c r="AH11" s="22" t="n"/>
+      <c r="AI11" s="22" t="n"/>
+      <c r="AJ11" s="22" t="n"/>
+      <c r="AK11" s="22" t="n"/>
+      <c r="AL11" s="22" t="n"/>
+      <c r="AM11" s="22" t="n"/>
+      <c r="AN11" s="22" t="n"/>
+      <c r="AO11" s="22" t="n"/>
+      <c r="AP11" s="23" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>負担割合</t>
         </is>
@@ -1591,58 +1531,58 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="53" t="inlineStr">
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>□1割</t>
         </is>
       </c>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
-      <c r="H12" s="54" t="inlineStr">
+      <c r="H12" s="48" t="inlineStr">
         <is>
           <t>□2割</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
-      <c r="K12" s="54" t="inlineStr">
+      <c r="K12" s="48" t="inlineStr">
         <is>
           <t>□3割</t>
         </is>
       </c>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
-      <c r="N12" s="55" t="n"/>
+      <c r="N12" s="49" t="n"/>
       <c r="O12" s="8" t="n"/>
       <c r="P12" s="8" t="n"/>
       <c r="Q12" s="8" t="n"/>
       <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="V12" s="27" t="n"/>
-      <c r="W12" s="28" t="n"/>
-      <c r="X12" s="28" t="n"/>
-      <c r="Y12" s="28" t="n"/>
-      <c r="Z12" s="28" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="28" t="n"/>
-      <c r="AD12" s="28" t="n"/>
-      <c r="AE12" s="28" t="n"/>
-      <c r="AF12" s="28" t="n"/>
-      <c r="AG12" s="28" t="n"/>
-      <c r="AH12" s="28" t="n"/>
-      <c r="AI12" s="28" t="n"/>
-      <c r="AJ12" s="28" t="n"/>
-      <c r="AK12" s="28" t="n"/>
-      <c r="AL12" s="28" t="n"/>
-      <c r="AM12" s="28" t="n"/>
-      <c r="AN12" s="28" t="n"/>
-      <c r="AO12" s="28" t="n"/>
-      <c r="AP12" s="29" t="n"/>
+      <c r="T12" s="20" t="n"/>
+      <c r="V12" s="21" t="n"/>
+      <c r="W12" s="22" t="n"/>
+      <c r="X12" s="22" t="n"/>
+      <c r="Y12" s="22" t="n"/>
+      <c r="Z12" s="22" t="n"/>
+      <c r="AA12" s="22" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+      <c r="AE12" s="22" t="n"/>
+      <c r="AF12" s="22" t="n"/>
+      <c r="AG12" s="22" t="n"/>
+      <c r="AH12" s="22" t="n"/>
+      <c r="AI12" s="22" t="n"/>
+      <c r="AJ12" s="22" t="n"/>
+      <c r="AK12" s="22" t="n"/>
+      <c r="AL12" s="22" t="n"/>
+      <c r="AM12" s="22" t="n"/>
+      <c r="AN12" s="22" t="n"/>
+      <c r="AO12" s="22" t="n"/>
+      <c r="AP12" s="23" t="n"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>疾患名</t>
         </is>
@@ -1665,123 +1605,123 @@
       <c r="Q13" s="8" t="n"/>
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="n"/>
-      <c r="T13" s="26" t="n"/>
-      <c r="V13" s="27" t="n"/>
-      <c r="W13" s="28" t="n"/>
-      <c r="X13" s="28" t="n"/>
-      <c r="Y13" s="28" t="n"/>
-      <c r="Z13" s="28" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="28" t="n"/>
-      <c r="AD13" s="28" t="n"/>
-      <c r="AE13" s="28" t="n"/>
-      <c r="AF13" s="28" t="n"/>
-      <c r="AG13" s="28" t="n"/>
-      <c r="AH13" s="28" t="n"/>
-      <c r="AI13" s="28" t="n"/>
-      <c r="AJ13" s="28" t="n"/>
-      <c r="AK13" s="28" t="n"/>
-      <c r="AL13" s="28" t="n"/>
-      <c r="AM13" s="28" t="n"/>
-      <c r="AN13" s="28" t="n"/>
-      <c r="AO13" s="28" t="n"/>
-      <c r="AP13" s="29" t="n"/>
+      <c r="T13" s="20" t="n"/>
+      <c r="V13" s="21" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="22" t="n"/>
+      <c r="Y13" s="22" t="n"/>
+      <c r="Z13" s="22" t="n"/>
+      <c r="AA13" s="22" t="n"/>
+      <c r="AB13" s="22" t="n"/>
+      <c r="AC13" s="22" t="n"/>
+      <c r="AD13" s="22" t="n"/>
+      <c r="AE13" s="22" t="n"/>
+      <c r="AF13" s="22" t="n"/>
+      <c r="AG13" s="22" t="n"/>
+      <c r="AH13" s="22" t="n"/>
+      <c r="AI13" s="22" t="n"/>
+      <c r="AJ13" s="22" t="n"/>
+      <c r="AK13" s="22" t="n"/>
+      <c r="AL13" s="22" t="n"/>
+      <c r="AM13" s="22" t="n"/>
+      <c r="AN13" s="22" t="n"/>
+      <c r="AO13" s="22" t="n"/>
+      <c r="AP13" s="23" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="56" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>麻痺</t>
         </is>
       </c>
-      <c r="B14" s="57" t="n"/>
-      <c r="C14" s="57" t="n"/>
-      <c r="D14" s="58" t="n"/>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="B14" s="51" t="n"/>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="53" t="inlineStr">
         <is>
           <t>□なし</t>
         </is>
       </c>
-      <c r="F14" s="60" t="n"/>
-      <c r="G14" s="61" t="inlineStr">
+      <c r="F14" s="54" t="n"/>
+      <c r="G14" s="55" t="inlineStr">
         <is>
           <t>□右片麻痺</t>
         </is>
       </c>
-      <c r="H14" s="60" t="n"/>
-      <c r="I14" s="60" t="n"/>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n"/>
+      <c r="J14" s="55" t="inlineStr">
         <is>
           <t>□左片麻痺</t>
         </is>
       </c>
-      <c r="K14" s="60" t="n"/>
-      <c r="L14" s="60" t="n"/>
-      <c r="M14" s="61" t="inlineStr">
+      <c r="K14" s="54" t="n"/>
+      <c r="L14" s="54" t="n"/>
+      <c r="M14" s="55" t="inlineStr">
         <is>
           <t>□その他</t>
         </is>
       </c>
-      <c r="N14" s="60" t="n"/>
-      <c r="O14" s="60" t="n"/>
-      <c r="P14" s="62" t="inlineStr">
+      <c r="N14" s="54" t="n"/>
+      <c r="O14" s="54" t="n"/>
+      <c r="P14" s="56" t="inlineStr">
         <is>
           <t>（　　　　）</t>
         </is>
       </c>
-      <c r="Q14" s="63" t="n"/>
-      <c r="R14" s="63" t="n"/>
-      <c r="S14" s="63" t="n"/>
-      <c r="T14" s="64" t="n"/>
-      <c r="V14" s="27" t="n"/>
-      <c r="W14" s="28" t="n"/>
-      <c r="X14" s="28" t="n"/>
-      <c r="Y14" s="28" t="n"/>
-      <c r="Z14" s="28" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="28" t="n"/>
-      <c r="AD14" s="28" t="n"/>
-      <c r="AE14" s="28" t="n"/>
-      <c r="AF14" s="28" t="n"/>
-      <c r="AG14" s="28" t="n"/>
-      <c r="AH14" s="28" t="n"/>
-      <c r="AI14" s="28" t="n"/>
-      <c r="AJ14" s="28" t="n"/>
-      <c r="AK14" s="28" t="n"/>
-      <c r="AL14" s="28" t="n"/>
-      <c r="AM14" s="28" t="n"/>
-      <c r="AN14" s="28" t="n"/>
-      <c r="AO14" s="28" t="n"/>
-      <c r="AP14" s="29" t="n"/>
+      <c r="Q14" s="57" t="n"/>
+      <c r="R14" s="57" t="n"/>
+      <c r="S14" s="57" t="n"/>
+      <c r="T14" s="58" t="n"/>
+      <c r="V14" s="21" t="n"/>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="22" t="n"/>
+      <c r="Y14" s="22" t="n"/>
+      <c r="Z14" s="22" t="n"/>
+      <c r="AA14" s="22" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="22" t="n"/>
+      <c r="AF14" s="22" t="n"/>
+      <c r="AG14" s="22" t="n"/>
+      <c r="AH14" s="22" t="n"/>
+      <c r="AI14" s="22" t="n"/>
+      <c r="AJ14" s="22" t="n"/>
+      <c r="AK14" s="22" t="n"/>
+      <c r="AL14" s="22" t="n"/>
+      <c r="AM14" s="22" t="n"/>
+      <c r="AN14" s="22" t="n"/>
+      <c r="AO14" s="22" t="n"/>
+      <c r="AP14" s="23" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="V15" s="27" t="n"/>
-      <c r="W15" s="28" t="n"/>
-      <c r="X15" s="28" t="n"/>
-      <c r="Y15" s="28" t="n"/>
-      <c r="Z15" s="28" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="28" t="n"/>
-      <c r="AD15" s="28" t="n"/>
-      <c r="AE15" s="28" t="n"/>
-      <c r="AF15" s="28" t="n"/>
-      <c r="AG15" s="28" t="n"/>
-      <c r="AH15" s="28" t="n"/>
-      <c r="AI15" s="28" t="n"/>
-      <c r="AJ15" s="28" t="n"/>
-      <c r="AK15" s="28" t="n"/>
-      <c r="AL15" s="28" t="n"/>
-      <c r="AM15" s="28" t="n"/>
-      <c r="AN15" s="28" t="n"/>
-      <c r="AO15" s="28" t="n"/>
-      <c r="AP15" s="29" t="n"/>
+      <c r="V15" s="21" t="n"/>
+      <c r="W15" s="22" t="n"/>
+      <c r="X15" s="22" t="n"/>
+      <c r="Y15" s="22" t="n"/>
+      <c r="Z15" s="22" t="n"/>
+      <c r="AA15" s="22" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+      <c r="AE15" s="22" t="n"/>
+      <c r="AF15" s="22" t="n"/>
+      <c r="AG15" s="22" t="n"/>
+      <c r="AH15" s="22" t="n"/>
+      <c r="AI15" s="22" t="n"/>
+      <c r="AJ15" s="22" t="n"/>
+      <c r="AK15" s="22" t="n"/>
+      <c r="AL15" s="22" t="n"/>
+      <c r="AM15" s="22" t="n"/>
+      <c r="AN15" s="22" t="n"/>
+      <c r="AO15" s="22" t="n"/>
+      <c r="AP15" s="23" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="65" t="inlineStr">
-        <is>
-          <t>改修項目（①～⑫は平面図の番号と対応）　単位：mm</t>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>改修項目</t>
         </is>
       </c>
       <c r="B16" s="17" t="n"/>
@@ -1802,31 +1742,31 @@
       <c r="Q16" s="17" t="n"/>
       <c r="R16" s="17" t="n"/>
       <c r="S16" s="17" t="n"/>
-      <c r="T16" s="66" t="n"/>
-      <c r="V16" s="27" t="n"/>
-      <c r="W16" s="28" t="n"/>
-      <c r="X16" s="28" t="n"/>
-      <c r="Y16" s="28" t="n"/>
-      <c r="Z16" s="28" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="28" t="n"/>
-      <c r="AD16" s="28" t="n"/>
-      <c r="AE16" s="28" t="n"/>
-      <c r="AF16" s="28" t="n"/>
-      <c r="AG16" s="28" t="n"/>
-      <c r="AH16" s="28" t="n"/>
-      <c r="AI16" s="28" t="n"/>
-      <c r="AJ16" s="28" t="n"/>
-      <c r="AK16" s="28" t="n"/>
-      <c r="AL16" s="28" t="n"/>
-      <c r="AM16" s="28" t="n"/>
-      <c r="AN16" s="28" t="n"/>
-      <c r="AO16" s="28" t="n"/>
-      <c r="AP16" s="29" t="n"/>
+      <c r="T16" s="18" t="n"/>
+      <c r="V16" s="21" t="n"/>
+      <c r="W16" s="22" t="n"/>
+      <c r="X16" s="22" t="n"/>
+      <c r="Y16" s="22" t="n"/>
+      <c r="Z16" s="22" t="n"/>
+      <c r="AA16" s="22" t="n"/>
+      <c r="AB16" s="22" t="n"/>
+      <c r="AC16" s="22" t="n"/>
+      <c r="AD16" s="22" t="n"/>
+      <c r="AE16" s="22" t="n"/>
+      <c r="AF16" s="22" t="n"/>
+      <c r="AG16" s="22" t="n"/>
+      <c r="AH16" s="22" t="n"/>
+      <c r="AI16" s="22" t="n"/>
+      <c r="AJ16" s="22" t="n"/>
+      <c r="AK16" s="22" t="n"/>
+      <c r="AL16" s="22" t="n"/>
+      <c r="AM16" s="22" t="n"/>
+      <c r="AN16" s="22" t="n"/>
+      <c r="AO16" s="22" t="n"/>
+      <c r="AP16" s="23" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
@@ -1852,44 +1792,44 @@
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="30" t="inlineStr">
+      <c r="O17" s="24" t="inlineStr">
         <is>
           <t>手すり長さ</t>
         </is>
       </c>
-      <c r="P17" s="41" t="n"/>
-      <c r="Q17" s="31" t="n"/>
-      <c r="R17" s="30" t="inlineStr">
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="25" t="n"/>
+      <c r="R17" s="24" t="inlineStr">
         <is>
           <t>手すり高さ</t>
         </is>
       </c>
-      <c r="S17" s="41" t="n"/>
-      <c r="T17" s="68" t="n"/>
-      <c r="V17" s="27" t="n"/>
-      <c r="W17" s="28" t="n"/>
-      <c r="X17" s="28" t="n"/>
-      <c r="Y17" s="28" t="n"/>
-      <c r="Z17" s="28" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="28" t="n"/>
-      <c r="AD17" s="28" t="n"/>
-      <c r="AE17" s="28" t="n"/>
-      <c r="AF17" s="28" t="n"/>
-      <c r="AG17" s="28" t="n"/>
-      <c r="AH17" s="28" t="n"/>
-      <c r="AI17" s="28" t="n"/>
-      <c r="AJ17" s="28" t="n"/>
-      <c r="AK17" s="28" t="n"/>
-      <c r="AL17" s="28" t="n"/>
-      <c r="AM17" s="28" t="n"/>
-      <c r="AN17" s="28" t="n"/>
-      <c r="AO17" s="28" t="n"/>
-      <c r="AP17" s="29" t="n"/>
+      <c r="S17" s="35" t="n"/>
+      <c r="T17" s="60" t="n"/>
+      <c r="V17" s="21" t="n"/>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="22" t="n"/>
+      <c r="Y17" s="22" t="n"/>
+      <c r="Z17" s="22" t="n"/>
+      <c r="AA17" s="22" t="n"/>
+      <c r="AB17" s="22" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AD17" s="22" t="n"/>
+      <c r="AE17" s="22" t="n"/>
+      <c r="AF17" s="22" t="n"/>
+      <c r="AG17" s="22" t="n"/>
+      <c r="AH17" s="22" t="n"/>
+      <c r="AI17" s="22" t="n"/>
+      <c r="AJ17" s="22" t="n"/>
+      <c r="AK17" s="22" t="n"/>
+      <c r="AL17" s="22" t="n"/>
+      <c r="AM17" s="22" t="n"/>
+      <c r="AN17" s="22" t="n"/>
+      <c r="AO17" s="22" t="n"/>
+      <c r="AP17" s="23" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="69" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>①</t>
         </is>
@@ -1907,36 +1847,36 @@
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="9" t="n"/>
-      <c r="O18" s="70" t="n"/>
+      <c r="O18" s="62" t="n"/>
       <c r="P18" s="8" t="n"/>
       <c r="Q18" s="9" t="n"/>
-      <c r="R18" s="70" t="n"/>
+      <c r="R18" s="62" t="n"/>
       <c r="S18" s="8" t="n"/>
-      <c r="T18" s="26" t="n"/>
-      <c r="V18" s="27" t="n"/>
-      <c r="W18" s="28" t="n"/>
-      <c r="X18" s="28" t="n"/>
-      <c r="Y18" s="28" t="n"/>
-      <c r="Z18" s="28" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="28" t="n"/>
-      <c r="AD18" s="28" t="n"/>
-      <c r="AE18" s="28" t="n"/>
-      <c r="AF18" s="28" t="n"/>
-      <c r="AG18" s="28" t="n"/>
-      <c r="AH18" s="28" t="n"/>
-      <c r="AI18" s="28" t="n"/>
-      <c r="AJ18" s="28" t="n"/>
-      <c r="AK18" s="28" t="n"/>
-      <c r="AL18" s="28" t="n"/>
-      <c r="AM18" s="28" t="n"/>
-      <c r="AN18" s="28" t="n"/>
-      <c r="AO18" s="28" t="n"/>
-      <c r="AP18" s="29" t="n"/>
+      <c r="T18" s="20" t="n"/>
+      <c r="V18" s="21" t="n"/>
+      <c r="W18" s="22" t="n"/>
+      <c r="X18" s="22" t="n"/>
+      <c r="Y18" s="22" t="n"/>
+      <c r="Z18" s="22" t="n"/>
+      <c r="AA18" s="22" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+      <c r="AE18" s="22" t="n"/>
+      <c r="AF18" s="22" t="n"/>
+      <c r="AG18" s="22" t="n"/>
+      <c r="AH18" s="22" t="n"/>
+      <c r="AI18" s="22" t="n"/>
+      <c r="AJ18" s="22" t="n"/>
+      <c r="AK18" s="22" t="n"/>
+      <c r="AL18" s="22" t="n"/>
+      <c r="AM18" s="22" t="n"/>
+      <c r="AN18" s="22" t="n"/>
+      <c r="AO18" s="22" t="n"/>
+      <c r="AP18" s="23" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="69" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>②</t>
         </is>
@@ -1954,36 +1894,36 @@
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
       <c r="N19" s="9" t="n"/>
-      <c r="O19" s="70" t="n"/>
+      <c r="O19" s="62" t="n"/>
       <c r="P19" s="8" t="n"/>
       <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="70" t="n"/>
+      <c r="R19" s="62" t="n"/>
       <c r="S19" s="8" t="n"/>
-      <c r="T19" s="26" t="n"/>
-      <c r="V19" s="27" t="n"/>
-      <c r="W19" s="28" t="n"/>
-      <c r="X19" s="28" t="n"/>
-      <c r="Y19" s="28" t="n"/>
-      <c r="Z19" s="28" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="28" t="n"/>
-      <c r="AD19" s="28" t="n"/>
-      <c r="AE19" s="28" t="n"/>
-      <c r="AF19" s="28" t="n"/>
-      <c r="AG19" s="28" t="n"/>
-      <c r="AH19" s="28" t="n"/>
-      <c r="AI19" s="28" t="n"/>
-      <c r="AJ19" s="28" t="n"/>
-      <c r="AK19" s="28" t="n"/>
-      <c r="AL19" s="28" t="n"/>
-      <c r="AM19" s="28" t="n"/>
-      <c r="AN19" s="28" t="n"/>
-      <c r="AO19" s="28" t="n"/>
-      <c r="AP19" s="29" t="n"/>
+      <c r="T19" s="20" t="n"/>
+      <c r="V19" s="21" t="n"/>
+      <c r="W19" s="22" t="n"/>
+      <c r="X19" s="22" t="n"/>
+      <c r="Y19" s="22" t="n"/>
+      <c r="Z19" s="22" t="n"/>
+      <c r="AA19" s="22" t="n"/>
+      <c r="AB19" s="22" t="n"/>
+      <c r="AC19" s="22" t="n"/>
+      <c r="AD19" s="22" t="n"/>
+      <c r="AE19" s="22" t="n"/>
+      <c r="AF19" s="22" t="n"/>
+      <c r="AG19" s="22" t="n"/>
+      <c r="AH19" s="22" t="n"/>
+      <c r="AI19" s="22" t="n"/>
+      <c r="AJ19" s="22" t="n"/>
+      <c r="AK19" s="22" t="n"/>
+      <c r="AL19" s="22" t="n"/>
+      <c r="AM19" s="22" t="n"/>
+      <c r="AN19" s="22" t="n"/>
+      <c r="AO19" s="22" t="n"/>
+      <c r="AP19" s="23" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="69" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>③</t>
         </is>
@@ -2001,36 +1941,36 @@
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="9" t="n"/>
-      <c r="O20" s="70" t="n"/>
+      <c r="O20" s="62" t="n"/>
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="9" t="n"/>
-      <c r="R20" s="70" t="n"/>
+      <c r="R20" s="62" t="n"/>
       <c r="S20" s="8" t="n"/>
-      <c r="T20" s="26" t="n"/>
-      <c r="V20" s="27" t="n"/>
-      <c r="W20" s="28" t="n"/>
-      <c r="X20" s="28" t="n"/>
-      <c r="Y20" s="28" t="n"/>
-      <c r="Z20" s="28" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="28" t="n"/>
-      <c r="AD20" s="28" t="n"/>
-      <c r="AE20" s="28" t="n"/>
-      <c r="AF20" s="28" t="n"/>
-      <c r="AG20" s="28" t="n"/>
-      <c r="AH20" s="28" t="n"/>
-      <c r="AI20" s="28" t="n"/>
-      <c r="AJ20" s="28" t="n"/>
-      <c r="AK20" s="28" t="n"/>
-      <c r="AL20" s="28" t="n"/>
-      <c r="AM20" s="28" t="n"/>
-      <c r="AN20" s="28" t="n"/>
-      <c r="AO20" s="28" t="n"/>
-      <c r="AP20" s="29" t="n"/>
+      <c r="T20" s="20" t="n"/>
+      <c r="V20" s="21" t="n"/>
+      <c r="W20" s="22" t="n"/>
+      <c r="X20" s="22" t="n"/>
+      <c r="Y20" s="22" t="n"/>
+      <c r="Z20" s="22" t="n"/>
+      <c r="AA20" s="22" t="n"/>
+      <c r="AB20" s="22" t="n"/>
+      <c r="AC20" s="22" t="n"/>
+      <c r="AD20" s="22" t="n"/>
+      <c r="AE20" s="22" t="n"/>
+      <c r="AF20" s="22" t="n"/>
+      <c r="AG20" s="22" t="n"/>
+      <c r="AH20" s="22" t="n"/>
+      <c r="AI20" s="22" t="n"/>
+      <c r="AJ20" s="22" t="n"/>
+      <c r="AK20" s="22" t="n"/>
+      <c r="AL20" s="22" t="n"/>
+      <c r="AM20" s="22" t="n"/>
+      <c r="AN20" s="22" t="n"/>
+      <c r="AO20" s="22" t="n"/>
+      <c r="AP20" s="23" t="n"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="69" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr">
         <is>
           <t>④</t>
         </is>
@@ -2048,36 +1988,36 @@
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="9" t="n"/>
-      <c r="O21" s="70" t="n"/>
+      <c r="O21" s="62" t="n"/>
       <c r="P21" s="8" t="n"/>
       <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="70" t="n"/>
+      <c r="R21" s="62" t="n"/>
       <c r="S21" s="8" t="n"/>
-      <c r="T21" s="26" t="n"/>
-      <c r="V21" s="27" t="n"/>
-      <c r="W21" s="28" t="n"/>
-      <c r="X21" s="28" t="n"/>
-      <c r="Y21" s="28" t="n"/>
-      <c r="Z21" s="28" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="28" t="n"/>
-      <c r="AD21" s="28" t="n"/>
-      <c r="AE21" s="28" t="n"/>
-      <c r="AF21" s="28" t="n"/>
-      <c r="AG21" s="28" t="n"/>
-      <c r="AH21" s="28" t="n"/>
-      <c r="AI21" s="28" t="n"/>
-      <c r="AJ21" s="28" t="n"/>
-      <c r="AK21" s="28" t="n"/>
-      <c r="AL21" s="28" t="n"/>
-      <c r="AM21" s="28" t="n"/>
-      <c r="AN21" s="28" t="n"/>
-      <c r="AO21" s="28" t="n"/>
-      <c r="AP21" s="29" t="n"/>
+      <c r="T21" s="20" t="n"/>
+      <c r="V21" s="21" t="n"/>
+      <c r="W21" s="22" t="n"/>
+      <c r="X21" s="22" t="n"/>
+      <c r="Y21" s="22" t="n"/>
+      <c r="Z21" s="22" t="n"/>
+      <c r="AA21" s="22" t="n"/>
+      <c r="AB21" s="22" t="n"/>
+      <c r="AC21" s="22" t="n"/>
+      <c r="AD21" s="22" t="n"/>
+      <c r="AE21" s="22" t="n"/>
+      <c r="AF21" s="22" t="n"/>
+      <c r="AG21" s="22" t="n"/>
+      <c r="AH21" s="22" t="n"/>
+      <c r="AI21" s="22" t="n"/>
+      <c r="AJ21" s="22" t="n"/>
+      <c r="AK21" s="22" t="n"/>
+      <c r="AL21" s="22" t="n"/>
+      <c r="AM21" s="22" t="n"/>
+      <c r="AN21" s="22" t="n"/>
+      <c r="AO21" s="22" t="n"/>
+      <c r="AP21" s="23" t="n"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="69" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
@@ -2095,36 +2035,36 @@
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="9" t="n"/>
-      <c r="O22" s="70" t="n"/>
+      <c r="O22" s="62" t="n"/>
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="70" t="n"/>
+      <c r="R22" s="62" t="n"/>
       <c r="S22" s="8" t="n"/>
-      <c r="T22" s="26" t="n"/>
-      <c r="V22" s="27" t="n"/>
-      <c r="W22" s="28" t="n"/>
-      <c r="X22" s="28" t="n"/>
-      <c r="Y22" s="28" t="n"/>
-      <c r="Z22" s="28" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="28" t="n"/>
-      <c r="AD22" s="28" t="n"/>
-      <c r="AE22" s="28" t="n"/>
-      <c r="AF22" s="28" t="n"/>
-      <c r="AG22" s="28" t="n"/>
-      <c r="AH22" s="28" t="n"/>
-      <c r="AI22" s="28" t="n"/>
-      <c r="AJ22" s="28" t="n"/>
-      <c r="AK22" s="28" t="n"/>
-      <c r="AL22" s="28" t="n"/>
-      <c r="AM22" s="28" t="n"/>
-      <c r="AN22" s="28" t="n"/>
-      <c r="AO22" s="28" t="n"/>
-      <c r="AP22" s="29" t="n"/>
+      <c r="T22" s="20" t="n"/>
+      <c r="V22" s="21" t="n"/>
+      <c r="W22" s="22" t="n"/>
+      <c r="X22" s="22" t="n"/>
+      <c r="Y22" s="22" t="n"/>
+      <c r="Z22" s="22" t="n"/>
+      <c r="AA22" s="22" t="n"/>
+      <c r="AB22" s="22" t="n"/>
+      <c r="AC22" s="22" t="n"/>
+      <c r="AD22" s="22" t="n"/>
+      <c r="AE22" s="22" t="n"/>
+      <c r="AF22" s="22" t="n"/>
+      <c r="AG22" s="22" t="n"/>
+      <c r="AH22" s="22" t="n"/>
+      <c r="AI22" s="22" t="n"/>
+      <c r="AJ22" s="22" t="n"/>
+      <c r="AK22" s="22" t="n"/>
+      <c r="AL22" s="22" t="n"/>
+      <c r="AM22" s="22" t="n"/>
+      <c r="AN22" s="22" t="n"/>
+      <c r="AO22" s="22" t="n"/>
+      <c r="AP22" s="23" t="n"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="69" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
@@ -2142,36 +2082,36 @@
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="9" t="n"/>
-      <c r="O23" s="70" t="n"/>
+      <c r="O23" s="62" t="n"/>
       <c r="P23" s="8" t="n"/>
       <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="70" t="n"/>
+      <c r="R23" s="62" t="n"/>
       <c r="S23" s="8" t="n"/>
-      <c r="T23" s="26" t="n"/>
-      <c r="V23" s="27" t="n"/>
-      <c r="W23" s="28" t="n"/>
-      <c r="X23" s="28" t="n"/>
-      <c r="Y23" s="28" t="n"/>
-      <c r="Z23" s="28" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="28" t="n"/>
-      <c r="AD23" s="28" t="n"/>
-      <c r="AE23" s="28" t="n"/>
-      <c r="AF23" s="28" t="n"/>
-      <c r="AG23" s="28" t="n"/>
-      <c r="AH23" s="28" t="n"/>
-      <c r="AI23" s="28" t="n"/>
-      <c r="AJ23" s="28" t="n"/>
-      <c r="AK23" s="28" t="n"/>
-      <c r="AL23" s="28" t="n"/>
-      <c r="AM23" s="28" t="n"/>
-      <c r="AN23" s="28" t="n"/>
-      <c r="AO23" s="28" t="n"/>
-      <c r="AP23" s="29" t="n"/>
+      <c r="T23" s="20" t="n"/>
+      <c r="V23" s="21" t="n"/>
+      <c r="W23" s="22" t="n"/>
+      <c r="X23" s="22" t="n"/>
+      <c r="Y23" s="22" t="n"/>
+      <c r="Z23" s="22" t="n"/>
+      <c r="AA23" s="22" t="n"/>
+      <c r="AB23" s="22" t="n"/>
+      <c r="AC23" s="22" t="n"/>
+      <c r="AD23" s="22" t="n"/>
+      <c r="AE23" s="22" t="n"/>
+      <c r="AF23" s="22" t="n"/>
+      <c r="AG23" s="22" t="n"/>
+      <c r="AH23" s="22" t="n"/>
+      <c r="AI23" s="22" t="n"/>
+      <c r="AJ23" s="22" t="n"/>
+      <c r="AK23" s="22" t="n"/>
+      <c r="AL23" s="22" t="n"/>
+      <c r="AM23" s="22" t="n"/>
+      <c r="AN23" s="22" t="n"/>
+      <c r="AO23" s="22" t="n"/>
+      <c r="AP23" s="23" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="69" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
@@ -2189,36 +2129,36 @@
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="9" t="n"/>
-      <c r="O24" s="70" t="n"/>
+      <c r="O24" s="62" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="70" t="n"/>
+      <c r="R24" s="62" t="n"/>
       <c r="S24" s="8" t="n"/>
-      <c r="T24" s="26" t="n"/>
-      <c r="V24" s="27" t="n"/>
-      <c r="W24" s="28" t="n"/>
-      <c r="X24" s="28" t="n"/>
-      <c r="Y24" s="28" t="n"/>
-      <c r="Z24" s="28" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="28" t="n"/>
-      <c r="AD24" s="28" t="n"/>
-      <c r="AE24" s="28" t="n"/>
-      <c r="AF24" s="28" t="n"/>
-      <c r="AG24" s="28" t="n"/>
-      <c r="AH24" s="28" t="n"/>
-      <c r="AI24" s="28" t="n"/>
-      <c r="AJ24" s="28" t="n"/>
-      <c r="AK24" s="28" t="n"/>
-      <c r="AL24" s="28" t="n"/>
-      <c r="AM24" s="28" t="n"/>
-      <c r="AN24" s="28" t="n"/>
-      <c r="AO24" s="28" t="n"/>
-      <c r="AP24" s="29" t="n"/>
+      <c r="T24" s="20" t="n"/>
+      <c r="V24" s="21" t="n"/>
+      <c r="W24" s="22" t="n"/>
+      <c r="X24" s="22" t="n"/>
+      <c r="Y24" s="22" t="n"/>
+      <c r="Z24" s="22" t="n"/>
+      <c r="AA24" s="22" t="n"/>
+      <c r="AB24" s="22" t="n"/>
+      <c r="AC24" s="22" t="n"/>
+      <c r="AD24" s="22" t="n"/>
+      <c r="AE24" s="22" t="n"/>
+      <c r="AF24" s="22" t="n"/>
+      <c r="AG24" s="22" t="n"/>
+      <c r="AH24" s="22" t="n"/>
+      <c r="AI24" s="22" t="n"/>
+      <c r="AJ24" s="22" t="n"/>
+      <c r="AK24" s="22" t="n"/>
+      <c r="AL24" s="22" t="n"/>
+      <c r="AM24" s="22" t="n"/>
+      <c r="AN24" s="22" t="n"/>
+      <c r="AO24" s="22" t="n"/>
+      <c r="AP24" s="23" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="69" t="inlineStr">
+      <c r="A25" s="61" t="inlineStr">
         <is>
           <t>⑧</t>
         </is>
@@ -2236,36 +2176,36 @@
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="9" t="n"/>
-      <c r="O25" s="70" t="n"/>
+      <c r="O25" s="62" t="n"/>
       <c r="P25" s="8" t="n"/>
       <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="70" t="n"/>
+      <c r="R25" s="62" t="n"/>
       <c r="S25" s="8" t="n"/>
-      <c r="T25" s="26" t="n"/>
-      <c r="V25" s="27" t="n"/>
-      <c r="W25" s="28" t="n"/>
-      <c r="X25" s="28" t="n"/>
-      <c r="Y25" s="28" t="n"/>
-      <c r="Z25" s="28" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="28" t="n"/>
-      <c r="AD25" s="28" t="n"/>
-      <c r="AE25" s="28" t="n"/>
-      <c r="AF25" s="28" t="n"/>
-      <c r="AG25" s="28" t="n"/>
-      <c r="AH25" s="28" t="n"/>
-      <c r="AI25" s="28" t="n"/>
-      <c r="AJ25" s="28" t="n"/>
-      <c r="AK25" s="28" t="n"/>
-      <c r="AL25" s="28" t="n"/>
-      <c r="AM25" s="28" t="n"/>
-      <c r="AN25" s="28" t="n"/>
-      <c r="AO25" s="28" t="n"/>
-      <c r="AP25" s="29" t="n"/>
+      <c r="T25" s="20" t="n"/>
+      <c r="V25" s="21" t="n"/>
+      <c r="W25" s="22" t="n"/>
+      <c r="X25" s="22" t="n"/>
+      <c r="Y25" s="22" t="n"/>
+      <c r="Z25" s="22" t="n"/>
+      <c r="AA25" s="22" t="n"/>
+      <c r="AB25" s="22" t="n"/>
+      <c r="AC25" s="22" t="n"/>
+      <c r="AD25" s="22" t="n"/>
+      <c r="AE25" s="22" t="n"/>
+      <c r="AF25" s="22" t="n"/>
+      <c r="AG25" s="22" t="n"/>
+      <c r="AH25" s="22" t="n"/>
+      <c r="AI25" s="22" t="n"/>
+      <c r="AJ25" s="22" t="n"/>
+      <c r="AK25" s="22" t="n"/>
+      <c r="AL25" s="22" t="n"/>
+      <c r="AM25" s="22" t="n"/>
+      <c r="AN25" s="22" t="n"/>
+      <c r="AO25" s="22" t="n"/>
+      <c r="AP25" s="23" t="n"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="69" t="inlineStr">
+      <c r="A26" s="61" t="inlineStr">
         <is>
           <t>⑨</t>
         </is>
@@ -2283,36 +2223,36 @@
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="9" t="n"/>
-      <c r="O26" s="70" t="n"/>
+      <c r="O26" s="62" t="n"/>
       <c r="P26" s="8" t="n"/>
       <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="70" t="n"/>
+      <c r="R26" s="62" t="n"/>
       <c r="S26" s="8" t="n"/>
-      <c r="T26" s="26" t="n"/>
-      <c r="V26" s="27" t="n"/>
-      <c r="W26" s="28" t="n"/>
-      <c r="X26" s="28" t="n"/>
-      <c r="Y26" s="28" t="n"/>
-      <c r="Z26" s="28" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="28" t="n"/>
-      <c r="AD26" s="28" t="n"/>
-      <c r="AE26" s="28" t="n"/>
-      <c r="AF26" s="28" t="n"/>
-      <c r="AG26" s="28" t="n"/>
-      <c r="AH26" s="28" t="n"/>
-      <c r="AI26" s="28" t="n"/>
-      <c r="AJ26" s="28" t="n"/>
-      <c r="AK26" s="28" t="n"/>
-      <c r="AL26" s="28" t="n"/>
-      <c r="AM26" s="28" t="n"/>
-      <c r="AN26" s="28" t="n"/>
-      <c r="AO26" s="28" t="n"/>
-      <c r="AP26" s="29" t="n"/>
+      <c r="T26" s="20" t="n"/>
+      <c r="V26" s="21" t="n"/>
+      <c r="W26" s="22" t="n"/>
+      <c r="X26" s="22" t="n"/>
+      <c r="Y26" s="22" t="n"/>
+      <c r="Z26" s="22" t="n"/>
+      <c r="AA26" s="22" t="n"/>
+      <c r="AB26" s="22" t="n"/>
+      <c r="AC26" s="22" t="n"/>
+      <c r="AD26" s="22" t="n"/>
+      <c r="AE26" s="22" t="n"/>
+      <c r="AF26" s="22" t="n"/>
+      <c r="AG26" s="22" t="n"/>
+      <c r="AH26" s="22" t="n"/>
+      <c r="AI26" s="22" t="n"/>
+      <c r="AJ26" s="22" t="n"/>
+      <c r="AK26" s="22" t="n"/>
+      <c r="AL26" s="22" t="n"/>
+      <c r="AM26" s="22" t="n"/>
+      <c r="AN26" s="22" t="n"/>
+      <c r="AO26" s="22" t="n"/>
+      <c r="AP26" s="23" t="n"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="69" t="inlineStr">
+      <c r="A27" s="61" t="inlineStr">
         <is>
           <t>⑩</t>
         </is>
@@ -2330,36 +2270,36 @@
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="9" t="n"/>
-      <c r="O27" s="70" t="n"/>
+      <c r="O27" s="62" t="n"/>
       <c r="P27" s="8" t="n"/>
       <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="70" t="n"/>
+      <c r="R27" s="62" t="n"/>
       <c r="S27" s="8" t="n"/>
-      <c r="T27" s="26" t="n"/>
-      <c r="V27" s="27" t="n"/>
-      <c r="W27" s="28" t="n"/>
-      <c r="X27" s="28" t="n"/>
-      <c r="Y27" s="28" t="n"/>
-      <c r="Z27" s="28" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="28" t="n"/>
-      <c r="AD27" s="28" t="n"/>
-      <c r="AE27" s="28" t="n"/>
-      <c r="AF27" s="28" t="n"/>
-      <c r="AG27" s="28" t="n"/>
-      <c r="AH27" s="28" t="n"/>
-      <c r="AI27" s="28" t="n"/>
-      <c r="AJ27" s="28" t="n"/>
-      <c r="AK27" s="28" t="n"/>
-      <c r="AL27" s="28" t="n"/>
-      <c r="AM27" s="28" t="n"/>
-      <c r="AN27" s="28" t="n"/>
-      <c r="AO27" s="28" t="n"/>
-      <c r="AP27" s="29" t="n"/>
+      <c r="T27" s="20" t="n"/>
+      <c r="V27" s="21" t="n"/>
+      <c r="W27" s="22" t="n"/>
+      <c r="X27" s="22" t="n"/>
+      <c r="Y27" s="22" t="n"/>
+      <c r="Z27" s="22" t="n"/>
+      <c r="AA27" s="22" t="n"/>
+      <c r="AB27" s="22" t="n"/>
+      <c r="AC27" s="22" t="n"/>
+      <c r="AD27" s="22" t="n"/>
+      <c r="AE27" s="22" t="n"/>
+      <c r="AF27" s="22" t="n"/>
+      <c r="AG27" s="22" t="n"/>
+      <c r="AH27" s="22" t="n"/>
+      <c r="AI27" s="22" t="n"/>
+      <c r="AJ27" s="22" t="n"/>
+      <c r="AK27" s="22" t="n"/>
+      <c r="AL27" s="22" t="n"/>
+      <c r="AM27" s="22" t="n"/>
+      <c r="AN27" s="22" t="n"/>
+      <c r="AO27" s="22" t="n"/>
+      <c r="AP27" s="23" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="69" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr">
         <is>
           <t>⑪</t>
         </is>
@@ -2377,91 +2317,83 @@
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="9" t="n"/>
-      <c r="O28" s="70" t="n"/>
+      <c r="O28" s="62" t="n"/>
       <c r="P28" s="8" t="n"/>
       <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="70" t="n"/>
+      <c r="R28" s="62" t="n"/>
       <c r="S28" s="8" t="n"/>
-      <c r="T28" s="26" t="n"/>
-      <c r="V28" s="71" t="inlineStr">
-        <is>
-          <t>凡例　━ 手すり　▲ 段差（高さmm）　Ｎ↑ 方位</t>
-        </is>
-      </c>
-      <c r="W28" s="72" t="n"/>
-      <c r="X28" s="72" t="n"/>
-      <c r="Y28" s="72" t="n"/>
-      <c r="Z28" s="72" t="n"/>
-      <c r="AA28" s="72" t="n"/>
-      <c r="AB28" s="72" t="n"/>
-      <c r="AC28" s="72" t="n"/>
-      <c r="AD28" s="72" t="n"/>
-      <c r="AE28" s="72" t="n"/>
-      <c r="AF28" s="72" t="n"/>
-      <c r="AG28" s="72" t="n"/>
-      <c r="AH28" s="72" t="n"/>
-      <c r="AI28" s="72" t="n"/>
-      <c r="AJ28" s="72" t="n"/>
-      <c r="AK28" s="72" t="n"/>
-      <c r="AL28" s="72" t="n"/>
-      <c r="AM28" s="72" t="n"/>
-      <c r="AN28" s="72" t="n"/>
-      <c r="AO28" s="72" t="n"/>
-      <c r="AP28" s="73" t="n"/>
+      <c r="T28" s="20" t="n"/>
+      <c r="V28" s="21" t="n"/>
+      <c r="W28" s="22" t="n"/>
+      <c r="X28" s="22" t="n"/>
+      <c r="Y28" s="22" t="n"/>
+      <c r="Z28" s="22" t="n"/>
+      <c r="AA28" s="22" t="n"/>
+      <c r="AB28" s="22" t="n"/>
+      <c r="AC28" s="22" t="n"/>
+      <c r="AD28" s="22" t="n"/>
+      <c r="AE28" s="22" t="n"/>
+      <c r="AF28" s="22" t="n"/>
+      <c r="AG28" s="22" t="n"/>
+      <c r="AH28" s="22" t="n"/>
+      <c r="AI28" s="22" t="n"/>
+      <c r="AJ28" s="22" t="n"/>
+      <c r="AK28" s="22" t="n"/>
+      <c r="AL28" s="22" t="n"/>
+      <c r="AM28" s="22" t="n"/>
+      <c r="AN28" s="22" t="n"/>
+      <c r="AO28" s="22" t="n"/>
+      <c r="AP28" s="23" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="74" t="inlineStr">
+      <c r="A29" s="63" t="inlineStr">
         <is>
           <t>⑫</t>
         </is>
       </c>
-      <c r="B29" s="75" t="n"/>
-      <c r="C29" s="76" t="n"/>
-      <c r="D29" s="76" t="n"/>
-      <c r="E29" s="76" t="n"/>
-      <c r="F29" s="77" t="n"/>
-      <c r="G29" s="75" t="n"/>
-      <c r="H29" s="76" t="n"/>
-      <c r="I29" s="76" t="n"/>
-      <c r="J29" s="76" t="n"/>
-      <c r="K29" s="76" t="n"/>
-      <c r="L29" s="76" t="n"/>
-      <c r="M29" s="76" t="n"/>
-      <c r="N29" s="77" t="n"/>
-      <c r="O29" s="78" t="n"/>
-      <c r="P29" s="76" t="n"/>
-      <c r="Q29" s="77" t="n"/>
-      <c r="R29" s="78" t="n"/>
-      <c r="S29" s="76" t="n"/>
-      <c r="T29" s="79" t="n"/>
-      <c r="V29" s="80" t="inlineStr">
-        <is>
-          <t>※改修する場所に①～⑫の番号を書き、左の改修項目と対応させてください。</t>
-        </is>
-      </c>
-      <c r="W29" s="81" t="n"/>
-      <c r="X29" s="81" t="n"/>
-      <c r="Y29" s="81" t="n"/>
-      <c r="Z29" s="81" t="n"/>
-      <c r="AA29" s="81" t="n"/>
-      <c r="AB29" s="81" t="n"/>
-      <c r="AC29" s="81" t="n"/>
-      <c r="AD29" s="81" t="n"/>
-      <c r="AE29" s="81" t="n"/>
-      <c r="AF29" s="81" t="n"/>
-      <c r="AG29" s="81" t="n"/>
-      <c r="AH29" s="81" t="n"/>
-      <c r="AI29" s="81" t="n"/>
-      <c r="AJ29" s="81" t="n"/>
-      <c r="AK29" s="81" t="n"/>
-      <c r="AL29" s="81" t="n"/>
-      <c r="AM29" s="81" t="n"/>
-      <c r="AN29" s="81" t="n"/>
-      <c r="AO29" s="81" t="n"/>
-      <c r="AP29" s="82" t="n"/>
+      <c r="B29" s="64" t="n"/>
+      <c r="C29" s="65" t="n"/>
+      <c r="D29" s="65" t="n"/>
+      <c r="E29" s="65" t="n"/>
+      <c r="F29" s="66" t="n"/>
+      <c r="G29" s="64" t="n"/>
+      <c r="H29" s="65" t="n"/>
+      <c r="I29" s="65" t="n"/>
+      <c r="J29" s="65" t="n"/>
+      <c r="K29" s="65" t="n"/>
+      <c r="L29" s="65" t="n"/>
+      <c r="M29" s="65" t="n"/>
+      <c r="N29" s="66" t="n"/>
+      <c r="O29" s="67" t="n"/>
+      <c r="P29" s="65" t="n"/>
+      <c r="Q29" s="66" t="n"/>
+      <c r="R29" s="67" t="n"/>
+      <c r="S29" s="65" t="n"/>
+      <c r="T29" s="68" t="n"/>
+      <c r="V29" s="69" t="n"/>
+      <c r="W29" s="70" t="n"/>
+      <c r="X29" s="70" t="n"/>
+      <c r="Y29" s="70" t="n"/>
+      <c r="Z29" s="70" t="n"/>
+      <c r="AA29" s="70" t="n"/>
+      <c r="AB29" s="70" t="n"/>
+      <c r="AC29" s="70" t="n"/>
+      <c r="AD29" s="70" t="n"/>
+      <c r="AE29" s="70" t="n"/>
+      <c r="AF29" s="70" t="n"/>
+      <c r="AG29" s="70" t="n"/>
+      <c r="AH29" s="70" t="n"/>
+      <c r="AI29" s="70" t="n"/>
+      <c r="AJ29" s="70" t="n"/>
+      <c r="AK29" s="70" t="n"/>
+      <c r="AL29" s="70" t="n"/>
+      <c r="AM29" s="70" t="n"/>
+      <c r="AN29" s="70" t="n"/>
+      <c r="AO29" s="70" t="n"/>
+      <c r="AP29" s="71" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="98">
     <mergeCell ref="O29:Q29"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="O7:P7"/>
@@ -2495,7 +2427,6 @@
     <mergeCell ref="R26:T26"/>
     <mergeCell ref="G27:N27"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="AI4:AK4"/>
     <mergeCell ref="G17:N17"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="AD2:AF2"/>
@@ -2516,7 +2447,7 @@
     <mergeCell ref="G22:N22"/>
     <mergeCell ref="E4:S4"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="V29:AP29"/>
+    <mergeCell ref="V4:AP4"/>
     <mergeCell ref="G21:N21"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="R21:T21"/>
@@ -2532,7 +2463,6 @@
     <mergeCell ref="G18:N18"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="AO4:AP4"/>
     <mergeCell ref="A1:T2"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="E7:F7"/>
@@ -2543,20 +2473,17 @@
     <mergeCell ref="R25:T25"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="V28:AP28"/>
     <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A7:D8"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="H10:N10"/>
-    <mergeCell ref="AL4:AN4"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="H9:N9"/>
     <mergeCell ref="R18:T18"/>
     <mergeCell ref="G24:N24"/>
-    <mergeCell ref="V4:AH4"/>
     <mergeCell ref="N12:T12"/>
     <mergeCell ref="O28:Q28"/>
     <mergeCell ref="O10:T10"/>
@@ -2593,7 +2520,7 @@
     <dataValidation sqref="M14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□その他,■その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6 G8 O6 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 AL4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
+    <dataValidation sqref="G6 G8 O6 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>

--- a/住宅改修_現地調査アセスメントシート.xlsx
+++ b/住宅改修_現地調査アセスメントシート.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アセスメントシート" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'アセスメントシート'!$A$1:$AP$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'アセスメントシート'!$A$1:$AR$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,7 +68,7 @@
       <charset val="128"/>
       <family val="3"/>
       <color rgb="00262626"/>
-      <sz val="8.5"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="BIZ UDPゴシック"/>
@@ -76,6 +76,13 @@
       <family val="3"/>
       <color rgb="00262626"/>
       <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="BIZ UDPゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <color rgb="00262626"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="BIZ UDPゴシック"/>
@@ -90,7 +97,7 @@
       <charset val="128"/>
       <family val="3"/>
       <color rgb="00262626"/>
-      <sz val="8"/>
+      <sz val="7.5"/>
     </font>
   </fonts>
   <fills count="4">
@@ -470,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -499,18 +506,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -529,23 +536,24 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -572,13 +580,17 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -590,13 +602,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -976,54 +992,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AP29"/>
+  <dimension ref="A1:AR29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3.5703125" customWidth="1" min="1" max="1"/>
-    <col width="3.5703125" customWidth="1" min="2" max="2"/>
-    <col width="3.5703125" customWidth="1" min="3" max="3"/>
-    <col width="3.5703125" customWidth="1" min="4" max="4"/>
-    <col width="3.5703125" customWidth="1" min="5" max="5"/>
-    <col width="3.5703125" customWidth="1" min="6" max="6"/>
-    <col width="3.5703125" customWidth="1" min="7" max="7"/>
-    <col width="3.5703125" customWidth="1" min="8" max="8"/>
-    <col width="3.5703125" customWidth="1" min="9" max="9"/>
-    <col width="3.5703125" customWidth="1" min="10" max="10"/>
-    <col width="3.5703125" customWidth="1" min="11" max="11"/>
-    <col width="3.5703125" customWidth="1" min="12" max="12"/>
-    <col width="3.5703125" customWidth="1" min="13" max="13"/>
-    <col width="3.5703125" customWidth="1" min="14" max="14"/>
-    <col width="3.5703125" customWidth="1" min="15" max="15"/>
-    <col width="3.5703125" customWidth="1" min="16" max="16"/>
-    <col width="3.5703125" customWidth="1" min="17" max="17"/>
-    <col width="3.5703125" customWidth="1" min="18" max="18"/>
-    <col width="3.5703125" customWidth="1" min="19" max="19"/>
-    <col width="3.5703125" customWidth="1" min="20" max="20"/>
-    <col width="3.5703125" customWidth="1" min="21" max="21"/>
-    <col width="3.5703125" customWidth="1" min="22" max="22"/>
-    <col width="3.5703125" customWidth="1" min="23" max="23"/>
-    <col width="3.5703125" customWidth="1" min="24" max="24"/>
-    <col width="3.5703125" customWidth="1" min="25" max="25"/>
-    <col width="3.5703125" customWidth="1" min="26" max="26"/>
-    <col width="3.5703125" customWidth="1" min="27" max="27"/>
-    <col width="3.5703125" customWidth="1" min="28" max="28"/>
-    <col width="3.5703125" customWidth="1" min="29" max="29"/>
-    <col width="3.5703125" customWidth="1" min="30" max="30"/>
-    <col width="3.5703125" customWidth="1" min="31" max="31"/>
-    <col width="3.5703125" customWidth="1" min="32" max="32"/>
-    <col width="3.5703125" customWidth="1" min="33" max="33"/>
-    <col width="3.5703125" customWidth="1" min="34" max="34"/>
-    <col width="3.5703125" customWidth="1" min="35" max="35"/>
-    <col width="3.5703125" customWidth="1" min="36" max="36"/>
-    <col width="3.5703125" customWidth="1" min="37" max="37"/>
-    <col width="3.5703125" customWidth="1" min="38" max="38"/>
-    <col width="3.5703125" customWidth="1" min="39" max="39"/>
-    <col width="3.5703125" customWidth="1" min="40" max="40"/>
-    <col width="3.5703125" customWidth="1" min="41" max="41"/>
-    <col width="3.5703125" customWidth="1" min="42" max="42"/>
+    <col width="3.36328125" customWidth="1" min="1" max="1"/>
+    <col width="3.36328125" customWidth="1" min="2" max="2"/>
+    <col width="3.36328125" customWidth="1" min="3" max="3"/>
+    <col width="3.36328125" customWidth="1" min="4" max="4"/>
+    <col width="3.36328125" customWidth="1" min="5" max="5"/>
+    <col width="3.36328125" customWidth="1" min="6" max="6"/>
+    <col width="3.36328125" customWidth="1" min="7" max="7"/>
+    <col width="3.36328125" customWidth="1" min="8" max="8"/>
+    <col width="3.36328125" customWidth="1" min="9" max="9"/>
+    <col width="3.36328125" customWidth="1" min="10" max="10"/>
+    <col width="3.36328125" customWidth="1" min="11" max="11"/>
+    <col width="3.36328125" customWidth="1" min="12" max="12"/>
+    <col width="3.36328125" customWidth="1" min="13" max="13"/>
+    <col width="3.36328125" customWidth="1" min="14" max="14"/>
+    <col width="3.36328125" customWidth="1" min="15" max="15"/>
+    <col width="3.36328125" customWidth="1" min="16" max="16"/>
+    <col width="3.36328125" customWidth="1" min="17" max="17"/>
+    <col width="3.36328125" customWidth="1" min="18" max="18"/>
+    <col width="3.36328125" customWidth="1" min="19" max="19"/>
+    <col width="3.36328125" customWidth="1" min="20" max="20"/>
+    <col width="3.36328125" customWidth="1" min="21" max="21"/>
+    <col width="3.36328125" customWidth="1" min="22" max="22"/>
+    <col width="3.36328125" customWidth="1" min="23" max="23"/>
+    <col width="3.36328125" customWidth="1" min="24" max="24"/>
+    <col width="3.36328125" customWidth="1" min="25" max="25"/>
+    <col width="3.36328125" customWidth="1" min="26" max="26"/>
+    <col width="3.36328125" customWidth="1" min="27" max="27"/>
+    <col width="3.36328125" customWidth="1" min="28" max="28"/>
+    <col width="3.36328125" customWidth="1" min="29" max="29"/>
+    <col width="3.36328125" customWidth="1" min="30" max="30"/>
+    <col width="3.36328125" customWidth="1" min="31" max="31"/>
+    <col width="3.36328125" customWidth="1" min="32" max="32"/>
+    <col width="3.36328125" customWidth="1" min="33" max="33"/>
+    <col width="3.36328125" customWidth="1" min="34" max="34"/>
+    <col width="3.36328125" customWidth="1" min="35" max="35"/>
+    <col width="3.36328125" customWidth="1" min="36" max="36"/>
+    <col width="3.36328125" customWidth="1" min="37" max="37"/>
+    <col width="3.36328125" customWidth="1" min="38" max="38"/>
+    <col width="3.36328125" customWidth="1" min="39" max="39"/>
+    <col width="3.36328125" customWidth="1" min="40" max="40"/>
+    <col width="3.36328125" customWidth="1" min="41" max="41"/>
+    <col width="3.36328125" customWidth="1" min="42" max="42"/>
+    <col width="3.36328125" customWidth="1" min="43" max="43"/>
+    <col width="3.36328125" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>住宅改修 現地調査アセスメントシート</t>
@@ -1048,8 +1066,11 @@
       <c r="R1" s="2" t="n"/>
       <c r="S1" s="2" t="n"/>
       <c r="T1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="18.75" customHeight="1">
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="n"/>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
@@ -1070,30 +1091,33 @@
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="U2" s="3" t="n"/>
+      <c r="V2" s="3" t="n"/>
+      <c r="W2" s="3" t="n"/>
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>調査日</t>
         </is>
       </c>
-      <c r="AE2" s="5" t="n"/>
-      <c r="AF2" s="6" t="n"/>
-      <c r="AG2" s="7" t="inlineStr">
+      <c r="AG2" s="5" t="n"/>
+      <c r="AH2" s="6" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
         <is>
           <t>令和　　年　　月　　日</t>
         </is>
       </c>
-      <c r="AH2" s="8" t="n"/>
-      <c r="AI2" s="8" t="n"/>
       <c r="AJ2" s="8" t="n"/>
       <c r="AK2" s="8" t="n"/>
       <c r="AL2" s="8" t="n"/>
       <c r="AM2" s="8" t="n"/>
       <c r="AN2" s="8" t="n"/>
       <c r="AO2" s="8" t="n"/>
-      <c r="AP2" s="9" t="n"/>
+      <c r="AP2" s="8" t="n"/>
+      <c r="AQ2" s="8" t="n"/>
+      <c r="AR2" s="9" t="n"/>
     </row>
     <row r="3" ht="4.5" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>利用者氏名</t>
@@ -1117,19 +1141,19 @@
       <c r="Q4" s="14" t="n"/>
       <c r="R4" s="14" t="n"/>
       <c r="S4" s="14" t="n"/>
-      <c r="T4" s="15" t="inlineStr">
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="15" t="inlineStr">
         <is>
           <t>様</t>
         </is>
       </c>
-      <c r="V4" s="16" t="inlineStr">
+      <c r="Y4" s="16" t="inlineStr">
         <is>
           <t>平面図</t>
         </is>
       </c>
-      <c r="W4" s="17" t="n"/>
-      <c r="X4" s="17" t="n"/>
-      <c r="Y4" s="17" t="n"/>
       <c r="Z4" s="17" t="n"/>
       <c r="AA4" s="17" t="n"/>
       <c r="AB4" s="17" t="n"/>
@@ -1146,9 +1170,11 @@
       <c r="AM4" s="17" t="n"/>
       <c r="AN4" s="17" t="n"/>
       <c r="AO4" s="17" t="n"/>
-      <c r="AP4" s="18" t="n"/>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
+      <c r="AP4" s="17" t="n"/>
+      <c r="AQ4" s="17" t="n"/>
+      <c r="AR4" s="18" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>住所</t>
@@ -1172,11 +1198,11 @@
       <c r="Q5" s="8" t="n"/>
       <c r="R5" s="8" t="n"/>
       <c r="S5" s="8" t="n"/>
-      <c r="T5" s="20" t="n"/>
-      <c r="V5" s="21" t="n"/>
-      <c r="W5" s="22" t="n"/>
-      <c r="X5" s="22" t="n"/>
-      <c r="Y5" s="22" t="n"/>
+      <c r="T5" s="8" t="n"/>
+      <c r="U5" s="8" t="n"/>
+      <c r="V5" s="8" t="n"/>
+      <c r="W5" s="20" t="n"/>
+      <c r="Y5" s="21" t="n"/>
       <c r="Z5" s="22" t="n"/>
       <c r="AA5" s="22" t="n"/>
       <c r="AB5" s="22" t="n"/>
@@ -1193,9 +1219,11 @@
       <c r="AM5" s="22" t="n"/>
       <c r="AN5" s="22" t="n"/>
       <c r="AO5" s="22" t="n"/>
-      <c r="AP5" s="23" t="n"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
+      <c r="AP5" s="22" t="n"/>
+      <c r="AQ5" s="22" t="n"/>
+      <c r="AR5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
           <t>電話番号</t>
@@ -1215,23 +1243,23 @@
       <c r="I6" s="8" t="n"/>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t>携帯</t>
         </is>
       </c>
-      <c r="N6" s="25" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="8" t="n"/>
+      <c r="O6" s="25" t="n"/>
+      <c r="P6" s="7" t="n"/>
       <c r="Q6" s="8" t="n"/>
       <c r="R6" s="8" t="n"/>
       <c r="S6" s="8" t="n"/>
-      <c r="T6" s="20" t="n"/>
-      <c r="V6" s="21" t="n"/>
-      <c r="W6" s="22" t="n"/>
-      <c r="X6" s="22" t="n"/>
-      <c r="Y6" s="22" t="n"/>
+      <c r="T6" s="8" t="n"/>
+      <c r="U6" s="8" t="n"/>
+      <c r="V6" s="8" t="n"/>
+      <c r="W6" s="20" t="n"/>
+      <c r="Y6" s="21" t="n"/>
       <c r="Z6" s="22" t="n"/>
       <c r="AA6" s="22" t="n"/>
       <c r="AB6" s="22" t="n"/>
@@ -1248,9 +1276,11 @@
       <c r="AM6" s="22" t="n"/>
       <c r="AN6" s="22" t="n"/>
       <c r="AO6" s="22" t="n"/>
-      <c r="AP6" s="23" t="n"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
+      <c r="AP6" s="22" t="n"/>
+      <c r="AQ6" s="22" t="n"/>
+      <c r="AR6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
           <t>キーパーソン</t>
@@ -1272,21 +1302,21 @@
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="24" t="inlineStr">
         <is>
           <t>続柄</t>
         </is>
       </c>
-      <c r="P7" s="25" t="n"/>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="8" t="n"/>
-      <c r="S7" s="8" t="n"/>
-      <c r="T7" s="20" t="n"/>
-      <c r="V7" s="21" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
+      <c r="R7" s="25" t="n"/>
+      <c r="S7" s="7" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="20" t="n"/>
+      <c r="Y7" s="21" t="n"/>
       <c r="Z7" s="22" t="n"/>
       <c r="AA7" s="22" t="n"/>
       <c r="AB7" s="22" t="n"/>
@@ -1303,9 +1333,11 @@
       <c r="AM7" s="22" t="n"/>
       <c r="AN7" s="22" t="n"/>
       <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="23" t="n"/>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
+      <c r="AP7" s="22" t="n"/>
+      <c r="AQ7" s="22" t="n"/>
+      <c r="AR7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="29" t="n"/>
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="30" t="n"/>
@@ -1329,11 +1361,11 @@
       <c r="Q8" s="8" t="n"/>
       <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="n"/>
-      <c r="T8" s="20" t="n"/>
-      <c r="V8" s="21" t="n"/>
-      <c r="W8" s="22" t="n"/>
-      <c r="X8" s="22" t="n"/>
-      <c r="Y8" s="22" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="20" t="n"/>
+      <c r="Y8" s="21" t="n"/>
       <c r="Z8" s="22" t="n"/>
       <c r="AA8" s="22" t="n"/>
       <c r="AB8" s="22" t="n"/>
@@ -1350,9 +1382,11 @@
       <c r="AM8" s="22" t="n"/>
       <c r="AN8" s="22" t="n"/>
       <c r="AO8" s="22" t="n"/>
-      <c r="AP8" s="23" t="n"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
+      <c r="AP8" s="22" t="n"/>
+      <c r="AQ8" s="22" t="n"/>
+      <c r="AR8" s="23" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>連絡がつきやすい
@@ -1379,21 +1413,21 @@
       <c r="K9" s="37" t="n"/>
       <c r="L9" s="37" t="n"/>
       <c r="M9" s="37" t="n"/>
-      <c r="N9" s="38" t="n"/>
-      <c r="O9" s="39" t="inlineStr">
+      <c r="N9" s="37" t="n"/>
+      <c r="O9" s="38" t="n"/>
+      <c r="P9" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">　　時 ～ 　　時</t>
         </is>
       </c>
-      <c r="P9" s="37" t="n"/>
-      <c r="Q9" s="37" t="n"/>
-      <c r="R9" s="37" t="n"/>
-      <c r="S9" s="37" t="n"/>
+      <c r="Q9" s="40" t="n"/>
+      <c r="R9" s="40" t="n"/>
+      <c r="S9" s="40" t="n"/>
       <c r="T9" s="40" t="n"/>
-      <c r="V9" s="21" t="n"/>
-      <c r="W9" s="22" t="n"/>
-      <c r="X9" s="22" t="n"/>
-      <c r="Y9" s="22" t="n"/>
+      <c r="U9" s="40" t="n"/>
+      <c r="V9" s="40" t="n"/>
+      <c r="W9" s="41" t="n"/>
+      <c r="Y9" s="21" t="n"/>
       <c r="Z9" s="22" t="n"/>
       <c r="AA9" s="22" t="n"/>
       <c r="AB9" s="22" t="n"/>
@@ -1410,20 +1444,22 @@
       <c r="AM9" s="22" t="n"/>
       <c r="AN9" s="22" t="n"/>
       <c r="AO9" s="22" t="n"/>
-      <c r="AP9" s="23" t="n"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="42" t="n"/>
-      <c r="C10" s="42" t="n"/>
-      <c r="D10" s="43" t="n"/>
-      <c r="E10" s="44" t="inlineStr">
+      <c r="AP9" s="22" t="n"/>
+      <c r="AQ9" s="22" t="n"/>
+      <c r="AR9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="42" t="n"/>
+      <c r="B10" s="43" t="n"/>
+      <c r="C10" s="43" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>キーパーソン</t>
         </is>
       </c>
-      <c r="F10" s="45" t="n"/>
-      <c r="G10" s="46" t="n"/>
+      <c r="F10" s="46" t="n"/>
+      <c r="G10" s="47" t="n"/>
       <c r="H10" s="36" t="inlineStr">
         <is>
           <t>月　火　水　木　金　土　日</t>
@@ -1434,21 +1470,21 @@
       <c r="K10" s="37" t="n"/>
       <c r="L10" s="37" t="n"/>
       <c r="M10" s="37" t="n"/>
-      <c r="N10" s="38" t="n"/>
-      <c r="O10" s="39" t="inlineStr">
+      <c r="N10" s="37" t="n"/>
+      <c r="O10" s="38" t="n"/>
+      <c r="P10" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">　　時 ～ 　　時</t>
         </is>
       </c>
-      <c r="P10" s="37" t="n"/>
-      <c r="Q10" s="37" t="n"/>
-      <c r="R10" s="37" t="n"/>
-      <c r="S10" s="37" t="n"/>
+      <c r="Q10" s="40" t="n"/>
+      <c r="R10" s="40" t="n"/>
+      <c r="S10" s="40" t="n"/>
       <c r="T10" s="40" t="n"/>
-      <c r="V10" s="21" t="n"/>
-      <c r="W10" s="22" t="n"/>
-      <c r="X10" s="22" t="n"/>
-      <c r="Y10" s="22" t="n"/>
+      <c r="U10" s="40" t="n"/>
+      <c r="V10" s="40" t="n"/>
+      <c r="W10" s="41" t="n"/>
+      <c r="Y10" s="21" t="n"/>
       <c r="Z10" s="22" t="n"/>
       <c r="AA10" s="22" t="n"/>
       <c r="AB10" s="22" t="n"/>
@@ -1465,9 +1501,11 @@
       <c r="AM10" s="22" t="n"/>
       <c r="AN10" s="22" t="n"/>
       <c r="AO10" s="22" t="n"/>
-      <c r="AP10" s="23" t="n"/>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
+      <c r="AP10" s="22" t="n"/>
+      <c r="AQ10" s="22" t="n"/>
+      <c r="AR10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
           <t>担当ケアマネ</t>
@@ -1489,21 +1527,21 @@
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
-      <c r="N11" s="9" t="n"/>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="P11" s="25" t="n"/>
-      <c r="Q11" s="7" t="n"/>
-      <c r="R11" s="8" t="n"/>
-      <c r="S11" s="8" t="n"/>
-      <c r="T11" s="20" t="n"/>
-      <c r="V11" s="21" t="n"/>
-      <c r="W11" s="22" t="n"/>
-      <c r="X11" s="22" t="n"/>
-      <c r="Y11" s="22" t="n"/>
+      <c r="R11" s="25" t="n"/>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="20" t="n"/>
+      <c r="Y11" s="21" t="n"/>
       <c r="Z11" s="22" t="n"/>
       <c r="AA11" s="22" t="n"/>
       <c r="AB11" s="22" t="n"/>
@@ -1520,9 +1558,11 @@
       <c r="AM11" s="22" t="n"/>
       <c r="AN11" s="22" t="n"/>
       <c r="AO11" s="22" t="n"/>
-      <c r="AP11" s="23" t="n"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
+      <c r="AP11" s="22" t="n"/>
+      <c r="AQ11" s="22" t="n"/>
+      <c r="AR11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
           <t>負担割合</t>
@@ -1531,38 +1571,38 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="47" t="inlineStr">
+      <c r="E12" s="48" t="inlineStr">
         <is>
           <t>□1割</t>
         </is>
       </c>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
-      <c r="H12" s="48" t="inlineStr">
+      <c r="H12" s="49" t="inlineStr">
         <is>
           <t>□2割</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
-      <c r="K12" s="48" t="inlineStr">
+      <c r="K12" s="49" t="inlineStr">
         <is>
           <t>□3割</t>
         </is>
       </c>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
-      <c r="N12" s="49" t="n"/>
+      <c r="N12" s="50" t="n"/>
       <c r="O12" s="8" t="n"/>
       <c r="P12" s="8" t="n"/>
       <c r="Q12" s="8" t="n"/>
       <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="n"/>
-      <c r="T12" s="20" t="n"/>
-      <c r="V12" s="21" t="n"/>
-      <c r="W12" s="22" t="n"/>
-      <c r="X12" s="22" t="n"/>
-      <c r="Y12" s="22" t="n"/>
+      <c r="T12" s="8" t="n"/>
+      <c r="U12" s="8" t="n"/>
+      <c r="V12" s="8" t="n"/>
+      <c r="W12" s="20" t="n"/>
+      <c r="Y12" s="21" t="n"/>
       <c r="Z12" s="22" t="n"/>
       <c r="AA12" s="22" t="n"/>
       <c r="AB12" s="22" t="n"/>
@@ -1579,9 +1619,11 @@
       <c r="AM12" s="22" t="n"/>
       <c r="AN12" s="22" t="n"/>
       <c r="AO12" s="22" t="n"/>
-      <c r="AP12" s="23" t="n"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
+      <c r="AP12" s="22" t="n"/>
+      <c r="AQ12" s="22" t="n"/>
+      <c r="AR12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>疾患名</t>
@@ -1605,11 +1647,11 @@
       <c r="Q13" s="8" t="n"/>
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="n"/>
-      <c r="T13" s="20" t="n"/>
-      <c r="V13" s="21" t="n"/>
-      <c r="W13" s="22" t="n"/>
-      <c r="X13" s="22" t="n"/>
-      <c r="Y13" s="22" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="20" t="n"/>
+      <c r="Y13" s="21" t="n"/>
       <c r="Z13" s="22" t="n"/>
       <c r="AA13" s="22" t="n"/>
       <c r="AB13" s="22" t="n"/>
@@ -1626,57 +1668,59 @@
       <c r="AM13" s="22" t="n"/>
       <c r="AN13" s="22" t="n"/>
       <c r="AO13" s="22" t="n"/>
-      <c r="AP13" s="23" t="n"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="AP13" s="22" t="n"/>
+      <c r="AQ13" s="22" t="n"/>
+      <c r="AR13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>麻痺</t>
         </is>
       </c>
-      <c r="B14" s="51" t="n"/>
-      <c r="C14" s="51" t="n"/>
-      <c r="D14" s="52" t="n"/>
-      <c r="E14" s="53" t="inlineStr">
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>□なし</t>
         </is>
       </c>
-      <c r="F14" s="54" t="n"/>
-      <c r="G14" s="55" t="inlineStr">
+      <c r="F14" s="55" t="n"/>
+      <c r="G14" s="56" t="inlineStr">
         <is>
           <t>□右片麻痺</t>
         </is>
       </c>
-      <c r="H14" s="54" t="n"/>
-      <c r="I14" s="54" t="n"/>
-      <c r="J14" s="55" t="inlineStr">
+      <c r="H14" s="55" t="n"/>
+      <c r="I14" s="55" t="n"/>
+      <c r="J14" s="56" t="inlineStr">
         <is>
           <t>□左片麻痺</t>
         </is>
       </c>
-      <c r="K14" s="54" t="n"/>
-      <c r="L14" s="54" t="n"/>
-      <c r="M14" s="55" t="inlineStr">
+      <c r="K14" s="55" t="n"/>
+      <c r="L14" s="55" t="n"/>
+      <c r="M14" s="56" t="inlineStr">
         <is>
           <t>□その他</t>
         </is>
       </c>
-      <c r="N14" s="54" t="n"/>
-      <c r="O14" s="54" t="n"/>
-      <c r="P14" s="56" t="inlineStr">
-        <is>
-          <t>（　　　　）</t>
-        </is>
-      </c>
-      <c r="Q14" s="57" t="n"/>
-      <c r="R14" s="57" t="n"/>
-      <c r="S14" s="57" t="n"/>
+      <c r="N14" s="55" t="n"/>
+      <c r="O14" s="55" t="n"/>
+      <c r="P14" s="57" t="inlineStr">
+        <is>
+          <t>（　　　　　　）</t>
+        </is>
+      </c>
+      <c r="Q14" s="58" t="n"/>
+      <c r="R14" s="58" t="n"/>
+      <c r="S14" s="58" t="n"/>
       <c r="T14" s="58" t="n"/>
-      <c r="V14" s="21" t="n"/>
-      <c r="W14" s="22" t="n"/>
-      <c r="X14" s="22" t="n"/>
-      <c r="Y14" s="22" t="n"/>
+      <c r="U14" s="58" t="n"/>
+      <c r="V14" s="58" t="n"/>
+      <c r="W14" s="59" t="n"/>
+      <c r="Y14" s="21" t="n"/>
       <c r="Z14" s="22" t="n"/>
       <c r="AA14" s="22" t="n"/>
       <c r="AB14" s="22" t="n"/>
@@ -1693,13 +1737,12 @@
       <c r="AM14" s="22" t="n"/>
       <c r="AN14" s="22" t="n"/>
       <c r="AO14" s="22" t="n"/>
-      <c r="AP14" s="23" t="n"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="V15" s="21" t="n"/>
-      <c r="W15" s="22" t="n"/>
-      <c r="X15" s="22" t="n"/>
-      <c r="Y15" s="22" t="n"/>
+      <c r="AP14" s="22" t="n"/>
+      <c r="AQ14" s="22" t="n"/>
+      <c r="AR14" s="23" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="Y15" s="21" t="n"/>
       <c r="Z15" s="22" t="n"/>
       <c r="AA15" s="22" t="n"/>
       <c r="AB15" s="22" t="n"/>
@@ -1716,9 +1759,11 @@
       <c r="AM15" s="22" t="n"/>
       <c r="AN15" s="22" t="n"/>
       <c r="AO15" s="22" t="n"/>
-      <c r="AP15" s="23" t="n"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
+      <c r="AP15" s="22" t="n"/>
+      <c r="AQ15" s="22" t="n"/>
+      <c r="AR15" s="23" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>改修項目</t>
@@ -1742,11 +1787,11 @@
       <c r="Q16" s="17" t="n"/>
       <c r="R16" s="17" t="n"/>
       <c r="S16" s="17" t="n"/>
-      <c r="T16" s="18" t="n"/>
-      <c r="V16" s="21" t="n"/>
-      <c r="W16" s="22" t="n"/>
-      <c r="X16" s="22" t="n"/>
-      <c r="Y16" s="22" t="n"/>
+      <c r="T16" s="17" t="n"/>
+      <c r="U16" s="17" t="n"/>
+      <c r="V16" s="17" t="n"/>
+      <c r="W16" s="18" t="n"/>
+      <c r="Y16" s="21" t="n"/>
       <c r="Z16" s="22" t="n"/>
       <c r="AA16" s="22" t="n"/>
       <c r="AB16" s="22" t="n"/>
@@ -1763,10 +1808,12 @@
       <c r="AM16" s="22" t="n"/>
       <c r="AN16" s="22" t="n"/>
       <c r="AO16" s="22" t="n"/>
-      <c r="AP16" s="23" t="n"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="AP16" s="22" t="n"/>
+      <c r="AQ16" s="22" t="n"/>
+      <c r="AR16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
@@ -1777,39 +1824,39 @@
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>改修内容</t>
         </is>
       </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
-      <c r="N17" s="6" t="n"/>
-      <c r="O17" s="24" t="inlineStr">
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="24" t="inlineStr">
         <is>
           <t>手すり長さ</t>
         </is>
       </c>
-      <c r="P17" s="35" t="n"/>
-      <c r="Q17" s="25" t="n"/>
-      <c r="R17" s="24" t="inlineStr">
+      <c r="Q17" s="35" t="n"/>
+      <c r="R17" s="35" t="n"/>
+      <c r="S17" s="35" t="n"/>
+      <c r="T17" s="25" t="n"/>
+      <c r="U17" s="24" t="inlineStr">
         <is>
           <t>手すり高さ</t>
         </is>
       </c>
-      <c r="S17" s="35" t="n"/>
-      <c r="T17" s="60" t="n"/>
-      <c r="V17" s="21" t="n"/>
-      <c r="W17" s="22" t="n"/>
-      <c r="X17" s="22" t="n"/>
-      <c r="Y17" s="22" t="n"/>
+      <c r="V17" s="35" t="n"/>
+      <c r="W17" s="61" t="n"/>
+      <c r="Y17" s="21" t="n"/>
       <c r="Z17" s="22" t="n"/>
       <c r="AA17" s="22" t="n"/>
       <c r="AB17" s="22" t="n"/>
@@ -1826,37 +1873,43 @@
       <c r="AM17" s="22" t="n"/>
       <c r="AN17" s="22" t="n"/>
       <c r="AO17" s="22" t="n"/>
-      <c r="AP17" s="23" t="n"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="61" t="inlineStr">
+      <c r="AP17" s="22" t="n"/>
+      <c r="AQ17" s="22" t="n"/>
+      <c r="AR17" s="23" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="62" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="9" t="n"/>
-      <c r="O18" s="62" t="n"/>
-      <c r="P18" s="8" t="n"/>
-      <c r="Q18" s="9" t="n"/>
-      <c r="R18" s="62" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="40" t="n"/>
+      <c r="I18" s="40" t="n"/>
+      <c r="J18" s="40" t="n"/>
+      <c r="K18" s="40" t="n"/>
+      <c r="L18" s="40" t="n"/>
+      <c r="M18" s="40" t="n"/>
+      <c r="N18" s="40" t="n"/>
+      <c r="O18" s="64" t="n"/>
+      <c r="P18" s="65" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="n"/>
-      <c r="T18" s="20" t="n"/>
-      <c r="V18" s="21" t="n"/>
-      <c r="W18" s="22" t="n"/>
-      <c r="X18" s="22" t="n"/>
-      <c r="Y18" s="22" t="n"/>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="65" t="n"/>
+      <c r="V18" s="8" t="n"/>
+      <c r="W18" s="20" t="n"/>
+      <c r="Y18" s="21" t="n"/>
       <c r="Z18" s="22" t="n"/>
       <c r="AA18" s="22" t="n"/>
       <c r="AB18" s="22" t="n"/>
@@ -1873,37 +1926,43 @@
       <c r="AM18" s="22" t="n"/>
       <c r="AN18" s="22" t="n"/>
       <c r="AO18" s="22" t="n"/>
-      <c r="AP18" s="23" t="n"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="AP18" s="22" t="n"/>
+      <c r="AQ18" s="22" t="n"/>
+      <c r="AR18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="9" t="n"/>
-      <c r="O19" s="62" t="n"/>
-      <c r="P19" s="8" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="62" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="40" t="n"/>
+      <c r="I19" s="40" t="n"/>
+      <c r="J19" s="40" t="n"/>
+      <c r="K19" s="40" t="n"/>
+      <c r="L19" s="40" t="n"/>
+      <c r="M19" s="40" t="n"/>
+      <c r="N19" s="40" t="n"/>
+      <c r="O19" s="64" t="n"/>
+      <c r="P19" s="65" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
       <c r="S19" s="8" t="n"/>
-      <c r="T19" s="20" t="n"/>
-      <c r="V19" s="21" t="n"/>
-      <c r="W19" s="22" t="n"/>
-      <c r="X19" s="22" t="n"/>
-      <c r="Y19" s="22" t="n"/>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="65" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="20" t="n"/>
+      <c r="Y19" s="21" t="n"/>
       <c r="Z19" s="22" t="n"/>
       <c r="AA19" s="22" t="n"/>
       <c r="AB19" s="22" t="n"/>
@@ -1920,37 +1979,43 @@
       <c r="AM19" s="22" t="n"/>
       <c r="AN19" s="22" t="n"/>
       <c r="AO19" s="22" t="n"/>
-      <c r="AP19" s="23" t="n"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="AP19" s="22" t="n"/>
+      <c r="AQ19" s="22" t="n"/>
+      <c r="AR19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="9" t="n"/>
-      <c r="O20" s="62" t="n"/>
-      <c r="P20" s="8" t="n"/>
-      <c r="Q20" s="9" t="n"/>
-      <c r="R20" s="62" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="40" t="n"/>
+      <c r="J20" s="40" t="n"/>
+      <c r="K20" s="40" t="n"/>
+      <c r="L20" s="40" t="n"/>
+      <c r="M20" s="40" t="n"/>
+      <c r="N20" s="40" t="n"/>
+      <c r="O20" s="64" t="n"/>
+      <c r="P20" s="65" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="n"/>
-      <c r="T20" s="20" t="n"/>
-      <c r="V20" s="21" t="n"/>
-      <c r="W20" s="22" t="n"/>
-      <c r="X20" s="22" t="n"/>
-      <c r="Y20" s="22" t="n"/>
+      <c r="T20" s="9" t="n"/>
+      <c r="U20" s="65" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="20" t="n"/>
+      <c r="Y20" s="21" t="n"/>
       <c r="Z20" s="22" t="n"/>
       <c r="AA20" s="22" t="n"/>
       <c r="AB20" s="22" t="n"/>
@@ -1967,37 +2032,43 @@
       <c r="AM20" s="22" t="n"/>
       <c r="AN20" s="22" t="n"/>
       <c r="AO20" s="22" t="n"/>
-      <c r="AP20" s="23" t="n"/>
-    </row>
-    <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="AP20" s="22" t="n"/>
+      <c r="AQ20" s="22" t="n"/>
+      <c r="AR20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="62" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="62" t="n"/>
-      <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="62" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="40" t="n"/>
+      <c r="I21" s="40" t="n"/>
+      <c r="J21" s="40" t="n"/>
+      <c r="K21" s="40" t="n"/>
+      <c r="L21" s="40" t="n"/>
+      <c r="M21" s="40" t="n"/>
+      <c r="N21" s="40" t="n"/>
+      <c r="O21" s="64" t="n"/>
+      <c r="P21" s="65" t="n"/>
+      <c r="Q21" s="8" t="n"/>
+      <c r="R21" s="8" t="n"/>
       <c r="S21" s="8" t="n"/>
-      <c r="T21" s="20" t="n"/>
-      <c r="V21" s="21" t="n"/>
-      <c r="W21" s="22" t="n"/>
-      <c r="X21" s="22" t="n"/>
-      <c r="Y21" s="22" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="65" t="n"/>
+      <c r="V21" s="8" t="n"/>
+      <c r="W21" s="20" t="n"/>
+      <c r="Y21" s="21" t="n"/>
       <c r="Z21" s="22" t="n"/>
       <c r="AA21" s="22" t="n"/>
       <c r="AB21" s="22" t="n"/>
@@ -2014,37 +2085,43 @@
       <c r="AM21" s="22" t="n"/>
       <c r="AN21" s="22" t="n"/>
       <c r="AO21" s="22" t="n"/>
-      <c r="AP21" s="23" t="n"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="AP21" s="22" t="n"/>
+      <c r="AQ21" s="22" t="n"/>
+      <c r="AR21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="62" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="62" t="n"/>
-      <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="62" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="40" t="n"/>
+      <c r="I22" s="40" t="n"/>
+      <c r="J22" s="40" t="n"/>
+      <c r="K22" s="40" t="n"/>
+      <c r="L22" s="40" t="n"/>
+      <c r="M22" s="40" t="n"/>
+      <c r="N22" s="40" t="n"/>
+      <c r="O22" s="64" t="n"/>
+      <c r="P22" s="65" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
-      <c r="T22" s="20" t="n"/>
-      <c r="V22" s="21" t="n"/>
-      <c r="W22" s="22" t="n"/>
-      <c r="X22" s="22" t="n"/>
-      <c r="Y22" s="22" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="65" t="n"/>
+      <c r="V22" s="8" t="n"/>
+      <c r="W22" s="20" t="n"/>
+      <c r="Y22" s="21" t="n"/>
       <c r="Z22" s="22" t="n"/>
       <c r="AA22" s="22" t="n"/>
       <c r="AB22" s="22" t="n"/>
@@ -2061,37 +2138,43 @@
       <c r="AM22" s="22" t="n"/>
       <c r="AN22" s="22" t="n"/>
       <c r="AO22" s="22" t="n"/>
-      <c r="AP22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="AP22" s="22" t="n"/>
+      <c r="AQ22" s="22" t="n"/>
+      <c r="AR22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
-      <c r="M23" s="8" t="n"/>
-      <c r="N23" s="9" t="n"/>
-      <c r="O23" s="62" t="n"/>
-      <c r="P23" s="8" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="62" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="40" t="n"/>
+      <c r="I23" s="40" t="n"/>
+      <c r="J23" s="40" t="n"/>
+      <c r="K23" s="40" t="n"/>
+      <c r="L23" s="40" t="n"/>
+      <c r="M23" s="40" t="n"/>
+      <c r="N23" s="40" t="n"/>
+      <c r="O23" s="64" t="n"/>
+      <c r="P23" s="65" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="8" t="n"/>
       <c r="S23" s="8" t="n"/>
-      <c r="T23" s="20" t="n"/>
-      <c r="V23" s="21" t="n"/>
-      <c r="W23" s="22" t="n"/>
-      <c r="X23" s="22" t="n"/>
-      <c r="Y23" s="22" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="65" t="n"/>
+      <c r="V23" s="8" t="n"/>
+      <c r="W23" s="20" t="n"/>
+      <c r="Y23" s="21" t="n"/>
       <c r="Z23" s="22" t="n"/>
       <c r="AA23" s="22" t="n"/>
       <c r="AB23" s="22" t="n"/>
@@ -2108,37 +2191,43 @@
       <c r="AM23" s="22" t="n"/>
       <c r="AN23" s="22" t="n"/>
       <c r="AO23" s="22" t="n"/>
-      <c r="AP23" s="23" t="n"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="61" t="inlineStr">
+      <c r="AP23" s="22" t="n"/>
+      <c r="AQ23" s="22" t="n"/>
+      <c r="AR23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="9" t="n"/>
-      <c r="O24" s="62" t="n"/>
-      <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="62" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="40" t="n"/>
+      <c r="I24" s="40" t="n"/>
+      <c r="J24" s="40" t="n"/>
+      <c r="K24" s="40" t="n"/>
+      <c r="L24" s="40" t="n"/>
+      <c r="M24" s="40" t="n"/>
+      <c r="N24" s="40" t="n"/>
+      <c r="O24" s="64" t="n"/>
+      <c r="P24" s="65" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="8" t="n"/>
       <c r="S24" s="8" t="n"/>
-      <c r="T24" s="20" t="n"/>
-      <c r="V24" s="21" t="n"/>
-      <c r="W24" s="22" t="n"/>
-      <c r="X24" s="22" t="n"/>
-      <c r="Y24" s="22" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="65" t="n"/>
+      <c r="V24" s="8" t="n"/>
+      <c r="W24" s="20" t="n"/>
+      <c r="Y24" s="21" t="n"/>
       <c r="Z24" s="22" t="n"/>
       <c r="AA24" s="22" t="n"/>
       <c r="AB24" s="22" t="n"/>
@@ -2155,37 +2244,43 @@
       <c r="AM24" s="22" t="n"/>
       <c r="AN24" s="22" t="n"/>
       <c r="AO24" s="22" t="n"/>
-      <c r="AP24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="61" t="inlineStr">
+      <c r="AP24" s="22" t="n"/>
+      <c r="AQ24" s="22" t="n"/>
+      <c r="AR24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t>⑧</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-      <c r="L25" s="8" t="n"/>
-      <c r="M25" s="8" t="n"/>
-      <c r="N25" s="9" t="n"/>
-      <c r="O25" s="62" t="n"/>
-      <c r="P25" s="8" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="62" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="40" t="n"/>
+      <c r="J25" s="40" t="n"/>
+      <c r="K25" s="40" t="n"/>
+      <c r="L25" s="40" t="n"/>
+      <c r="M25" s="40" t="n"/>
+      <c r="N25" s="40" t="n"/>
+      <c r="O25" s="64" t="n"/>
+      <c r="P25" s="65" t="n"/>
+      <c r="Q25" s="8" t="n"/>
+      <c r="R25" s="8" t="n"/>
       <c r="S25" s="8" t="n"/>
-      <c r="T25" s="20" t="n"/>
-      <c r="V25" s="21" t="n"/>
-      <c r="W25" s="22" t="n"/>
-      <c r="X25" s="22" t="n"/>
-      <c r="Y25" s="22" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="65" t="n"/>
+      <c r="V25" s="8" t="n"/>
+      <c r="W25" s="20" t="n"/>
+      <c r="Y25" s="21" t="n"/>
       <c r="Z25" s="22" t="n"/>
       <c r="AA25" s="22" t="n"/>
       <c r="AB25" s="22" t="n"/>
@@ -2202,37 +2297,43 @@
       <c r="AM25" s="22" t="n"/>
       <c r="AN25" s="22" t="n"/>
       <c r="AO25" s="22" t="n"/>
-      <c r="AP25" s="23" t="n"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="61" t="inlineStr">
+      <c r="AP25" s="22" t="n"/>
+      <c r="AQ25" s="22" t="n"/>
+      <c r="AR25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>⑨</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n"/>
-      <c r="M26" s="8" t="n"/>
-      <c r="N26" s="9" t="n"/>
-      <c r="O26" s="62" t="n"/>
-      <c r="P26" s="8" t="n"/>
-      <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="62" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="40" t="n"/>
+      <c r="I26" s="40" t="n"/>
+      <c r="J26" s="40" t="n"/>
+      <c r="K26" s="40" t="n"/>
+      <c r="L26" s="40" t="n"/>
+      <c r="M26" s="40" t="n"/>
+      <c r="N26" s="40" t="n"/>
+      <c r="O26" s="64" t="n"/>
+      <c r="P26" s="65" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="8" t="n"/>
       <c r="S26" s="8" t="n"/>
-      <c r="T26" s="20" t="n"/>
-      <c r="V26" s="21" t="n"/>
-      <c r="W26" s="22" t="n"/>
-      <c r="X26" s="22" t="n"/>
-      <c r="Y26" s="22" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="65" t="n"/>
+      <c r="V26" s="8" t="n"/>
+      <c r="W26" s="20" t="n"/>
+      <c r="Y26" s="21" t="n"/>
       <c r="Z26" s="22" t="n"/>
       <c r="AA26" s="22" t="n"/>
       <c r="AB26" s="22" t="n"/>
@@ -2249,37 +2350,43 @@
       <c r="AM26" s="22" t="n"/>
       <c r="AN26" s="22" t="n"/>
       <c r="AO26" s="22" t="n"/>
-      <c r="AP26" s="23" t="n"/>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="AP26" s="22" t="n"/>
+      <c r="AQ26" s="22" t="n"/>
+      <c r="AR26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>⑩</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
-      <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8" t="n"/>
-      <c r="N27" s="9" t="n"/>
-      <c r="O27" s="62" t="n"/>
-      <c r="P27" s="8" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="62" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="40" t="n"/>
+      <c r="I27" s="40" t="n"/>
+      <c r="J27" s="40" t="n"/>
+      <c r="K27" s="40" t="n"/>
+      <c r="L27" s="40" t="n"/>
+      <c r="M27" s="40" t="n"/>
+      <c r="N27" s="40" t="n"/>
+      <c r="O27" s="64" t="n"/>
+      <c r="P27" s="65" t="n"/>
+      <c r="Q27" s="8" t="n"/>
+      <c r="R27" s="8" t="n"/>
       <c r="S27" s="8" t="n"/>
-      <c r="T27" s="20" t="n"/>
-      <c r="V27" s="21" t="n"/>
-      <c r="W27" s="22" t="n"/>
-      <c r="X27" s="22" t="n"/>
-      <c r="Y27" s="22" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="65" t="n"/>
+      <c r="V27" s="8" t="n"/>
+      <c r="W27" s="20" t="n"/>
+      <c r="Y27" s="21" t="n"/>
       <c r="Z27" s="22" t="n"/>
       <c r="AA27" s="22" t="n"/>
       <c r="AB27" s="22" t="n"/>
@@ -2296,37 +2403,43 @@
       <c r="AM27" s="22" t="n"/>
       <c r="AN27" s="22" t="n"/>
       <c r="AO27" s="22" t="n"/>
-      <c r="AP27" s="23" t="n"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="61" t="inlineStr">
+      <c r="AP27" s="22" t="n"/>
+      <c r="AQ27" s="22" t="n"/>
+      <c r="AR27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="62" t="inlineStr">
         <is>
           <t>⑪</t>
         </is>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
-      <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
-      <c r="N28" s="9" t="n"/>
-      <c r="O28" s="62" t="n"/>
-      <c r="P28" s="8" t="n"/>
-      <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="62" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="40" t="n"/>
+      <c r="I28" s="40" t="n"/>
+      <c r="J28" s="40" t="n"/>
+      <c r="K28" s="40" t="n"/>
+      <c r="L28" s="40" t="n"/>
+      <c r="M28" s="40" t="n"/>
+      <c r="N28" s="40" t="n"/>
+      <c r="O28" s="64" t="n"/>
+      <c r="P28" s="65" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n"/>
-      <c r="T28" s="20" t="n"/>
-      <c r="V28" s="21" t="n"/>
-      <c r="W28" s="22" t="n"/>
-      <c r="X28" s="22" t="n"/>
-      <c r="Y28" s="22" t="n"/>
+      <c r="T28" s="9" t="n"/>
+      <c r="U28" s="65" t="n"/>
+      <c r="V28" s="8" t="n"/>
+      <c r="W28" s="20" t="n"/>
+      <c r="Y28" s="21" t="n"/>
       <c r="Z28" s="22" t="n"/>
       <c r="AA28" s="22" t="n"/>
       <c r="AB28" s="22" t="n"/>
@@ -2343,157 +2456,165 @@
       <c r="AM28" s="22" t="n"/>
       <c r="AN28" s="22" t="n"/>
       <c r="AO28" s="22" t="n"/>
-      <c r="AP28" s="23" t="n"/>
-    </row>
-    <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="63" t="inlineStr">
+      <c r="AP28" s="22" t="n"/>
+      <c r="AQ28" s="22" t="n"/>
+      <c r="AR28" s="23" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="66" t="inlineStr">
         <is>
           <t>⑫</t>
         </is>
       </c>
-      <c r="B29" s="64" t="n"/>
-      <c r="C29" s="65" t="n"/>
-      <c r="D29" s="65" t="n"/>
-      <c r="E29" s="65" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="64" t="n"/>
-      <c r="H29" s="65" t="n"/>
-      <c r="I29" s="65" t="n"/>
-      <c r="J29" s="65" t="n"/>
-      <c r="K29" s="65" t="n"/>
-      <c r="L29" s="65" t="n"/>
-      <c r="M29" s="65" t="n"/>
-      <c r="N29" s="66" t="n"/>
-      <c r="O29" s="67" t="n"/>
-      <c r="P29" s="65" t="n"/>
-      <c r="Q29" s="66" t="n"/>
-      <c r="R29" s="67" t="n"/>
-      <c r="S29" s="65" t="n"/>
-      <c r="T29" s="68" t="n"/>
-      <c r="V29" s="69" t="n"/>
-      <c r="W29" s="70" t="n"/>
-      <c r="X29" s="70" t="n"/>
-      <c r="Y29" s="70" t="n"/>
-      <c r="Z29" s="70" t="n"/>
-      <c r="AA29" s="70" t="n"/>
-      <c r="AB29" s="70" t="n"/>
-      <c r="AC29" s="70" t="n"/>
-      <c r="AD29" s="70" t="n"/>
-      <c r="AE29" s="70" t="n"/>
-      <c r="AF29" s="70" t="n"/>
-      <c r="AG29" s="70" t="n"/>
-      <c r="AH29" s="70" t="n"/>
-      <c r="AI29" s="70" t="n"/>
-      <c r="AJ29" s="70" t="n"/>
-      <c r="AK29" s="70" t="n"/>
-      <c r="AL29" s="70" t="n"/>
-      <c r="AM29" s="70" t="n"/>
-      <c r="AN29" s="70" t="n"/>
-      <c r="AO29" s="70" t="n"/>
-      <c r="AP29" s="71" t="n"/>
+      <c r="B29" s="67" t="n"/>
+      <c r="C29" s="68" t="n"/>
+      <c r="D29" s="69" t="n"/>
+      <c r="E29" s="70" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（　　　　　）</t>
+        </is>
+      </c>
+      <c r="F29" s="58" t="n"/>
+      <c r="G29" s="58" t="n"/>
+      <c r="H29" s="58" t="n"/>
+      <c r="I29" s="58" t="n"/>
+      <c r="J29" s="58" t="n"/>
+      <c r="K29" s="58" t="n"/>
+      <c r="L29" s="58" t="n"/>
+      <c r="M29" s="58" t="n"/>
+      <c r="N29" s="58" t="n"/>
+      <c r="O29" s="71" t="n"/>
+      <c r="P29" s="72" t="n"/>
+      <c r="Q29" s="68" t="n"/>
+      <c r="R29" s="68" t="n"/>
+      <c r="S29" s="68" t="n"/>
+      <c r="T29" s="69" t="n"/>
+      <c r="U29" s="72" t="n"/>
+      <c r="V29" s="68" t="n"/>
+      <c r="W29" s="73" t="n"/>
+      <c r="Y29" s="74" t="n"/>
+      <c r="Z29" s="75" t="n"/>
+      <c r="AA29" s="75" t="n"/>
+      <c r="AB29" s="75" t="n"/>
+      <c r="AC29" s="75" t="n"/>
+      <c r="AD29" s="75" t="n"/>
+      <c r="AE29" s="75" t="n"/>
+      <c r="AF29" s="75" t="n"/>
+      <c r="AG29" s="75" t="n"/>
+      <c r="AH29" s="75" t="n"/>
+      <c r="AI29" s="75" t="n"/>
+      <c r="AJ29" s="75" t="n"/>
+      <c r="AK29" s="75" t="n"/>
+      <c r="AL29" s="75" t="n"/>
+      <c r="AM29" s="75" t="n"/>
+      <c r="AN29" s="75" t="n"/>
+      <c r="AO29" s="75" t="n"/>
+      <c r="AP29" s="75" t="n"/>
+      <c r="AQ29" s="75" t="n"/>
+      <c r="AR29" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="O29:Q29"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="P26:T26"/>
+    <mergeCell ref="Y4:AR4"/>
+    <mergeCell ref="E24:O24"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="G19:N19"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="G28:N28"/>
-    <mergeCell ref="E5:T5"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="P14:T14"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E27:O27"/>
+    <mergeCell ref="P28:T28"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="E13:W13"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="E22:O22"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="E4:V4"/>
+    <mergeCell ref="E21:O21"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="R26:T26"/>
-    <mergeCell ref="G27:N27"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="G17:N17"/>
+    <mergeCell ref="H11:P11"/>
+    <mergeCell ref="H9:O9"/>
+    <mergeCell ref="E23:O23"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="G8:W8"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="P6:W6"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="P27:T27"/>
     <mergeCell ref="M14:O14"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="AG2:AP2"/>
-    <mergeCell ref="G20:N20"/>
+    <mergeCell ref="P17:T17"/>
+    <mergeCell ref="U26:W26"/>
+    <mergeCell ref="N12:W12"/>
+    <mergeCell ref="P19:T19"/>
+    <mergeCell ref="E26:O26"/>
     <mergeCell ref="J14:L14"/>
-    <mergeCell ref="R29:T29"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="E13:T13"/>
-    <mergeCell ref="G29:N29"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="G22:N22"/>
-    <mergeCell ref="E4:S4"/>
+    <mergeCell ref="A1:W2"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="E25:O25"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E18:O18"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="V4:AP4"/>
-    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="P20:T20"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="P29:T29"/>
     <mergeCell ref="E9:G9"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="G23:N23"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="G8:T8"/>
+    <mergeCell ref="H10:O10"/>
+    <mergeCell ref="P22:T22"/>
+    <mergeCell ref="P9:W9"/>
+    <mergeCell ref="U28:W28"/>
     <mergeCell ref="E11:G11"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="G18:N18"/>
+    <mergeCell ref="E20:O20"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="P21:T21"/>
+    <mergeCell ref="E29:O29"/>
+    <mergeCell ref="A16:W16"/>
+    <mergeCell ref="P23:T23"/>
+    <mergeCell ref="U20:W20"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="U23:W23"/>
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A1:T2"/>
-    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="G7:P7"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="P18:T18"/>
+    <mergeCell ref="G6:M6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="O9:T9"/>
-    <mergeCell ref="R28:T28"/>
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="P25:T25"/>
     <mergeCell ref="A7:D8"/>
-    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="P10:W10"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="AI2:AR2"/>
+    <mergeCell ref="E17:O17"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="S7:W7"/>
+    <mergeCell ref="E19:O19"/>
     <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="E28:O28"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="G24:N24"/>
-    <mergeCell ref="N12:T12"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O10:T10"/>
-    <mergeCell ref="G26:N26"/>
+    <mergeCell ref="E5:W5"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A9:D10"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="P24:T24"/>
+    <mergeCell ref="P14:W14"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:AP29">
+  <conditionalFormatting sqref="A1:AR29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(A1,1)="■"</formula>
     </cfRule>
@@ -2520,7 +2641,7 @@
     <dataValidation sqref="M14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□その他,■その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6 G8 O6 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
+    <dataValidation sqref="G6 G8 P6 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>

--- a/住宅改修_現地調査アセスメントシート.xlsx
+++ b/住宅改修_現地調査アセスメントシート.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アセスメントシート" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'アセスメントシート'!$A$1:$AR$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'アセスメントシート'!$A$1:$AS$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -536,16 +536,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -575,11 +573,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -590,7 +590,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -600,12 +606,17 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -992,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AR29"/>
+  <dimension ref="A1:AS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.36328125" customWidth="1" min="1" max="1"/>
@@ -1021,7 +1032,7 @@
     <col width="3.36328125" customWidth="1" min="24" max="24"/>
     <col width="3.36328125" customWidth="1" min="25" max="25"/>
     <col width="3.36328125" customWidth="1" min="26" max="26"/>
-    <col width="3.36328125" customWidth="1" min="27" max="27"/>
+    <col width="1.140625" customWidth="1" min="27" max="27"/>
     <col width="3.36328125" customWidth="1" min="28" max="28"/>
     <col width="3.36328125" customWidth="1" min="29" max="29"/>
     <col width="3.36328125" customWidth="1" min="30" max="30"/>
@@ -1039,6 +1050,7 @@
     <col width="3.36328125" customWidth="1" min="42" max="42"/>
     <col width="3.36328125" customWidth="1" min="43" max="43"/>
     <col width="3.36328125" customWidth="1" min="44" max="44"/>
+    <col width="3.36328125" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -1069,6 +1081,9 @@
       <c r="U1" s="2" t="n"/>
       <c r="V1" s="2" t="n"/>
       <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="n"/>
@@ -1094,19 +1109,21 @@
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="n"/>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="X2" s="3" t="n"/>
+      <c r="Y2" s="3" t="n"/>
+      <c r="Z2" s="3" t="n"/>
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>調査日</t>
         </is>
       </c>
-      <c r="AG2" s="5" t="n"/>
-      <c r="AH2" s="6" t="n"/>
-      <c r="AI2" s="7" t="inlineStr">
+      <c r="AH2" s="5" t="n"/>
+      <c r="AI2" s="6" t="n"/>
+      <c r="AJ2" s="7" t="inlineStr">
         <is>
           <t>令和　　年　　月　　日</t>
         </is>
       </c>
-      <c r="AJ2" s="8" t="n"/>
       <c r="AK2" s="8" t="n"/>
       <c r="AL2" s="8" t="n"/>
       <c r="AM2" s="8" t="n"/>
@@ -1114,7 +1131,8 @@
       <c r="AO2" s="8" t="n"/>
       <c r="AP2" s="8" t="n"/>
       <c r="AQ2" s="8" t="n"/>
-      <c r="AR2" s="9" t="n"/>
+      <c r="AR2" s="8" t="n"/>
+      <c r="AS2" s="9" t="n"/>
     </row>
     <row r="3" ht="4.5" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
@@ -1144,19 +1162,19 @@
       <c r="T4" s="14" t="n"/>
       <c r="U4" s="14" t="n"/>
       <c r="V4" s="14" t="n"/>
-      <c r="W4" s="15" t="inlineStr">
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+      <c r="Z4" s="15" t="inlineStr">
         <is>
           <t>様</t>
         </is>
       </c>
-      <c r="Y4" s="16" t="inlineStr">
+      <c r="AB4" s="16" t="inlineStr">
         <is>
           <t>平面図</t>
         </is>
       </c>
-      <c r="Z4" s="17" t="n"/>
-      <c r="AA4" s="17" t="n"/>
-      <c r="AB4" s="17" t="n"/>
       <c r="AC4" s="17" t="n"/>
       <c r="AD4" s="17" t="n"/>
       <c r="AE4" s="17" t="n"/>
@@ -1172,7 +1190,8 @@
       <c r="AO4" s="17" t="n"/>
       <c r="AP4" s="17" t="n"/>
       <c r="AQ4" s="17" t="n"/>
-      <c r="AR4" s="18" t="n"/>
+      <c r="AR4" s="17" t="n"/>
+      <c r="AS4" s="18" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -1201,11 +1220,11 @@
       <c r="T5" s="8" t="n"/>
       <c r="U5" s="8" t="n"/>
       <c r="V5" s="8" t="n"/>
-      <c r="W5" s="20" t="n"/>
-      <c r="Y5" s="21" t="n"/>
-      <c r="Z5" s="22" t="n"/>
-      <c r="AA5" s="22" t="n"/>
-      <c r="AB5" s="22" t="n"/>
+      <c r="W5" s="8" t="n"/>
+      <c r="X5" s="8" t="n"/>
+      <c r="Y5" s="8" t="n"/>
+      <c r="Z5" s="20" t="n"/>
+      <c r="AB5" s="21" t="n"/>
       <c r="AC5" s="22" t="n"/>
       <c r="AD5" s="22" t="n"/>
       <c r="AE5" s="22" t="n"/>
@@ -1221,7 +1240,8 @@
       <c r="AO5" s="22" t="n"/>
       <c r="AP5" s="22" t="n"/>
       <c r="AQ5" s="22" t="n"/>
-      <c r="AR5" s="23" t="n"/>
+      <c r="AR5" s="22" t="n"/>
+      <c r="AS5" s="23" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -1244,25 +1264,25 @@
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="24" t="inlineStr">
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="24" t="inlineStr">
         <is>
           <t>携帯</t>
         </is>
       </c>
-      <c r="O6" s="25" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="8" t="n"/>
-      <c r="R6" s="8" t="n"/>
+      <c r="Q6" s="25" t="n"/>
+      <c r="R6" s="7" t="n"/>
       <c r="S6" s="8" t="n"/>
       <c r="T6" s="8" t="n"/>
       <c r="U6" s="8" t="n"/>
       <c r="V6" s="8" t="n"/>
-      <c r="W6" s="20" t="n"/>
-      <c r="Y6" s="21" t="n"/>
-      <c r="Z6" s="22" t="n"/>
-      <c r="AA6" s="22" t="n"/>
-      <c r="AB6" s="22" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="20" t="n"/>
+      <c r="AB6" s="21" t="n"/>
       <c r="AC6" s="22" t="n"/>
       <c r="AD6" s="22" t="n"/>
       <c r="AE6" s="22" t="n"/>
@@ -1278,7 +1298,8 @@
       <c r="AO6" s="22" t="n"/>
       <c r="AP6" s="22" t="n"/>
       <c r="AQ6" s="22" t="n"/>
-      <c r="AR6" s="23" t="n"/>
+      <c r="AR6" s="22" t="n"/>
+      <c r="AS6" s="23" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
@@ -1304,22 +1325,22 @@
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="24" t="inlineStr">
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="24" t="inlineStr">
         <is>
           <t>続柄</t>
         </is>
       </c>
-      <c r="R7" s="25" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="8" t="n"/>
-      <c r="U7" s="8" t="n"/>
+      <c r="T7" s="25" t="n"/>
+      <c r="U7" s="7" t="n"/>
       <c r="V7" s="8" t="n"/>
-      <c r="W7" s="20" t="n"/>
-      <c r="Y7" s="21" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="20" t="n"/>
+      <c r="AB7" s="21" t="n"/>
       <c r="AC7" s="22" t="n"/>
       <c r="AD7" s="22" t="n"/>
       <c r="AE7" s="22" t="n"/>
@@ -1335,7 +1356,8 @@
       <c r="AO7" s="22" t="n"/>
       <c r="AP7" s="22" t="n"/>
       <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="23" t="n"/>
+      <c r="AR7" s="22" t="n"/>
+      <c r="AS7" s="23" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="29" t="n"/>
@@ -1364,11 +1386,11 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
       <c r="V8" s="8" t="n"/>
-      <c r="W8" s="20" t="n"/>
-      <c r="Y8" s="21" t="n"/>
-      <c r="Z8" s="22" t="n"/>
-      <c r="AA8" s="22" t="n"/>
-      <c r="AB8" s="22" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="20" t="n"/>
+      <c r="AB8" s="21" t="n"/>
       <c r="AC8" s="22" t="n"/>
       <c r="AD8" s="22" t="n"/>
       <c r="AE8" s="22" t="n"/>
@@ -1384,7 +1406,8 @@
       <c r="AO8" s="22" t="n"/>
       <c r="AP8" s="22" t="n"/>
       <c r="AQ8" s="22" t="n"/>
-      <c r="AR8" s="23" t="n"/>
+      <c r="AR8" s="22" t="n"/>
+      <c r="AS8" s="23" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="32" t="inlineStr">
@@ -1408,29 +1431,29 @@
           <t>月　火　水　木　金　土　日</t>
         </is>
       </c>
-      <c r="I9" s="37" t="n"/>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
-      <c r="L9" s="37" t="n"/>
-      <c r="M9" s="37" t="n"/>
-      <c r="N9" s="37" t="n"/>
-      <c r="O9" s="38" t="n"/>
-      <c r="P9" s="39" t="inlineStr">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="8" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　時 ～ 　　時</t>
         </is>
       </c>
-      <c r="Q9" s="40" t="n"/>
-      <c r="R9" s="40" t="n"/>
-      <c r="S9" s="40" t="n"/>
-      <c r="T9" s="40" t="n"/>
-      <c r="U9" s="40" t="n"/>
-      <c r="V9" s="40" t="n"/>
-      <c r="W9" s="41" t="n"/>
-      <c r="Y9" s="21" t="n"/>
-      <c r="Z9" s="22" t="n"/>
-      <c r="AA9" s="22" t="n"/>
-      <c r="AB9" s="22" t="n"/>
+      <c r="R9" s="38" t="n"/>
+      <c r="S9" s="38" t="n"/>
+      <c r="T9" s="38" t="n"/>
+      <c r="U9" s="38" t="n"/>
+      <c r="V9" s="38" t="n"/>
+      <c r="W9" s="38" t="n"/>
+      <c r="X9" s="38" t="n"/>
+      <c r="Y9" s="38" t="n"/>
+      <c r="Z9" s="39" t="n"/>
+      <c r="AB9" s="21" t="n"/>
       <c r="AC9" s="22" t="n"/>
       <c r="AD9" s="22" t="n"/>
       <c r="AE9" s="22" t="n"/>
@@ -1446,48 +1469,49 @@
       <c r="AO9" s="22" t="n"/>
       <c r="AP9" s="22" t="n"/>
       <c r="AQ9" s="22" t="n"/>
-      <c r="AR9" s="23" t="n"/>
+      <c r="AR9" s="22" t="n"/>
+      <c r="AS9" s="23" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="42" t="n"/>
-      <c r="B10" s="43" t="n"/>
-      <c r="C10" s="43" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="45" t="inlineStr">
+      <c r="A10" s="40" t="n"/>
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="43" t="inlineStr">
         <is>
           <t>キーパーソン</t>
         </is>
       </c>
-      <c r="F10" s="46" t="n"/>
-      <c r="G10" s="47" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="45" t="n"/>
       <c r="H10" s="36" t="inlineStr">
         <is>
           <t>月　火　水　木　金　土　日</t>
         </is>
       </c>
-      <c r="I10" s="37" t="n"/>
-      <c r="J10" s="37" t="n"/>
-      <c r="K10" s="37" t="n"/>
-      <c r="L10" s="37" t="n"/>
-      <c r="M10" s="37" t="n"/>
-      <c r="N10" s="37" t="n"/>
-      <c r="O10" s="38" t="n"/>
-      <c r="P10" s="39" t="inlineStr">
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　時 ～ 　　時</t>
         </is>
       </c>
-      <c r="Q10" s="40" t="n"/>
-      <c r="R10" s="40" t="n"/>
-      <c r="S10" s="40" t="n"/>
-      <c r="T10" s="40" t="n"/>
-      <c r="U10" s="40" t="n"/>
-      <c r="V10" s="40" t="n"/>
-      <c r="W10" s="41" t="n"/>
-      <c r="Y10" s="21" t="n"/>
-      <c r="Z10" s="22" t="n"/>
-      <c r="AA10" s="22" t="n"/>
-      <c r="AB10" s="22" t="n"/>
+      <c r="R10" s="38" t="n"/>
+      <c r="S10" s="38" t="n"/>
+      <c r="T10" s="38" t="n"/>
+      <c r="U10" s="38" t="n"/>
+      <c r="V10" s="38" t="n"/>
+      <c r="W10" s="38" t="n"/>
+      <c r="X10" s="38" t="n"/>
+      <c r="Y10" s="38" t="n"/>
+      <c r="Z10" s="39" t="n"/>
+      <c r="AB10" s="21" t="n"/>
       <c r="AC10" s="22" t="n"/>
       <c r="AD10" s="22" t="n"/>
       <c r="AE10" s="22" t="n"/>
@@ -1503,7 +1527,8 @@
       <c r="AO10" s="22" t="n"/>
       <c r="AP10" s="22" t="n"/>
       <c r="AQ10" s="22" t="n"/>
-      <c r="AR10" s="23" t="n"/>
+      <c r="AR10" s="22" t="n"/>
+      <c r="AS10" s="23" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -1529,22 +1554,22 @@
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="24" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="R11" s="25" t="n"/>
-      <c r="S11" s="7" t="n"/>
-      <c r="T11" s="8" t="n"/>
-      <c r="U11" s="8" t="n"/>
+      <c r="T11" s="25" t="n"/>
+      <c r="U11" s="7" t="n"/>
       <c r="V11" s="8" t="n"/>
-      <c r="W11" s="20" t="n"/>
-      <c r="Y11" s="21" t="n"/>
-      <c r="Z11" s="22" t="n"/>
-      <c r="AA11" s="22" t="n"/>
-      <c r="AB11" s="22" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="20" t="n"/>
+      <c r="AB11" s="21" t="n"/>
       <c r="AC11" s="22" t="n"/>
       <c r="AD11" s="22" t="n"/>
       <c r="AE11" s="22" t="n"/>
@@ -1560,7 +1585,8 @@
       <c r="AO11" s="22" t="n"/>
       <c r="AP11" s="22" t="n"/>
       <c r="AQ11" s="22" t="n"/>
-      <c r="AR11" s="23" t="n"/>
+      <c r="AR11" s="22" t="n"/>
+      <c r="AS11" s="23" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -1571,28 +1597,28 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="48" t="inlineStr">
+      <c r="E12" s="46" t="inlineStr">
         <is>
           <t>□1割</t>
         </is>
       </c>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
-      <c r="H12" s="49" t="inlineStr">
+      <c r="H12" s="47" t="inlineStr">
         <is>
           <t>□2割</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
-      <c r="K12" s="49" t="inlineStr">
+      <c r="K12" s="47" t="inlineStr">
         <is>
           <t>□3割</t>
         </is>
       </c>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
-      <c r="N12" s="50" t="n"/>
+      <c r="N12" s="48" t="n"/>
       <c r="O12" s="8" t="n"/>
       <c r="P12" s="8" t="n"/>
       <c r="Q12" s="8" t="n"/>
@@ -1601,11 +1627,11 @@
       <c r="T12" s="8" t="n"/>
       <c r="U12" s="8" t="n"/>
       <c r="V12" s="8" t="n"/>
-      <c r="W12" s="20" t="n"/>
-      <c r="Y12" s="21" t="n"/>
-      <c r="Z12" s="22" t="n"/>
-      <c r="AA12" s="22" t="n"/>
-      <c r="AB12" s="22" t="n"/>
+      <c r="W12" s="8" t="n"/>
+      <c r="X12" s="8" t="n"/>
+      <c r="Y12" s="8" t="n"/>
+      <c r="Z12" s="20" t="n"/>
+      <c r="AB12" s="21" t="n"/>
       <c r="AC12" s="22" t="n"/>
       <c r="AD12" s="22" t="n"/>
       <c r="AE12" s="22" t="n"/>
@@ -1621,7 +1647,8 @@
       <c r="AO12" s="22" t="n"/>
       <c r="AP12" s="22" t="n"/>
       <c r="AQ12" s="22" t="n"/>
-      <c r="AR12" s="23" t="n"/>
+      <c r="AR12" s="22" t="n"/>
+      <c r="AS12" s="23" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -1650,11 +1677,11 @@
       <c r="T13" s="8" t="n"/>
       <c r="U13" s="8" t="n"/>
       <c r="V13" s="8" t="n"/>
-      <c r="W13" s="20" t="n"/>
-      <c r="Y13" s="21" t="n"/>
-      <c r="Z13" s="22" t="n"/>
-      <c r="AA13" s="22" t="n"/>
-      <c r="AB13" s="22" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="20" t="n"/>
+      <c r="AB13" s="21" t="n"/>
       <c r="AC13" s="22" t="n"/>
       <c r="AD13" s="22" t="n"/>
       <c r="AE13" s="22" t="n"/>
@@ -1670,60 +1697,65 @@
       <c r="AO13" s="22" t="n"/>
       <c r="AP13" s="22" t="n"/>
       <c r="AQ13" s="22" t="n"/>
-      <c r="AR13" s="23" t="n"/>
+      <c r="AR13" s="22" t="n"/>
+      <c r="AS13" s="23" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>麻痺</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="53" t="n"/>
-      <c r="E14" s="54" t="inlineStr">
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="52" t="inlineStr">
         <is>
           <t>□なし</t>
         </is>
       </c>
-      <c r="F14" s="55" t="n"/>
-      <c r="G14" s="56" t="inlineStr">
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="54" t="inlineStr">
         <is>
           <t>□右片麻痺</t>
         </is>
       </c>
-      <c r="H14" s="55" t="n"/>
-      <c r="I14" s="55" t="n"/>
-      <c r="J14" s="56" t="inlineStr">
+      <c r="H14" s="53" t="n"/>
+      <c r="I14" s="53" t="n"/>
+      <c r="J14" s="54" t="inlineStr">
         <is>
           <t>□左片麻痺</t>
         </is>
       </c>
-      <c r="K14" s="55" t="n"/>
-      <c r="L14" s="55" t="n"/>
-      <c r="M14" s="56" t="inlineStr">
+      <c r="K14" s="53" t="n"/>
+      <c r="L14" s="53" t="n"/>
+      <c r="M14" s="54" t="inlineStr">
         <is>
           <t>□その他</t>
         </is>
       </c>
-      <c r="N14" s="55" t="n"/>
-      <c r="O14" s="55" t="n"/>
-      <c r="P14" s="57" t="inlineStr">
-        <is>
-          <t>（　　　　　　）</t>
-        </is>
-      </c>
-      <c r="Q14" s="58" t="n"/>
-      <c r="R14" s="58" t="n"/>
-      <c r="S14" s="58" t="n"/>
-      <c r="T14" s="58" t="n"/>
-      <c r="U14" s="58" t="n"/>
-      <c r="V14" s="58" t="n"/>
-      <c r="W14" s="59" t="n"/>
-      <c r="Y14" s="21" t="n"/>
-      <c r="Z14" s="22" t="n"/>
-      <c r="AA14" s="22" t="n"/>
-      <c r="AB14" s="22" t="n"/>
+      <c r="N14" s="53" t="n"/>
+      <c r="O14" s="53" t="n"/>
+      <c r="P14" s="54" t="inlineStr">
+        <is>
+          <t>（</t>
+        </is>
+      </c>
+      <c r="Q14" s="55" t="n"/>
+      <c r="R14" s="56" t="n"/>
+      <c r="S14" s="56" t="n"/>
+      <c r="T14" s="56" t="n"/>
+      <c r="U14" s="56" t="n"/>
+      <c r="V14" s="56" t="n"/>
+      <c r="W14" s="56" t="n"/>
+      <c r="X14" s="56" t="n"/>
+      <c r="Y14" s="56" t="n"/>
+      <c r="Z14" s="57" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="AB14" s="21" t="n"/>
       <c r="AC14" s="22" t="n"/>
       <c r="AD14" s="22" t="n"/>
       <c r="AE14" s="22" t="n"/>
@@ -1739,13 +1771,11 @@
       <c r="AO14" s="22" t="n"/>
       <c r="AP14" s="22" t="n"/>
       <c r="AQ14" s="22" t="n"/>
-      <c r="AR14" s="23" t="n"/>
+      <c r="AR14" s="22" t="n"/>
+      <c r="AS14" s="23" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="Y15" s="21" t="n"/>
-      <c r="Z15" s="22" t="n"/>
-      <c r="AA15" s="22" t="n"/>
-      <c r="AB15" s="22" t="n"/>
+      <c r="AB15" s="21" t="n"/>
       <c r="AC15" s="22" t="n"/>
       <c r="AD15" s="22" t="n"/>
       <c r="AE15" s="22" t="n"/>
@@ -1761,7 +1791,8 @@
       <c r="AO15" s="22" t="n"/>
       <c r="AP15" s="22" t="n"/>
       <c r="AQ15" s="22" t="n"/>
-      <c r="AR15" s="23" t="n"/>
+      <c r="AR15" s="22" t="n"/>
+      <c r="AS15" s="23" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -1790,11 +1821,11 @@
       <c r="T16" s="17" t="n"/>
       <c r="U16" s="17" t="n"/>
       <c r="V16" s="17" t="n"/>
-      <c r="W16" s="18" t="n"/>
-      <c r="Y16" s="21" t="n"/>
-      <c r="Z16" s="22" t="n"/>
-      <c r="AA16" s="22" t="n"/>
-      <c r="AB16" s="22" t="n"/>
+      <c r="W16" s="17" t="n"/>
+      <c r="X16" s="17" t="n"/>
+      <c r="Y16" s="17" t="n"/>
+      <c r="Z16" s="18" t="n"/>
+      <c r="AB16" s="21" t="n"/>
       <c r="AC16" s="22" t="n"/>
       <c r="AD16" s="22" t="n"/>
       <c r="AE16" s="22" t="n"/>
@@ -1810,10 +1841,11 @@
       <c r="AO16" s="22" t="n"/>
       <c r="AP16" s="22" t="n"/>
       <c r="AQ16" s="22" t="n"/>
-      <c r="AR16" s="23" t="n"/>
+      <c r="AR16" s="22" t="n"/>
+      <c r="AS16" s="23" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
@@ -1839,27 +1871,27 @@
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="24" t="inlineStr">
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="24" t="inlineStr">
         <is>
           <t>手すり長さ</t>
         </is>
       </c>
-      <c r="Q17" s="35" t="n"/>
-      <c r="R17" s="35" t="n"/>
-      <c r="S17" s="35" t="n"/>
-      <c r="T17" s="25" t="n"/>
-      <c r="U17" s="24" t="inlineStr">
+      <c r="T17" s="35" t="n"/>
+      <c r="U17" s="35" t="n"/>
+      <c r="V17" s="35" t="n"/>
+      <c r="W17" s="25" t="n"/>
+      <c r="X17" s="24" t="inlineStr">
         <is>
           <t>手すり高さ</t>
         </is>
       </c>
-      <c r="V17" s="35" t="n"/>
-      <c r="W17" s="61" t="n"/>
-      <c r="Y17" s="21" t="n"/>
-      <c r="Z17" s="22" t="n"/>
-      <c r="AA17" s="22" t="n"/>
-      <c r="AB17" s="22" t="n"/>
+      <c r="Y17" s="35" t="n"/>
+      <c r="Z17" s="59" t="n"/>
+      <c r="AB17" s="21" t="n"/>
       <c r="AC17" s="22" t="n"/>
       <c r="AD17" s="22" t="n"/>
       <c r="AE17" s="22" t="n"/>
@@ -1875,10 +1907,11 @@
       <c r="AO17" s="22" t="n"/>
       <c r="AP17" s="22" t="n"/>
       <c r="AQ17" s="22" t="n"/>
-      <c r="AR17" s="23" t="n"/>
+      <c r="AR17" s="22" t="n"/>
+      <c r="AS17" s="23" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="62" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>①</t>
         </is>
@@ -1886,33 +1919,37 @@
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="9" t="n"/>
-      <c r="E18" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F18" s="40" t="n"/>
-      <c r="G18" s="40" t="n"/>
-      <c r="H18" s="40" t="n"/>
-      <c r="I18" s="40" t="n"/>
-      <c r="J18" s="40" t="n"/>
-      <c r="K18" s="40" t="n"/>
-      <c r="L18" s="40" t="n"/>
-      <c r="M18" s="40" t="n"/>
-      <c r="N18" s="40" t="n"/>
-      <c r="O18" s="64" t="n"/>
-      <c r="P18" s="65" t="n"/>
-      <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="8" t="n"/>
-      <c r="S18" s="8" t="n"/>
-      <c r="T18" s="9" t="n"/>
-      <c r="U18" s="65" t="n"/>
+      <c r="E18" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F18" s="62" t="n"/>
+      <c r="G18" s="62" t="n"/>
+      <c r="H18" s="62" t="n"/>
+      <c r="I18" s="62" t="n"/>
+      <c r="J18" s="62" t="n"/>
+      <c r="K18" s="62" t="n"/>
+      <c r="L18" s="62" t="n"/>
+      <c r="M18" s="63" t="n"/>
+      <c r="N18" s="62" t="n"/>
+      <c r="O18" s="62" t="n"/>
+      <c r="P18" s="62" t="n"/>
+      <c r="Q18" s="62" t="n"/>
+      <c r="R18" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S18" s="65" t="n"/>
+      <c r="T18" s="8" t="n"/>
+      <c r="U18" s="8" t="n"/>
       <c r="V18" s="8" t="n"/>
-      <c r="W18" s="20" t="n"/>
-      <c r="Y18" s="21" t="n"/>
-      <c r="Z18" s="22" t="n"/>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="22" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="65" t="n"/>
+      <c r="Y18" s="8" t="n"/>
+      <c r="Z18" s="20" t="n"/>
+      <c r="AB18" s="21" t="n"/>
       <c r="AC18" s="22" t="n"/>
       <c r="AD18" s="22" t="n"/>
       <c r="AE18" s="22" t="n"/>
@@ -1928,10 +1965,11 @@
       <c r="AO18" s="22" t="n"/>
       <c r="AP18" s="22" t="n"/>
       <c r="AQ18" s="22" t="n"/>
-      <c r="AR18" s="23" t="n"/>
+      <c r="AR18" s="22" t="n"/>
+      <c r="AS18" s="23" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="62" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>②</t>
         </is>
@@ -1939,33 +1977,37 @@
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="9" t="n"/>
-      <c r="E19" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F19" s="40" t="n"/>
-      <c r="G19" s="40" t="n"/>
-      <c r="H19" s="40" t="n"/>
-      <c r="I19" s="40" t="n"/>
-      <c r="J19" s="40" t="n"/>
-      <c r="K19" s="40" t="n"/>
-      <c r="L19" s="40" t="n"/>
-      <c r="M19" s="40" t="n"/>
-      <c r="N19" s="40" t="n"/>
-      <c r="O19" s="64" t="n"/>
-      <c r="P19" s="65" t="n"/>
-      <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="8" t="n"/>
-      <c r="S19" s="8" t="n"/>
-      <c r="T19" s="9" t="n"/>
-      <c r="U19" s="65" t="n"/>
+      <c r="E19" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F19" s="62" t="n"/>
+      <c r="G19" s="62" t="n"/>
+      <c r="H19" s="62" t="n"/>
+      <c r="I19" s="62" t="n"/>
+      <c r="J19" s="62" t="n"/>
+      <c r="K19" s="62" t="n"/>
+      <c r="L19" s="62" t="n"/>
+      <c r="M19" s="63" t="n"/>
+      <c r="N19" s="62" t="n"/>
+      <c r="O19" s="62" t="n"/>
+      <c r="P19" s="62" t="n"/>
+      <c r="Q19" s="62" t="n"/>
+      <c r="R19" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S19" s="65" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
-      <c r="W19" s="20" t="n"/>
-      <c r="Y19" s="21" t="n"/>
-      <c r="Z19" s="22" t="n"/>
-      <c r="AA19" s="22" t="n"/>
-      <c r="AB19" s="22" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="65" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="20" t="n"/>
+      <c r="AB19" s="21" t="n"/>
       <c r="AC19" s="22" t="n"/>
       <c r="AD19" s="22" t="n"/>
       <c r="AE19" s="22" t="n"/>
@@ -1981,10 +2023,11 @@
       <c r="AO19" s="22" t="n"/>
       <c r="AP19" s="22" t="n"/>
       <c r="AQ19" s="22" t="n"/>
-      <c r="AR19" s="23" t="n"/>
+      <c r="AR19" s="22" t="n"/>
+      <c r="AS19" s="23" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="62" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>③</t>
         </is>
@@ -1992,33 +2035,37 @@
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="9" t="n"/>
-      <c r="E20" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F20" s="40" t="n"/>
-      <c r="G20" s="40" t="n"/>
-      <c r="H20" s="40" t="n"/>
-      <c r="I20" s="40" t="n"/>
-      <c r="J20" s="40" t="n"/>
-      <c r="K20" s="40" t="n"/>
-      <c r="L20" s="40" t="n"/>
-      <c r="M20" s="40" t="n"/>
-      <c r="N20" s="40" t="n"/>
-      <c r="O20" s="64" t="n"/>
-      <c r="P20" s="65" t="n"/>
-      <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="8" t="n"/>
-      <c r="S20" s="8" t="n"/>
-      <c r="T20" s="9" t="n"/>
-      <c r="U20" s="65" t="n"/>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F20" s="62" t="n"/>
+      <c r="G20" s="62" t="n"/>
+      <c r="H20" s="62" t="n"/>
+      <c r="I20" s="62" t="n"/>
+      <c r="J20" s="62" t="n"/>
+      <c r="K20" s="62" t="n"/>
+      <c r="L20" s="62" t="n"/>
+      <c r="M20" s="63" t="n"/>
+      <c r="N20" s="62" t="n"/>
+      <c r="O20" s="62" t="n"/>
+      <c r="P20" s="62" t="n"/>
+      <c r="Q20" s="62" t="n"/>
+      <c r="R20" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S20" s="65" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
-      <c r="W20" s="20" t="n"/>
-      <c r="Y20" s="21" t="n"/>
-      <c r="Z20" s="22" t="n"/>
-      <c r="AA20" s="22" t="n"/>
-      <c r="AB20" s="22" t="n"/>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="65" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="20" t="n"/>
+      <c r="AB20" s="21" t="n"/>
       <c r="AC20" s="22" t="n"/>
       <c r="AD20" s="22" t="n"/>
       <c r="AE20" s="22" t="n"/>
@@ -2034,10 +2081,11 @@
       <c r="AO20" s="22" t="n"/>
       <c r="AP20" s="22" t="n"/>
       <c r="AQ20" s="22" t="n"/>
-      <c r="AR20" s="23" t="n"/>
+      <c r="AR20" s="22" t="n"/>
+      <c r="AS20" s="23" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="62" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>④</t>
         </is>
@@ -2045,33 +2093,37 @@
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F21" s="40" t="n"/>
-      <c r="G21" s="40" t="n"/>
-      <c r="H21" s="40" t="n"/>
-      <c r="I21" s="40" t="n"/>
-      <c r="J21" s="40" t="n"/>
-      <c r="K21" s="40" t="n"/>
-      <c r="L21" s="40" t="n"/>
-      <c r="M21" s="40" t="n"/>
-      <c r="N21" s="40" t="n"/>
-      <c r="O21" s="64" t="n"/>
-      <c r="P21" s="65" t="n"/>
-      <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="8" t="n"/>
-      <c r="S21" s="8" t="n"/>
-      <c r="T21" s="9" t="n"/>
-      <c r="U21" s="65" t="n"/>
+      <c r="E21" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="62" t="n"/>
+      <c r="H21" s="62" t="n"/>
+      <c r="I21" s="62" t="n"/>
+      <c r="J21" s="62" t="n"/>
+      <c r="K21" s="62" t="n"/>
+      <c r="L21" s="62" t="n"/>
+      <c r="M21" s="63" t="n"/>
+      <c r="N21" s="62" t="n"/>
+      <c r="O21" s="62" t="n"/>
+      <c r="P21" s="62" t="n"/>
+      <c r="Q21" s="62" t="n"/>
+      <c r="R21" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S21" s="65" t="n"/>
+      <c r="T21" s="8" t="n"/>
+      <c r="U21" s="8" t="n"/>
       <c r="V21" s="8" t="n"/>
-      <c r="W21" s="20" t="n"/>
-      <c r="Y21" s="21" t="n"/>
-      <c r="Z21" s="22" t="n"/>
-      <c r="AA21" s="22" t="n"/>
-      <c r="AB21" s="22" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="65" t="n"/>
+      <c r="Y21" s="8" t="n"/>
+      <c r="Z21" s="20" t="n"/>
+      <c r="AB21" s="21" t="n"/>
       <c r="AC21" s="22" t="n"/>
       <c r="AD21" s="22" t="n"/>
       <c r="AE21" s="22" t="n"/>
@@ -2087,10 +2139,11 @@
       <c r="AO21" s="22" t="n"/>
       <c r="AP21" s="22" t="n"/>
       <c r="AQ21" s="22" t="n"/>
-      <c r="AR21" s="23" t="n"/>
+      <c r="AR21" s="22" t="n"/>
+      <c r="AS21" s="23" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="62" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
@@ -2098,33 +2151,37 @@
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="9" t="n"/>
-      <c r="E22" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F22" s="40" t="n"/>
-      <c r="G22" s="40" t="n"/>
-      <c r="H22" s="40" t="n"/>
-      <c r="I22" s="40" t="n"/>
-      <c r="J22" s="40" t="n"/>
-      <c r="K22" s="40" t="n"/>
-      <c r="L22" s="40" t="n"/>
-      <c r="M22" s="40" t="n"/>
-      <c r="N22" s="40" t="n"/>
-      <c r="O22" s="64" t="n"/>
-      <c r="P22" s="65" t="n"/>
-      <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="8" t="n"/>
-      <c r="S22" s="8" t="n"/>
-      <c r="T22" s="9" t="n"/>
-      <c r="U22" s="65" t="n"/>
+      <c r="E22" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F22" s="62" t="n"/>
+      <c r="G22" s="62" t="n"/>
+      <c r="H22" s="62" t="n"/>
+      <c r="I22" s="62" t="n"/>
+      <c r="J22" s="62" t="n"/>
+      <c r="K22" s="62" t="n"/>
+      <c r="L22" s="62" t="n"/>
+      <c r="M22" s="63" t="n"/>
+      <c r="N22" s="62" t="n"/>
+      <c r="O22" s="62" t="n"/>
+      <c r="P22" s="62" t="n"/>
+      <c r="Q22" s="62" t="n"/>
+      <c r="R22" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S22" s="65" t="n"/>
+      <c r="T22" s="8" t="n"/>
+      <c r="U22" s="8" t="n"/>
       <c r="V22" s="8" t="n"/>
-      <c r="W22" s="20" t="n"/>
-      <c r="Y22" s="21" t="n"/>
-      <c r="Z22" s="22" t="n"/>
-      <c r="AA22" s="22" t="n"/>
-      <c r="AB22" s="22" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="65" t="n"/>
+      <c r="Y22" s="8" t="n"/>
+      <c r="Z22" s="20" t="n"/>
+      <c r="AB22" s="21" t="n"/>
       <c r="AC22" s="22" t="n"/>
       <c r="AD22" s="22" t="n"/>
       <c r="AE22" s="22" t="n"/>
@@ -2140,10 +2197,11 @@
       <c r="AO22" s="22" t="n"/>
       <c r="AP22" s="22" t="n"/>
       <c r="AQ22" s="22" t="n"/>
-      <c r="AR22" s="23" t="n"/>
+      <c r="AR22" s="22" t="n"/>
+      <c r="AS22" s="23" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="62" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
@@ -2151,33 +2209,37 @@
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F23" s="40" t="n"/>
-      <c r="G23" s="40" t="n"/>
-      <c r="H23" s="40" t="n"/>
-      <c r="I23" s="40" t="n"/>
-      <c r="J23" s="40" t="n"/>
-      <c r="K23" s="40" t="n"/>
-      <c r="L23" s="40" t="n"/>
-      <c r="M23" s="40" t="n"/>
-      <c r="N23" s="40" t="n"/>
-      <c r="O23" s="64" t="n"/>
-      <c r="P23" s="65" t="n"/>
-      <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="8" t="n"/>
-      <c r="S23" s="8" t="n"/>
-      <c r="T23" s="9" t="n"/>
-      <c r="U23" s="65" t="n"/>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F23" s="62" t="n"/>
+      <c r="G23" s="62" t="n"/>
+      <c r="H23" s="62" t="n"/>
+      <c r="I23" s="62" t="n"/>
+      <c r="J23" s="62" t="n"/>
+      <c r="K23" s="62" t="n"/>
+      <c r="L23" s="62" t="n"/>
+      <c r="M23" s="63" t="n"/>
+      <c r="N23" s="62" t="n"/>
+      <c r="O23" s="62" t="n"/>
+      <c r="P23" s="62" t="n"/>
+      <c r="Q23" s="62" t="n"/>
+      <c r="R23" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S23" s="65" t="n"/>
+      <c r="T23" s="8" t="n"/>
+      <c r="U23" s="8" t="n"/>
       <c r="V23" s="8" t="n"/>
-      <c r="W23" s="20" t="n"/>
-      <c r="Y23" s="21" t="n"/>
-      <c r="Z23" s="22" t="n"/>
-      <c r="AA23" s="22" t="n"/>
-      <c r="AB23" s="22" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="65" t="n"/>
+      <c r="Y23" s="8" t="n"/>
+      <c r="Z23" s="20" t="n"/>
+      <c r="AB23" s="21" t="n"/>
       <c r="AC23" s="22" t="n"/>
       <c r="AD23" s="22" t="n"/>
       <c r="AE23" s="22" t="n"/>
@@ -2193,10 +2255,11 @@
       <c r="AO23" s="22" t="n"/>
       <c r="AP23" s="22" t="n"/>
       <c r="AQ23" s="22" t="n"/>
-      <c r="AR23" s="23" t="n"/>
+      <c r="AR23" s="22" t="n"/>
+      <c r="AS23" s="23" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="62" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
@@ -2204,33 +2267,37 @@
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="9" t="n"/>
-      <c r="E24" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F24" s="40" t="n"/>
-      <c r="G24" s="40" t="n"/>
-      <c r="H24" s="40" t="n"/>
-      <c r="I24" s="40" t="n"/>
-      <c r="J24" s="40" t="n"/>
-      <c r="K24" s="40" t="n"/>
-      <c r="L24" s="40" t="n"/>
-      <c r="M24" s="40" t="n"/>
-      <c r="N24" s="40" t="n"/>
-      <c r="O24" s="64" t="n"/>
-      <c r="P24" s="65" t="n"/>
-      <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="8" t="n"/>
-      <c r="S24" s="8" t="n"/>
-      <c r="T24" s="9" t="n"/>
-      <c r="U24" s="65" t="n"/>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F24" s="62" t="n"/>
+      <c r="G24" s="62" t="n"/>
+      <c r="H24" s="62" t="n"/>
+      <c r="I24" s="62" t="n"/>
+      <c r="J24" s="62" t="n"/>
+      <c r="K24" s="62" t="n"/>
+      <c r="L24" s="62" t="n"/>
+      <c r="M24" s="63" t="n"/>
+      <c r="N24" s="62" t="n"/>
+      <c r="O24" s="62" t="n"/>
+      <c r="P24" s="62" t="n"/>
+      <c r="Q24" s="62" t="n"/>
+      <c r="R24" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S24" s="65" t="n"/>
+      <c r="T24" s="8" t="n"/>
+      <c r="U24" s="8" t="n"/>
       <c r="V24" s="8" t="n"/>
-      <c r="W24" s="20" t="n"/>
-      <c r="Y24" s="21" t="n"/>
-      <c r="Z24" s="22" t="n"/>
-      <c r="AA24" s="22" t="n"/>
-      <c r="AB24" s="22" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="65" t="n"/>
+      <c r="Y24" s="8" t="n"/>
+      <c r="Z24" s="20" t="n"/>
+      <c r="AB24" s="21" t="n"/>
       <c r="AC24" s="22" t="n"/>
       <c r="AD24" s="22" t="n"/>
       <c r="AE24" s="22" t="n"/>
@@ -2246,10 +2313,11 @@
       <c r="AO24" s="22" t="n"/>
       <c r="AP24" s="22" t="n"/>
       <c r="AQ24" s="22" t="n"/>
-      <c r="AR24" s="23" t="n"/>
+      <c r="AR24" s="22" t="n"/>
+      <c r="AS24" s="23" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="62" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>⑧</t>
         </is>
@@ -2257,33 +2325,37 @@
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="9" t="n"/>
-      <c r="E25" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F25" s="40" t="n"/>
-      <c r="G25" s="40" t="n"/>
-      <c r="H25" s="40" t="n"/>
-      <c r="I25" s="40" t="n"/>
-      <c r="J25" s="40" t="n"/>
-      <c r="K25" s="40" t="n"/>
-      <c r="L25" s="40" t="n"/>
-      <c r="M25" s="40" t="n"/>
-      <c r="N25" s="40" t="n"/>
-      <c r="O25" s="64" t="n"/>
-      <c r="P25" s="65" t="n"/>
-      <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="8" t="n"/>
-      <c r="S25" s="8" t="n"/>
-      <c r="T25" s="9" t="n"/>
-      <c r="U25" s="65" t="n"/>
+      <c r="E25" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F25" s="62" t="n"/>
+      <c r="G25" s="62" t="n"/>
+      <c r="H25" s="62" t="n"/>
+      <c r="I25" s="62" t="n"/>
+      <c r="J25" s="62" t="n"/>
+      <c r="K25" s="62" t="n"/>
+      <c r="L25" s="62" t="n"/>
+      <c r="M25" s="63" t="n"/>
+      <c r="N25" s="62" t="n"/>
+      <c r="O25" s="62" t="n"/>
+      <c r="P25" s="62" t="n"/>
+      <c r="Q25" s="62" t="n"/>
+      <c r="R25" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S25" s="65" t="n"/>
+      <c r="T25" s="8" t="n"/>
+      <c r="U25" s="8" t="n"/>
       <c r="V25" s="8" t="n"/>
-      <c r="W25" s="20" t="n"/>
-      <c r="Y25" s="21" t="n"/>
-      <c r="Z25" s="22" t="n"/>
-      <c r="AA25" s="22" t="n"/>
-      <c r="AB25" s="22" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="65" t="n"/>
+      <c r="Y25" s="8" t="n"/>
+      <c r="Z25" s="20" t="n"/>
+      <c r="AB25" s="21" t="n"/>
       <c r="AC25" s="22" t="n"/>
       <c r="AD25" s="22" t="n"/>
       <c r="AE25" s="22" t="n"/>
@@ -2299,10 +2371,11 @@
       <c r="AO25" s="22" t="n"/>
       <c r="AP25" s="22" t="n"/>
       <c r="AQ25" s="22" t="n"/>
-      <c r="AR25" s="23" t="n"/>
+      <c r="AR25" s="22" t="n"/>
+      <c r="AS25" s="23" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="62" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>⑨</t>
         </is>
@@ -2310,33 +2383,37 @@
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="9" t="n"/>
-      <c r="E26" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F26" s="40" t="n"/>
-      <c r="G26" s="40" t="n"/>
-      <c r="H26" s="40" t="n"/>
-      <c r="I26" s="40" t="n"/>
-      <c r="J26" s="40" t="n"/>
-      <c r="K26" s="40" t="n"/>
-      <c r="L26" s="40" t="n"/>
-      <c r="M26" s="40" t="n"/>
-      <c r="N26" s="40" t="n"/>
-      <c r="O26" s="64" t="n"/>
-      <c r="P26" s="65" t="n"/>
-      <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="8" t="n"/>
-      <c r="S26" s="8" t="n"/>
-      <c r="T26" s="9" t="n"/>
-      <c r="U26" s="65" t="n"/>
+      <c r="E26" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F26" s="62" t="n"/>
+      <c r="G26" s="62" t="n"/>
+      <c r="H26" s="62" t="n"/>
+      <c r="I26" s="62" t="n"/>
+      <c r="J26" s="62" t="n"/>
+      <c r="K26" s="62" t="n"/>
+      <c r="L26" s="62" t="n"/>
+      <c r="M26" s="63" t="n"/>
+      <c r="N26" s="62" t="n"/>
+      <c r="O26" s="62" t="n"/>
+      <c r="P26" s="62" t="n"/>
+      <c r="Q26" s="62" t="n"/>
+      <c r="R26" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S26" s="65" t="n"/>
+      <c r="T26" s="8" t="n"/>
+      <c r="U26" s="8" t="n"/>
       <c r="V26" s="8" t="n"/>
-      <c r="W26" s="20" t="n"/>
-      <c r="Y26" s="21" t="n"/>
-      <c r="Z26" s="22" t="n"/>
-      <c r="AA26" s="22" t="n"/>
-      <c r="AB26" s="22" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="65" t="n"/>
+      <c r="Y26" s="8" t="n"/>
+      <c r="Z26" s="20" t="n"/>
+      <c r="AB26" s="21" t="n"/>
       <c r="AC26" s="22" t="n"/>
       <c r="AD26" s="22" t="n"/>
       <c r="AE26" s="22" t="n"/>
@@ -2352,10 +2429,11 @@
       <c r="AO26" s="22" t="n"/>
       <c r="AP26" s="22" t="n"/>
       <c r="AQ26" s="22" t="n"/>
-      <c r="AR26" s="23" t="n"/>
+      <c r="AR26" s="22" t="n"/>
+      <c r="AS26" s="23" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="62" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>⑩</t>
         </is>
@@ -2363,33 +2441,37 @@
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
-      <c r="E27" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F27" s="40" t="n"/>
-      <c r="G27" s="40" t="n"/>
-      <c r="H27" s="40" t="n"/>
-      <c r="I27" s="40" t="n"/>
-      <c r="J27" s="40" t="n"/>
-      <c r="K27" s="40" t="n"/>
-      <c r="L27" s="40" t="n"/>
-      <c r="M27" s="40" t="n"/>
-      <c r="N27" s="40" t="n"/>
-      <c r="O27" s="64" t="n"/>
-      <c r="P27" s="65" t="n"/>
-      <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="8" t="n"/>
-      <c r="S27" s="8" t="n"/>
-      <c r="T27" s="9" t="n"/>
-      <c r="U27" s="65" t="n"/>
+      <c r="E27" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F27" s="62" t="n"/>
+      <c r="G27" s="62" t="n"/>
+      <c r="H27" s="62" t="n"/>
+      <c r="I27" s="62" t="n"/>
+      <c r="J27" s="62" t="n"/>
+      <c r="K27" s="62" t="n"/>
+      <c r="L27" s="62" t="n"/>
+      <c r="M27" s="63" t="n"/>
+      <c r="N27" s="62" t="n"/>
+      <c r="O27" s="62" t="n"/>
+      <c r="P27" s="62" t="n"/>
+      <c r="Q27" s="62" t="n"/>
+      <c r="R27" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S27" s="65" t="n"/>
+      <c r="T27" s="8" t="n"/>
+      <c r="U27" s="8" t="n"/>
       <c r="V27" s="8" t="n"/>
-      <c r="W27" s="20" t="n"/>
-      <c r="Y27" s="21" t="n"/>
-      <c r="Z27" s="22" t="n"/>
-      <c r="AA27" s="22" t="n"/>
-      <c r="AB27" s="22" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="65" t="n"/>
+      <c r="Y27" s="8" t="n"/>
+      <c r="Z27" s="20" t="n"/>
+      <c r="AB27" s="21" t="n"/>
       <c r="AC27" s="22" t="n"/>
       <c r="AD27" s="22" t="n"/>
       <c r="AE27" s="22" t="n"/>
@@ -2405,10 +2487,11 @@
       <c r="AO27" s="22" t="n"/>
       <c r="AP27" s="22" t="n"/>
       <c r="AQ27" s="22" t="n"/>
-      <c r="AR27" s="23" t="n"/>
+      <c r="AR27" s="22" t="n"/>
+      <c r="AS27" s="23" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="62" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>⑪</t>
         </is>
@@ -2416,33 +2499,37 @@
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="9" t="n"/>
-      <c r="E28" s="63" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="n"/>
-      <c r="G28" s="40" t="n"/>
-      <c r="H28" s="40" t="n"/>
-      <c r="I28" s="40" t="n"/>
-      <c r="J28" s="40" t="n"/>
-      <c r="K28" s="40" t="n"/>
-      <c r="L28" s="40" t="n"/>
-      <c r="M28" s="40" t="n"/>
-      <c r="N28" s="40" t="n"/>
-      <c r="O28" s="64" t="n"/>
-      <c r="P28" s="65" t="n"/>
-      <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="8" t="n"/>
-      <c r="S28" s="8" t="n"/>
-      <c r="T28" s="9" t="n"/>
-      <c r="U28" s="65" t="n"/>
+      <c r="E28" s="61" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F28" s="62" t="n"/>
+      <c r="G28" s="62" t="n"/>
+      <c r="H28" s="62" t="n"/>
+      <c r="I28" s="62" t="n"/>
+      <c r="J28" s="62" t="n"/>
+      <c r="K28" s="62" t="n"/>
+      <c r="L28" s="62" t="n"/>
+      <c r="M28" s="63" t="n"/>
+      <c r="N28" s="62" t="n"/>
+      <c r="O28" s="62" t="n"/>
+      <c r="P28" s="62" t="n"/>
+      <c r="Q28" s="62" t="n"/>
+      <c r="R28" s="64" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S28" s="65" t="n"/>
+      <c r="T28" s="8" t="n"/>
+      <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
-      <c r="W28" s="20" t="n"/>
-      <c r="Y28" s="21" t="n"/>
-      <c r="Z28" s="22" t="n"/>
-      <c r="AA28" s="22" t="n"/>
-      <c r="AB28" s="22" t="n"/>
+      <c r="W28" s="9" t="n"/>
+      <c r="X28" s="65" t="n"/>
+      <c r="Y28" s="8" t="n"/>
+      <c r="Z28" s="20" t="n"/>
+      <c r="AB28" s="21" t="n"/>
       <c r="AC28" s="22" t="n"/>
       <c r="AD28" s="22" t="n"/>
       <c r="AE28" s="22" t="n"/>
@@ -2458,7 +2545,8 @@
       <c r="AO28" s="22" t="n"/>
       <c r="AP28" s="22" t="n"/>
       <c r="AQ28" s="22" t="n"/>
-      <c r="AR28" s="23" t="n"/>
+      <c r="AR28" s="22" t="n"/>
+      <c r="AS28" s="23" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="66" t="inlineStr">
@@ -2467,154 +2555,171 @@
         </is>
       </c>
       <c r="B29" s="67" t="n"/>
-      <c r="C29" s="68" t="n"/>
-      <c r="D29" s="69" t="n"/>
-      <c r="E29" s="70" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（　　　　　）</t>
-        </is>
-      </c>
-      <c r="F29" s="58" t="n"/>
-      <c r="G29" s="58" t="n"/>
-      <c r="H29" s="58" t="n"/>
-      <c r="I29" s="58" t="n"/>
-      <c r="J29" s="58" t="n"/>
-      <c r="K29" s="58" t="n"/>
-      <c r="L29" s="58" t="n"/>
-      <c r="M29" s="58" t="n"/>
-      <c r="N29" s="58" t="n"/>
-      <c r="O29" s="71" t="n"/>
-      <c r="P29" s="72" t="n"/>
-      <c r="Q29" s="68" t="n"/>
-      <c r="R29" s="68" t="n"/>
-      <c r="S29" s="68" t="n"/>
-      <c r="T29" s="69" t="n"/>
-      <c r="U29" s="72" t="n"/>
-      <c r="V29" s="68" t="n"/>
-      <c r="W29" s="73" t="n"/>
-      <c r="Y29" s="74" t="n"/>
-      <c r="Z29" s="75" t="n"/>
-      <c r="AA29" s="75" t="n"/>
+      <c r="C29" s="56" t="n"/>
+      <c r="D29" s="68" t="n"/>
+      <c r="E29" s="69" t="inlineStr">
+        <is>
+          <t>手すり　段差の解消　その他（</t>
+        </is>
+      </c>
+      <c r="F29" s="70" t="n"/>
+      <c r="G29" s="70" t="n"/>
+      <c r="H29" s="70" t="n"/>
+      <c r="I29" s="70" t="n"/>
+      <c r="J29" s="70" t="n"/>
+      <c r="K29" s="70" t="n"/>
+      <c r="L29" s="70" t="n"/>
+      <c r="M29" s="71" t="n"/>
+      <c r="N29" s="70" t="n"/>
+      <c r="O29" s="70" t="n"/>
+      <c r="P29" s="70" t="n"/>
+      <c r="Q29" s="70" t="n"/>
+      <c r="R29" s="72" t="inlineStr">
+        <is>
+          <t>）</t>
+        </is>
+      </c>
+      <c r="S29" s="73" t="n"/>
+      <c r="T29" s="56" t="n"/>
+      <c r="U29" s="56" t="n"/>
+      <c r="V29" s="56" t="n"/>
+      <c r="W29" s="68" t="n"/>
+      <c r="X29" s="73" t="n"/>
+      <c r="Y29" s="56" t="n"/>
+      <c r="Z29" s="74" t="n"/>
       <c r="AB29" s="75" t="n"/>
-      <c r="AC29" s="75" t="n"/>
-      <c r="AD29" s="75" t="n"/>
-      <c r="AE29" s="75" t="n"/>
-      <c r="AF29" s="75" t="n"/>
-      <c r="AG29" s="75" t="n"/>
-      <c r="AH29" s="75" t="n"/>
-      <c r="AI29" s="75" t="n"/>
-      <c r="AJ29" s="75" t="n"/>
-      <c r="AK29" s="75" t="n"/>
-      <c r="AL29" s="75" t="n"/>
-      <c r="AM29" s="75" t="n"/>
-      <c r="AN29" s="75" t="n"/>
-      <c r="AO29" s="75" t="n"/>
-      <c r="AP29" s="75" t="n"/>
-      <c r="AQ29" s="75" t="n"/>
+      <c r="AC29" s="76" t="n"/>
+      <c r="AD29" s="76" t="n"/>
+      <c r="AE29" s="76" t="n"/>
+      <c r="AF29" s="76" t="n"/>
+      <c r="AG29" s="76" t="n"/>
+      <c r="AH29" s="76" t="n"/>
+      <c r="AI29" s="76" t="n"/>
+      <c r="AJ29" s="76" t="n"/>
+      <c r="AK29" s="76" t="n"/>
+      <c r="AL29" s="76" t="n"/>
+      <c r="AM29" s="76" t="n"/>
+      <c r="AN29" s="76" t="n"/>
+      <c r="AO29" s="76" t="n"/>
+      <c r="AP29" s="76" t="n"/>
+      <c r="AQ29" s="76" t="n"/>
       <c r="AR29" s="76" t="n"/>
+      <c r="AS29" s="77" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="98">
+  <mergeCells count="110">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="P26:T26"/>
-    <mergeCell ref="Y4:AR4"/>
-    <mergeCell ref="E24:O24"/>
+    <mergeCell ref="U11:Z11"/>
+    <mergeCell ref="E18:L18"/>
+    <mergeCell ref="AB4:AS4"/>
+    <mergeCell ref="E4:Y4"/>
+    <mergeCell ref="R6:Z6"/>
+    <mergeCell ref="X18:Z18"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="G8:Z8"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="E28:L28"/>
+    <mergeCell ref="S23:W23"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E27:O27"/>
-    <mergeCell ref="P28:T28"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="E13:W13"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="E22:O22"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="E4:V4"/>
-    <mergeCell ref="E21:O21"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="X22:Z22"/>
+    <mergeCell ref="S24:W24"/>
+    <mergeCell ref="N12:Z12"/>
+    <mergeCell ref="M27:Q27"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="A1:Z2"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="S25:W25"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E24:L24"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="H11:P11"/>
-    <mergeCell ref="H9:O9"/>
-    <mergeCell ref="E23:O23"/>
-    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="S17:W17"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="G8:W8"/>
+    <mergeCell ref="M20:Q20"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="P6:W6"/>
+    <mergeCell ref="E19:L19"/>
+    <mergeCell ref="A16:Z16"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="P27:T27"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="S28:W28"/>
+    <mergeCell ref="AJ2:AS2"/>
+    <mergeCell ref="X25:Z25"/>
     <mergeCell ref="M14:O14"/>
-    <mergeCell ref="P17:T17"/>
-    <mergeCell ref="U26:W26"/>
-    <mergeCell ref="N12:W12"/>
-    <mergeCell ref="P19:T19"/>
-    <mergeCell ref="E26:O26"/>
+    <mergeCell ref="H11:R11"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="Q10:Z10"/>
     <mergeCell ref="J14:L14"/>
-    <mergeCell ref="A1:W2"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="E25:O25"/>
+    <mergeCell ref="M29:Q29"/>
+    <mergeCell ref="M23:Q23"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E18:O18"/>
+    <mergeCell ref="E22:L22"/>
+    <mergeCell ref="S26:W26"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="P20:T20"/>
-    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="E21:L21"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="P29:T29"/>
+    <mergeCell ref="Q14:Y14"/>
     <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H10:O10"/>
-    <mergeCell ref="P22:T22"/>
-    <mergeCell ref="P9:W9"/>
-    <mergeCell ref="U28:W28"/>
+    <mergeCell ref="E23:L23"/>
+    <mergeCell ref="S18:W18"/>
+    <mergeCell ref="S27:W27"/>
+    <mergeCell ref="X24:Z24"/>
+    <mergeCell ref="E17:R17"/>
     <mergeCell ref="E11:G11"/>
-    <mergeCell ref="E20:O20"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="P21:T21"/>
-    <mergeCell ref="E29:O29"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="P23:T23"/>
-    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="X26:Z26"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="E5:Z5"/>
+    <mergeCell ref="M28:Q28"/>
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="G7:P7"/>
-    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="E27:L27"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="P18:T18"/>
-    <mergeCell ref="G6:M6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E13:Z13"/>
+    <mergeCell ref="S20:W20"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="S29:W29"/>
+    <mergeCell ref="S22:W22"/>
     <mergeCell ref="A14:D14"/>
+    <mergeCell ref="G7:R7"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="X28:Z28"/>
+    <mergeCell ref="Q9:Z9"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="P25:T25"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="G6:O6"/>
     <mergeCell ref="A7:D8"/>
-    <mergeCell ref="P10:W10"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="AI2:AR2"/>
-    <mergeCell ref="E17:O17"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="S7:W7"/>
-    <mergeCell ref="E19:O19"/>
+    <mergeCell ref="U7:Z7"/>
+    <mergeCell ref="X20:Z20"/>
+    <mergeCell ref="E20:L20"/>
+    <mergeCell ref="X29:Z29"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="E29:L29"/>
     <mergeCell ref="H12:J12"/>
-    <mergeCell ref="E28:O28"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E5:W5"/>
-    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="S19:W19"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="E26:L26"/>
+    <mergeCell ref="H10:P10"/>
     <mergeCell ref="A9:D10"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="P24:T24"/>
-    <mergeCell ref="P14:W14"/>
+    <mergeCell ref="H9:P9"/>
+    <mergeCell ref="M19:Q19"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:AR29">
+  <conditionalFormatting sqref="A1:AS29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(A1,1)="■"</formula>
     </cfRule>
@@ -2641,10 +2746,10 @@
     <dataValidation sqref="M14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□その他,■その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6 G8 P6 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
+    <dataValidation sqref="G6 G8 R6 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/住宅改修_現地調査アセスメントシート.xlsx
+++ b/住宅改修_現地調査アセスメントシート.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アセスメントシート" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'アセスメントシート'!$A$1:$CK$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'アセスメントシート'!$A$1:$CK$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,7 +127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -320,6 +320,70 @@
       </bottom>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00595959"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00595959"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00404040"/>
+      </left>
+      <top style="thin">
+        <color rgb="00595959"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00595959"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00595959"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <top style="thin">
+        <color rgb="00595959"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="00404040"/>
+      </right>
+      <top style="thin">
+        <color rgb="00595959"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="medium">
+        <color rgb="00404040"/>
+      </right>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="00E4E4E4"/>
       </left>
@@ -333,16 +397,11 @@
         <color rgb="00E4E4E4"/>
       </bottom>
     </border>
-    <border>
-      <right style="medium">
-        <color rgb="00404040"/>
-      </right>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -397,9 +456,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -497,14 +556,59 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -887,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CK55"/>
+  <dimension ref="A1:CK61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.6796875" customWidth="1" min="1" max="1"/>
@@ -984,7 +1088,7 @@
     <row r="1" ht="9" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>住宅改修 現地調査アセスメントシート</t>
+          <t>家屋調査　アセスメントシート</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5474,58 +5578,58 @@
       <c r="CK50" s="38" t="n"/>
     </row>
     <row r="51" ht="9" customHeight="1">
-      <c r="A51" s="99" t="n"/>
-      <c r="B51" s="100" t="n"/>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="14" t="n"/>
-      <c r="H51" s="15" t="n"/>
-      <c r="I51" s="101" t="n"/>
-      <c r="J51" s="102" t="n"/>
-      <c r="K51" s="102" t="n"/>
-      <c r="L51" s="102" t="n"/>
-      <c r="M51" s="102" t="n"/>
-      <c r="N51" s="102" t="n"/>
-      <c r="O51" s="102" t="n"/>
-      <c r="P51" s="102" t="n"/>
-      <c r="Q51" s="102" t="n"/>
-      <c r="R51" s="102" t="n"/>
-      <c r="S51" s="102" t="n"/>
-      <c r="T51" s="102" t="n"/>
-      <c r="U51" s="102" t="n"/>
-      <c r="V51" s="102" t="n"/>
-      <c r="W51" s="102" t="n"/>
-      <c r="X51" s="102" t="n"/>
-      <c r="Y51" s="102" t="n"/>
-      <c r="Z51" s="102" t="n"/>
-      <c r="AA51" s="102" t="n"/>
-      <c r="AB51" s="102" t="n"/>
-      <c r="AC51" s="102" t="n"/>
-      <c r="AD51" s="102" t="n"/>
-      <c r="AE51" s="102" t="n"/>
-      <c r="AF51" s="102" t="n"/>
-      <c r="AG51" s="102" t="n"/>
-      <c r="AH51" s="102" t="n"/>
-      <c r="AI51" s="102" t="n"/>
-      <c r="AJ51" s="103" t="n"/>
-      <c r="AK51" s="13" t="n"/>
-      <c r="AL51" s="14" t="n"/>
-      <c r="AM51" s="14" t="n"/>
-      <c r="AN51" s="14" t="n"/>
-      <c r="AO51" s="14" t="n"/>
-      <c r="AP51" s="14" t="n"/>
-      <c r="AQ51" s="14" t="n"/>
-      <c r="AR51" s="14" t="n"/>
-      <c r="AS51" s="14" t="n"/>
-      <c r="AT51" s="15" t="n"/>
-      <c r="AU51" s="13" t="n"/>
-      <c r="AV51" s="14" t="n"/>
-      <c r="AW51" s="14" t="n"/>
-      <c r="AX51" s="14" t="n"/>
-      <c r="AY51" s="14" t="n"/>
-      <c r="AZ51" s="39" t="n"/>
+      <c r="A51" s="104" t="n"/>
+      <c r="B51" s="105" t="n"/>
+      <c r="C51" s="106" t="n"/>
+      <c r="D51" s="107" t="n"/>
+      <c r="E51" s="107" t="n"/>
+      <c r="F51" s="107" t="n"/>
+      <c r="G51" s="107" t="n"/>
+      <c r="H51" s="108" t="n"/>
+      <c r="I51" s="109" t="n"/>
+      <c r="J51" s="110" t="n"/>
+      <c r="K51" s="110" t="n"/>
+      <c r="L51" s="110" t="n"/>
+      <c r="M51" s="110" t="n"/>
+      <c r="N51" s="110" t="n"/>
+      <c r="O51" s="110" t="n"/>
+      <c r="P51" s="110" t="n"/>
+      <c r="Q51" s="110" t="n"/>
+      <c r="R51" s="110" t="n"/>
+      <c r="S51" s="110" t="n"/>
+      <c r="T51" s="110" t="n"/>
+      <c r="U51" s="110" t="n"/>
+      <c r="V51" s="110" t="n"/>
+      <c r="W51" s="110" t="n"/>
+      <c r="X51" s="110" t="n"/>
+      <c r="Y51" s="110" t="n"/>
+      <c r="Z51" s="110" t="n"/>
+      <c r="AA51" s="110" t="n"/>
+      <c r="AB51" s="110" t="n"/>
+      <c r="AC51" s="110" t="n"/>
+      <c r="AD51" s="110" t="n"/>
+      <c r="AE51" s="110" t="n"/>
+      <c r="AF51" s="110" t="n"/>
+      <c r="AG51" s="110" t="n"/>
+      <c r="AH51" s="110" t="n"/>
+      <c r="AI51" s="110" t="n"/>
+      <c r="AJ51" s="111" t="n"/>
+      <c r="AK51" s="106" t="n"/>
+      <c r="AL51" s="107" t="n"/>
+      <c r="AM51" s="107" t="n"/>
+      <c r="AN51" s="107" t="n"/>
+      <c r="AO51" s="107" t="n"/>
+      <c r="AP51" s="107" t="n"/>
+      <c r="AQ51" s="107" t="n"/>
+      <c r="AR51" s="107" t="n"/>
+      <c r="AS51" s="107" t="n"/>
+      <c r="AT51" s="108" t="n"/>
+      <c r="AU51" s="106" t="n"/>
+      <c r="AV51" s="107" t="n"/>
+      <c r="AW51" s="107" t="n"/>
+      <c r="AX51" s="107" t="n"/>
+      <c r="AY51" s="107" t="n"/>
+      <c r="AZ51" s="112" t="n"/>
       <c r="BB51" s="36" t="n"/>
       <c r="BC51" s="40" t="n"/>
       <c r="BD51" s="40" t="n"/>
@@ -5564,70 +5668,90 @@
       <c r="CK51" s="38" t="n"/>
     </row>
     <row r="52" ht="9" customHeight="1">
-      <c r="A52" s="91" t="inlineStr">
-        <is>
-          <t>⑪</t>
-        </is>
-      </c>
-      <c r="B52" s="92" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="93" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（</t>
-        </is>
-      </c>
-      <c r="J52" s="94" t="n"/>
-      <c r="K52" s="94" t="n"/>
-      <c r="L52" s="94" t="n"/>
-      <c r="M52" s="94" t="n"/>
-      <c r="N52" s="94" t="n"/>
-      <c r="O52" s="94" t="n"/>
-      <c r="P52" s="94" t="n"/>
-      <c r="Q52" s="94" t="n"/>
-      <c r="R52" s="94" t="n"/>
-      <c r="S52" s="94" t="n"/>
-      <c r="T52" s="94" t="n"/>
-      <c r="U52" s="94" t="n"/>
-      <c r="V52" s="94" t="n"/>
-      <c r="W52" s="94" t="n"/>
-      <c r="X52" s="94" t="n"/>
-      <c r="Y52" s="95" t="n"/>
-      <c r="Z52" s="94" t="n"/>
-      <c r="AA52" s="94" t="n"/>
-      <c r="AB52" s="94" t="n"/>
-      <c r="AC52" s="94" t="n"/>
-      <c r="AD52" s="94" t="n"/>
-      <c r="AE52" s="94" t="n"/>
-      <c r="AF52" s="94" t="n"/>
-      <c r="AG52" s="94" t="n"/>
-      <c r="AH52" s="94" t="n"/>
-      <c r="AI52" s="96" t="inlineStr">
-        <is>
-          <t>）</t>
-        </is>
-      </c>
-      <c r="AJ52" s="97" t="n"/>
-      <c r="AK52" s="98" t="n"/>
-      <c r="AL52" s="7" t="n"/>
-      <c r="AM52" s="7" t="n"/>
-      <c r="AN52" s="7" t="n"/>
-      <c r="AO52" s="7" t="n"/>
-      <c r="AP52" s="7" t="n"/>
-      <c r="AQ52" s="7" t="n"/>
-      <c r="AR52" s="7" t="n"/>
-      <c r="AS52" s="7" t="n"/>
-      <c r="AT52" s="8" t="n"/>
-      <c r="AU52" s="98" t="n"/>
-      <c r="AV52" s="7" t="n"/>
-      <c r="AW52" s="7" t="n"/>
-      <c r="AX52" s="7" t="n"/>
-      <c r="AY52" s="7" t="n"/>
-      <c r="AZ52" s="35" t="n"/>
+      <c r="A52" s="113" t="inlineStr">
+        <is>
+          <t>特定福祉用具</t>
+        </is>
+      </c>
+      <c r="B52" s="114" t="n"/>
+      <c r="C52" s="114" t="n"/>
+      <c r="D52" s="114" t="n"/>
+      <c r="E52" s="114" t="n"/>
+      <c r="F52" s="114" t="n"/>
+      <c r="G52" s="114" t="n"/>
+      <c r="H52" s="115" t="n"/>
+      <c r="I52" s="116" t="inlineStr">
+        <is>
+          <t>腰掛便座</t>
+        </is>
+      </c>
+      <c r="J52" s="117" t="n"/>
+      <c r="K52" s="117" t="n"/>
+      <c r="L52" s="117" t="n"/>
+      <c r="M52" s="117" t="n"/>
+      <c r="N52" s="117" t="n"/>
+      <c r="O52" s="117" t="n"/>
+      <c r="P52" s="118" t="inlineStr">
+        <is>
+          <t>入浴補助用具</t>
+        </is>
+      </c>
+      <c r="Q52" s="117" t="n"/>
+      <c r="R52" s="117" t="n"/>
+      <c r="S52" s="117" t="n"/>
+      <c r="T52" s="117" t="n"/>
+      <c r="U52" s="117" t="n"/>
+      <c r="V52" s="117" t="n"/>
+      <c r="W52" s="117" t="n"/>
+      <c r="X52" s="118" t="inlineStr">
+        <is>
+          <t>簡易浴槽</t>
+        </is>
+      </c>
+      <c r="Y52" s="117" t="n"/>
+      <c r="Z52" s="117" t="n"/>
+      <c r="AA52" s="117" t="n"/>
+      <c r="AB52" s="117" t="n"/>
+      <c r="AC52" s="117" t="n"/>
+      <c r="AD52" s="117" t="n"/>
+      <c r="AE52" s="118" t="inlineStr">
+        <is>
+          <t>固定用スロープ</t>
+        </is>
+      </c>
+      <c r="AF52" s="117" t="n"/>
+      <c r="AG52" s="117" t="n"/>
+      <c r="AH52" s="117" t="n"/>
+      <c r="AI52" s="117" t="n"/>
+      <c r="AJ52" s="117" t="n"/>
+      <c r="AK52" s="117" t="n"/>
+      <c r="AL52" s="117" t="n"/>
+      <c r="AM52" s="117" t="n"/>
+      <c r="AN52" s="118" t="inlineStr">
+        <is>
+          <t>歩行器</t>
+        </is>
+      </c>
+      <c r="AO52" s="117" t="n"/>
+      <c r="AP52" s="117" t="n"/>
+      <c r="AQ52" s="117" t="n"/>
+      <c r="AR52" s="117" t="n"/>
+      <c r="AS52" s="118" t="inlineStr">
+        <is>
+          <t>杖</t>
+        </is>
+      </c>
+      <c r="AT52" s="117" t="n"/>
+      <c r="AU52" s="117" t="n"/>
+      <c r="AV52" s="118" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="AW52" s="117" t="n"/>
+      <c r="AX52" s="117" t="n"/>
+      <c r="AY52" s="117" t="n"/>
+      <c r="AZ52" s="119" t="n"/>
       <c r="BB52" s="36" t="n"/>
       <c r="BC52" s="40" t="n"/>
       <c r="BD52" s="40" t="n"/>
@@ -5666,14 +5790,14 @@
       <c r="CK52" s="38" t="n"/>
     </row>
     <row r="53" ht="9" customHeight="1">
-      <c r="A53" s="99" t="n"/>
-      <c r="B53" s="100" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="14" t="n"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="14" t="n"/>
-      <c r="H53" s="15" t="n"/>
+      <c r="A53" s="120" t="n"/>
+      <c r="B53" s="45" t="n"/>
+      <c r="C53" s="45" t="n"/>
+      <c r="D53" s="45" t="n"/>
+      <c r="E53" s="45" t="n"/>
+      <c r="F53" s="45" t="n"/>
+      <c r="G53" s="45" t="n"/>
+      <c r="H53" s="46" t="n"/>
       <c r="I53" s="101" t="n"/>
       <c r="J53" s="102" t="n"/>
       <c r="K53" s="102" t="n"/>
@@ -5701,23 +5825,23 @@
       <c r="AG53" s="102" t="n"/>
       <c r="AH53" s="102" t="n"/>
       <c r="AI53" s="102" t="n"/>
-      <c r="AJ53" s="103" t="n"/>
-      <c r="AK53" s="13" t="n"/>
-      <c r="AL53" s="14" t="n"/>
-      <c r="AM53" s="14" t="n"/>
-      <c r="AN53" s="14" t="n"/>
-      <c r="AO53" s="14" t="n"/>
-      <c r="AP53" s="14" t="n"/>
-      <c r="AQ53" s="14" t="n"/>
-      <c r="AR53" s="14" t="n"/>
-      <c r="AS53" s="14" t="n"/>
-      <c r="AT53" s="15" t="n"/>
-      <c r="AU53" s="13" t="n"/>
-      <c r="AV53" s="14" t="n"/>
-      <c r="AW53" s="14" t="n"/>
-      <c r="AX53" s="14" t="n"/>
-      <c r="AY53" s="14" t="n"/>
-      <c r="AZ53" s="39" t="n"/>
+      <c r="AJ53" s="102" t="n"/>
+      <c r="AK53" s="102" t="n"/>
+      <c r="AL53" s="102" t="n"/>
+      <c r="AM53" s="102" t="n"/>
+      <c r="AN53" s="102" t="n"/>
+      <c r="AO53" s="102" t="n"/>
+      <c r="AP53" s="102" t="n"/>
+      <c r="AQ53" s="102" t="n"/>
+      <c r="AR53" s="102" t="n"/>
+      <c r="AS53" s="102" t="n"/>
+      <c r="AT53" s="102" t="n"/>
+      <c r="AU53" s="102" t="n"/>
+      <c r="AV53" s="102" t="n"/>
+      <c r="AW53" s="102" t="n"/>
+      <c r="AX53" s="102" t="n"/>
+      <c r="AY53" s="102" t="n"/>
+      <c r="AZ53" s="121" t="n"/>
       <c r="BB53" s="36" t="n"/>
       <c r="BC53" s="40" t="n"/>
       <c r="BD53" s="40" t="n"/>
@@ -5756,23 +5880,19 @@
       <c r="CK53" s="38" t="n"/>
     </row>
     <row r="54" ht="9" customHeight="1">
-      <c r="A54" s="91" t="inlineStr">
-        <is>
-          <t>⑫</t>
-        </is>
-      </c>
-      <c r="B54" s="92" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="93" t="inlineStr">
-        <is>
-          <t>手すり　段差の解消　その他（</t>
-        </is>
-      </c>
+      <c r="A54" s="122" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="n"/>
+      <c r="C54" s="42" t="n"/>
+      <c r="D54" s="42" t="n"/>
+      <c r="E54" s="42" t="n"/>
+      <c r="F54" s="42" t="n"/>
+      <c r="G54" s="42" t="n"/>
+      <c r="H54" s="43" t="n"/>
+      <c r="I54" s="123" t="n"/>
       <c r="J54" s="94" t="n"/>
       <c r="K54" s="94" t="n"/>
       <c r="L54" s="94" t="n"/>
@@ -5788,7 +5908,7 @@
       <c r="V54" s="94" t="n"/>
       <c r="W54" s="94" t="n"/>
       <c r="X54" s="94" t="n"/>
-      <c r="Y54" s="95" t="n"/>
+      <c r="Y54" s="94" t="n"/>
       <c r="Z54" s="94" t="n"/>
       <c r="AA54" s="94" t="n"/>
       <c r="AB54" s="94" t="n"/>
@@ -5798,28 +5918,24 @@
       <c r="AF54" s="94" t="n"/>
       <c r="AG54" s="94" t="n"/>
       <c r="AH54" s="94" t="n"/>
-      <c r="AI54" s="96" t="inlineStr">
-        <is>
-          <t>）</t>
-        </is>
-      </c>
-      <c r="AJ54" s="97" t="n"/>
-      <c r="AK54" s="98" t="n"/>
-      <c r="AL54" s="7" t="n"/>
-      <c r="AM54" s="7" t="n"/>
-      <c r="AN54" s="7" t="n"/>
-      <c r="AO54" s="7" t="n"/>
-      <c r="AP54" s="7" t="n"/>
-      <c r="AQ54" s="7" t="n"/>
-      <c r="AR54" s="7" t="n"/>
-      <c r="AS54" s="7" t="n"/>
-      <c r="AT54" s="8" t="n"/>
-      <c r="AU54" s="98" t="n"/>
-      <c r="AV54" s="7" t="n"/>
-      <c r="AW54" s="7" t="n"/>
-      <c r="AX54" s="7" t="n"/>
-      <c r="AY54" s="7" t="n"/>
-      <c r="AZ54" s="35" t="n"/>
+      <c r="AI54" s="94" t="n"/>
+      <c r="AJ54" s="94" t="n"/>
+      <c r="AK54" s="94" t="n"/>
+      <c r="AL54" s="94" t="n"/>
+      <c r="AM54" s="94" t="n"/>
+      <c r="AN54" s="94" t="n"/>
+      <c r="AO54" s="94" t="n"/>
+      <c r="AP54" s="94" t="n"/>
+      <c r="AQ54" s="94" t="n"/>
+      <c r="AR54" s="94" t="n"/>
+      <c r="AS54" s="94" t="n"/>
+      <c r="AT54" s="94" t="n"/>
+      <c r="AU54" s="94" t="n"/>
+      <c r="AV54" s="94" t="n"/>
+      <c r="AW54" s="94" t="n"/>
+      <c r="AX54" s="94" t="n"/>
+      <c r="AY54" s="94" t="n"/>
+      <c r="AZ54" s="124" t="n"/>
       <c r="BB54" s="36" t="n"/>
       <c r="BC54" s="40" t="n"/>
       <c r="BD54" s="40" t="n"/>
@@ -5858,120 +5974,719 @@
       <c r="CK54" s="38" t="n"/>
     </row>
     <row r="55" ht="9" customHeight="1">
-      <c r="A55" s="104" t="n"/>
-      <c r="B55" s="105" t="n"/>
-      <c r="C55" s="106" t="n"/>
-      <c r="D55" s="83" t="n"/>
-      <c r="E55" s="83" t="n"/>
-      <c r="F55" s="83" t="n"/>
-      <c r="G55" s="83" t="n"/>
-      <c r="H55" s="107" t="n"/>
-      <c r="I55" s="108" t="n"/>
-      <c r="J55" s="109" t="n"/>
-      <c r="K55" s="109" t="n"/>
-      <c r="L55" s="109" t="n"/>
-      <c r="M55" s="109" t="n"/>
-      <c r="N55" s="109" t="n"/>
-      <c r="O55" s="109" t="n"/>
-      <c r="P55" s="109" t="n"/>
-      <c r="Q55" s="109" t="n"/>
-      <c r="R55" s="109" t="n"/>
-      <c r="S55" s="109" t="n"/>
-      <c r="T55" s="109" t="n"/>
-      <c r="U55" s="109" t="n"/>
-      <c r="V55" s="109" t="n"/>
-      <c r="W55" s="109" t="n"/>
-      <c r="X55" s="109" t="n"/>
-      <c r="Y55" s="109" t="n"/>
-      <c r="Z55" s="109" t="n"/>
-      <c r="AA55" s="109" t="n"/>
-      <c r="AB55" s="109" t="n"/>
-      <c r="AC55" s="109" t="n"/>
-      <c r="AD55" s="109" t="n"/>
-      <c r="AE55" s="109" t="n"/>
-      <c r="AF55" s="109" t="n"/>
-      <c r="AG55" s="109" t="n"/>
-      <c r="AH55" s="109" t="n"/>
-      <c r="AI55" s="109" t="n"/>
+      <c r="A55" s="125" t="n"/>
+      <c r="B55" s="126" t="n"/>
+      <c r="C55" s="126" t="n"/>
+      <c r="D55" s="126" t="n"/>
+      <c r="E55" s="126" t="n"/>
+      <c r="F55" s="126" t="n"/>
+      <c r="G55" s="126" t="n"/>
+      <c r="H55" s="127" t="n"/>
+      <c r="I55" s="109" t="n"/>
+      <c r="J55" s="110" t="n"/>
+      <c r="K55" s="110" t="n"/>
+      <c r="L55" s="110" t="n"/>
+      <c r="M55" s="110" t="n"/>
+      <c r="N55" s="110" t="n"/>
+      <c r="O55" s="110" t="n"/>
+      <c r="P55" s="110" t="n"/>
+      <c r="Q55" s="110" t="n"/>
+      <c r="R55" s="110" t="n"/>
+      <c r="S55" s="110" t="n"/>
+      <c r="T55" s="110" t="n"/>
+      <c r="U55" s="110" t="n"/>
+      <c r="V55" s="110" t="n"/>
+      <c r="W55" s="110" t="n"/>
+      <c r="X55" s="110" t="n"/>
+      <c r="Y55" s="110" t="n"/>
+      <c r="Z55" s="110" t="n"/>
+      <c r="AA55" s="110" t="n"/>
+      <c r="AB55" s="110" t="n"/>
+      <c r="AC55" s="110" t="n"/>
+      <c r="AD55" s="110" t="n"/>
+      <c r="AE55" s="110" t="n"/>
+      <c r="AF55" s="110" t="n"/>
+      <c r="AG55" s="110" t="n"/>
+      <c r="AH55" s="110" t="n"/>
+      <c r="AI55" s="110" t="n"/>
       <c r="AJ55" s="110" t="n"/>
-      <c r="AK55" s="106" t="n"/>
-      <c r="AL55" s="83" t="n"/>
-      <c r="AM55" s="83" t="n"/>
-      <c r="AN55" s="83" t="n"/>
-      <c r="AO55" s="83" t="n"/>
-      <c r="AP55" s="83" t="n"/>
-      <c r="AQ55" s="83" t="n"/>
-      <c r="AR55" s="83" t="n"/>
-      <c r="AS55" s="83" t="n"/>
-      <c r="AT55" s="107" t="n"/>
-      <c r="AU55" s="106" t="n"/>
-      <c r="AV55" s="83" t="n"/>
-      <c r="AW55" s="83" t="n"/>
-      <c r="AX55" s="83" t="n"/>
-      <c r="AY55" s="83" t="n"/>
-      <c r="AZ55" s="111" t="n"/>
-      <c r="BB55" s="112" t="n"/>
-      <c r="BC55" s="113" t="n"/>
-      <c r="BD55" s="113" t="n"/>
-      <c r="BE55" s="113" t="n"/>
-      <c r="BF55" s="113" t="n"/>
-      <c r="BG55" s="113" t="n"/>
-      <c r="BH55" s="113" t="n"/>
-      <c r="BI55" s="113" t="n"/>
-      <c r="BJ55" s="113" t="n"/>
-      <c r="BK55" s="113" t="n"/>
-      <c r="BL55" s="113" t="n"/>
-      <c r="BM55" s="113" t="n"/>
-      <c r="BN55" s="113" t="n"/>
-      <c r="BO55" s="113" t="n"/>
-      <c r="BP55" s="113" t="n"/>
-      <c r="BQ55" s="113" t="n"/>
-      <c r="BR55" s="113" t="n"/>
-      <c r="BS55" s="113" t="n"/>
-      <c r="BT55" s="113" t="n"/>
-      <c r="BU55" s="113" t="n"/>
-      <c r="BV55" s="113" t="n"/>
-      <c r="BW55" s="113" t="n"/>
-      <c r="BX55" s="113" t="n"/>
-      <c r="BY55" s="113" t="n"/>
-      <c r="BZ55" s="113" t="n"/>
-      <c r="CA55" s="113" t="n"/>
-      <c r="CB55" s="113" t="n"/>
-      <c r="CC55" s="113" t="n"/>
-      <c r="CD55" s="113" t="n"/>
-      <c r="CE55" s="113" t="n"/>
-      <c r="CF55" s="113" t="n"/>
-      <c r="CG55" s="113" t="n"/>
-      <c r="CH55" s="113" t="n"/>
-      <c r="CI55" s="113" t="n"/>
-      <c r="CJ55" s="113" t="n"/>
-      <c r="CK55" s="114" t="n"/>
+      <c r="AK55" s="110" t="n"/>
+      <c r="AL55" s="110" t="n"/>
+      <c r="AM55" s="110" t="n"/>
+      <c r="AN55" s="110" t="n"/>
+      <c r="AO55" s="110" t="n"/>
+      <c r="AP55" s="110" t="n"/>
+      <c r="AQ55" s="110" t="n"/>
+      <c r="AR55" s="110" t="n"/>
+      <c r="AS55" s="110" t="n"/>
+      <c r="AT55" s="110" t="n"/>
+      <c r="AU55" s="110" t="n"/>
+      <c r="AV55" s="110" t="n"/>
+      <c r="AW55" s="110" t="n"/>
+      <c r="AX55" s="110" t="n"/>
+      <c r="AY55" s="110" t="n"/>
+      <c r="AZ55" s="128" t="n"/>
+      <c r="BB55" s="36" t="n"/>
+      <c r="BC55" s="40" t="n"/>
+      <c r="BD55" s="40" t="n"/>
+      <c r="BE55" s="40" t="n"/>
+      <c r="BF55" s="40" t="n"/>
+      <c r="BG55" s="40" t="n"/>
+      <c r="BH55" s="40" t="n"/>
+      <c r="BI55" s="40" t="n"/>
+      <c r="BJ55" s="40" t="n"/>
+      <c r="BK55" s="40" t="n"/>
+      <c r="BL55" s="40" t="n"/>
+      <c r="BM55" s="40" t="n"/>
+      <c r="BN55" s="40" t="n"/>
+      <c r="BO55" s="40" t="n"/>
+      <c r="BP55" s="40" t="n"/>
+      <c r="BQ55" s="40" t="n"/>
+      <c r="BR55" s="40" t="n"/>
+      <c r="BS55" s="40" t="n"/>
+      <c r="BT55" s="40" t="n"/>
+      <c r="BU55" s="40" t="n"/>
+      <c r="BV55" s="40" t="n"/>
+      <c r="BW55" s="40" t="n"/>
+      <c r="BX55" s="40" t="n"/>
+      <c r="BY55" s="40" t="n"/>
+      <c r="BZ55" s="40" t="n"/>
+      <c r="CA55" s="40" t="n"/>
+      <c r="CB55" s="40" t="n"/>
+      <c r="CC55" s="40" t="n"/>
+      <c r="CD55" s="40" t="n"/>
+      <c r="CE55" s="40" t="n"/>
+      <c r="CF55" s="40" t="n"/>
+      <c r="CG55" s="40" t="n"/>
+      <c r="CH55" s="40" t="n"/>
+      <c r="CI55" s="40" t="n"/>
+      <c r="CJ55" s="40" t="n"/>
+      <c r="CK55" s="38" t="n"/>
+    </row>
+    <row r="56" ht="9" customHeight="1">
+      <c r="A56" s="113" t="inlineStr">
+        <is>
+          <t>レンタル商品</t>
+        </is>
+      </c>
+      <c r="B56" s="114" t="n"/>
+      <c r="C56" s="114" t="n"/>
+      <c r="D56" s="114" t="n"/>
+      <c r="E56" s="114" t="n"/>
+      <c r="F56" s="114" t="n"/>
+      <c r="G56" s="114" t="n"/>
+      <c r="H56" s="115" t="n"/>
+      <c r="I56" s="116" t="inlineStr">
+        <is>
+          <t>車いす</t>
+        </is>
+      </c>
+      <c r="J56" s="117" t="n"/>
+      <c r="K56" s="117" t="n"/>
+      <c r="L56" s="117" t="n"/>
+      <c r="M56" s="117" t="n"/>
+      <c r="N56" s="118" t="inlineStr">
+        <is>
+          <t>車いす付属品</t>
+        </is>
+      </c>
+      <c r="O56" s="117" t="n"/>
+      <c r="P56" s="117" t="n"/>
+      <c r="Q56" s="117" t="n"/>
+      <c r="R56" s="117" t="n"/>
+      <c r="S56" s="117" t="n"/>
+      <c r="T56" s="117" t="n"/>
+      <c r="U56" s="117" t="n"/>
+      <c r="V56" s="118" t="inlineStr">
+        <is>
+          <t>特殊寝台</t>
+        </is>
+      </c>
+      <c r="W56" s="117" t="n"/>
+      <c r="X56" s="117" t="n"/>
+      <c r="Y56" s="117" t="n"/>
+      <c r="Z56" s="117" t="n"/>
+      <c r="AA56" s="117" t="n"/>
+      <c r="AB56" s="118" t="inlineStr">
+        <is>
+          <t>特殊寝台付属品</t>
+        </is>
+      </c>
+      <c r="AC56" s="117" t="n"/>
+      <c r="AD56" s="117" t="n"/>
+      <c r="AE56" s="117" t="n"/>
+      <c r="AF56" s="117" t="n"/>
+      <c r="AG56" s="117" t="n"/>
+      <c r="AH56" s="117" t="n"/>
+      <c r="AI56" s="117" t="n"/>
+      <c r="AJ56" s="117" t="n"/>
+      <c r="AK56" s="118" t="inlineStr">
+        <is>
+          <t>床ずれ防止用具</t>
+        </is>
+      </c>
+      <c r="AL56" s="117" t="n"/>
+      <c r="AM56" s="117" t="n"/>
+      <c r="AN56" s="117" t="n"/>
+      <c r="AO56" s="117" t="n"/>
+      <c r="AP56" s="117" t="n"/>
+      <c r="AQ56" s="117" t="n"/>
+      <c r="AR56" s="117" t="n"/>
+      <c r="AS56" s="117" t="n"/>
+      <c r="AT56" s="118" t="inlineStr">
+        <is>
+          <t>体位変換器</t>
+        </is>
+      </c>
+      <c r="AU56" s="117" t="n"/>
+      <c r="AV56" s="117" t="n"/>
+      <c r="AW56" s="117" t="n"/>
+      <c r="AX56" s="117" t="n"/>
+      <c r="AY56" s="117" t="n"/>
+      <c r="AZ56" s="119" t="n"/>
+      <c r="BB56" s="36" t="n"/>
+      <c r="BC56" s="40" t="n"/>
+      <c r="BD56" s="40" t="n"/>
+      <c r="BE56" s="40" t="n"/>
+      <c r="BF56" s="40" t="n"/>
+      <c r="BG56" s="40" t="n"/>
+      <c r="BH56" s="40" t="n"/>
+      <c r="BI56" s="40" t="n"/>
+      <c r="BJ56" s="40" t="n"/>
+      <c r="BK56" s="40" t="n"/>
+      <c r="BL56" s="40" t="n"/>
+      <c r="BM56" s="40" t="n"/>
+      <c r="BN56" s="40" t="n"/>
+      <c r="BO56" s="40" t="n"/>
+      <c r="BP56" s="40" t="n"/>
+      <c r="BQ56" s="40" t="n"/>
+      <c r="BR56" s="40" t="n"/>
+      <c r="BS56" s="40" t="n"/>
+      <c r="BT56" s="40" t="n"/>
+      <c r="BU56" s="40" t="n"/>
+      <c r="BV56" s="40" t="n"/>
+      <c r="BW56" s="40" t="n"/>
+      <c r="BX56" s="40" t="n"/>
+      <c r="BY56" s="40" t="n"/>
+      <c r="BZ56" s="40" t="n"/>
+      <c r="CA56" s="40" t="n"/>
+      <c r="CB56" s="40" t="n"/>
+      <c r="CC56" s="40" t="n"/>
+      <c r="CD56" s="40" t="n"/>
+      <c r="CE56" s="40" t="n"/>
+      <c r="CF56" s="40" t="n"/>
+      <c r="CG56" s="40" t="n"/>
+      <c r="CH56" s="40" t="n"/>
+      <c r="CI56" s="40" t="n"/>
+      <c r="CJ56" s="40" t="n"/>
+      <c r="CK56" s="38" t="n"/>
+    </row>
+    <row r="57" ht="9" customHeight="1">
+      <c r="A57" s="129" t="n"/>
+      <c r="B57" s="130" t="n"/>
+      <c r="C57" s="130" t="n"/>
+      <c r="D57" s="130" t="n"/>
+      <c r="E57" s="130" t="n"/>
+      <c r="F57" s="130" t="n"/>
+      <c r="G57" s="130" t="n"/>
+      <c r="H57" s="131" t="n"/>
+      <c r="I57" s="132" t="n"/>
+      <c r="J57" s="133" t="n"/>
+      <c r="K57" s="133" t="n"/>
+      <c r="L57" s="133" t="n"/>
+      <c r="M57" s="133" t="n"/>
+      <c r="N57" s="133" t="n"/>
+      <c r="O57" s="133" t="n"/>
+      <c r="P57" s="133" t="n"/>
+      <c r="Q57" s="133" t="n"/>
+      <c r="R57" s="133" t="n"/>
+      <c r="S57" s="133" t="n"/>
+      <c r="T57" s="133" t="n"/>
+      <c r="U57" s="133" t="n"/>
+      <c r="V57" s="133" t="n"/>
+      <c r="W57" s="133" t="n"/>
+      <c r="X57" s="133" t="n"/>
+      <c r="Y57" s="133" t="n"/>
+      <c r="Z57" s="133" t="n"/>
+      <c r="AA57" s="133" t="n"/>
+      <c r="AB57" s="133" t="n"/>
+      <c r="AC57" s="133" t="n"/>
+      <c r="AD57" s="133" t="n"/>
+      <c r="AE57" s="133" t="n"/>
+      <c r="AF57" s="133" t="n"/>
+      <c r="AG57" s="133" t="n"/>
+      <c r="AH57" s="133" t="n"/>
+      <c r="AI57" s="133" t="n"/>
+      <c r="AJ57" s="133" t="n"/>
+      <c r="AK57" s="133" t="n"/>
+      <c r="AL57" s="133" t="n"/>
+      <c r="AM57" s="133" t="n"/>
+      <c r="AN57" s="133" t="n"/>
+      <c r="AO57" s="133" t="n"/>
+      <c r="AP57" s="133" t="n"/>
+      <c r="AQ57" s="133" t="n"/>
+      <c r="AR57" s="133" t="n"/>
+      <c r="AS57" s="133" t="n"/>
+      <c r="AT57" s="133" t="n"/>
+      <c r="AU57" s="133" t="n"/>
+      <c r="AV57" s="133" t="n"/>
+      <c r="AW57" s="133" t="n"/>
+      <c r="AX57" s="133" t="n"/>
+      <c r="AY57" s="133" t="n"/>
+      <c r="AZ57" s="134" t="n"/>
+      <c r="BB57" s="36" t="n"/>
+      <c r="BC57" s="40" t="n"/>
+      <c r="BD57" s="40" t="n"/>
+      <c r="BE57" s="40" t="n"/>
+      <c r="BF57" s="40" t="n"/>
+      <c r="BG57" s="40" t="n"/>
+      <c r="BH57" s="40" t="n"/>
+      <c r="BI57" s="40" t="n"/>
+      <c r="BJ57" s="40" t="n"/>
+      <c r="BK57" s="40" t="n"/>
+      <c r="BL57" s="40" t="n"/>
+      <c r="BM57" s="40" t="n"/>
+      <c r="BN57" s="40" t="n"/>
+      <c r="BO57" s="40" t="n"/>
+      <c r="BP57" s="40" t="n"/>
+      <c r="BQ57" s="40" t="n"/>
+      <c r="BR57" s="40" t="n"/>
+      <c r="BS57" s="40" t="n"/>
+      <c r="BT57" s="40" t="n"/>
+      <c r="BU57" s="40" t="n"/>
+      <c r="BV57" s="40" t="n"/>
+      <c r="BW57" s="40" t="n"/>
+      <c r="BX57" s="40" t="n"/>
+      <c r="BY57" s="40" t="n"/>
+      <c r="BZ57" s="40" t="n"/>
+      <c r="CA57" s="40" t="n"/>
+      <c r="CB57" s="40" t="n"/>
+      <c r="CC57" s="40" t="n"/>
+      <c r="CD57" s="40" t="n"/>
+      <c r="CE57" s="40" t="n"/>
+      <c r="CF57" s="40" t="n"/>
+      <c r="CG57" s="40" t="n"/>
+      <c r="CH57" s="40" t="n"/>
+      <c r="CI57" s="40" t="n"/>
+      <c r="CJ57" s="40" t="n"/>
+      <c r="CK57" s="38" t="n"/>
+    </row>
+    <row r="58" ht="9" customHeight="1">
+      <c r="A58" s="129" t="n"/>
+      <c r="B58" s="130" t="n"/>
+      <c r="C58" s="130" t="n"/>
+      <c r="D58" s="130" t="n"/>
+      <c r="E58" s="130" t="n"/>
+      <c r="F58" s="130" t="n"/>
+      <c r="G58" s="130" t="n"/>
+      <c r="H58" s="131" t="n"/>
+      <c r="I58" s="135" t="inlineStr">
+        <is>
+          <t>手すり</t>
+        </is>
+      </c>
+      <c r="J58" s="133" t="n"/>
+      <c r="K58" s="133" t="n"/>
+      <c r="L58" s="133" t="n"/>
+      <c r="M58" s="136" t="inlineStr">
+        <is>
+          <t>スロープ</t>
+        </is>
+      </c>
+      <c r="N58" s="133" t="n"/>
+      <c r="O58" s="133" t="n"/>
+      <c r="P58" s="133" t="n"/>
+      <c r="Q58" s="133" t="n"/>
+      <c r="R58" s="136" t="inlineStr">
+        <is>
+          <t>歩行器</t>
+        </is>
+      </c>
+      <c r="S58" s="133" t="n"/>
+      <c r="T58" s="133" t="n"/>
+      <c r="U58" s="133" t="n"/>
+      <c r="V58" s="133" t="n"/>
+      <c r="W58" s="136" t="inlineStr">
+        <is>
+          <t>歩行補助つえ</t>
+        </is>
+      </c>
+      <c r="X58" s="133" t="n"/>
+      <c r="Y58" s="133" t="n"/>
+      <c r="Z58" s="133" t="n"/>
+      <c r="AA58" s="133" t="n"/>
+      <c r="AB58" s="133" t="n"/>
+      <c r="AC58" s="133" t="n"/>
+      <c r="AD58" s="136" t="inlineStr">
+        <is>
+          <t>徘徊感知機器</t>
+        </is>
+      </c>
+      <c r="AE58" s="133" t="n"/>
+      <c r="AF58" s="133" t="n"/>
+      <c r="AG58" s="133" t="n"/>
+      <c r="AH58" s="133" t="n"/>
+      <c r="AI58" s="133" t="n"/>
+      <c r="AJ58" s="133" t="n"/>
+      <c r="AK58" s="136" t="inlineStr">
+        <is>
+          <t>移動用リフト</t>
+        </is>
+      </c>
+      <c r="AL58" s="133" t="n"/>
+      <c r="AM58" s="133" t="n"/>
+      <c r="AN58" s="133" t="n"/>
+      <c r="AO58" s="133" t="n"/>
+      <c r="AP58" s="133" t="n"/>
+      <c r="AQ58" s="133" t="n"/>
+      <c r="AR58" s="136" t="inlineStr">
+        <is>
+          <t>自動排泄処理装置</t>
+        </is>
+      </c>
+      <c r="AS58" s="133" t="n"/>
+      <c r="AT58" s="133" t="n"/>
+      <c r="AU58" s="133" t="n"/>
+      <c r="AV58" s="133" t="n"/>
+      <c r="AW58" s="133" t="n"/>
+      <c r="AX58" s="133" t="n"/>
+      <c r="AY58" s="133" t="n"/>
+      <c r="AZ58" s="134" t="n"/>
+      <c r="BB58" s="36" t="n"/>
+      <c r="BC58" s="40" t="n"/>
+      <c r="BD58" s="40" t="n"/>
+      <c r="BE58" s="40" t="n"/>
+      <c r="BF58" s="40" t="n"/>
+      <c r="BG58" s="40" t="n"/>
+      <c r="BH58" s="40" t="n"/>
+      <c r="BI58" s="40" t="n"/>
+      <c r="BJ58" s="40" t="n"/>
+      <c r="BK58" s="40" t="n"/>
+      <c r="BL58" s="40" t="n"/>
+      <c r="BM58" s="40" t="n"/>
+      <c r="BN58" s="40" t="n"/>
+      <c r="BO58" s="40" t="n"/>
+      <c r="BP58" s="40" t="n"/>
+      <c r="BQ58" s="40" t="n"/>
+      <c r="BR58" s="40" t="n"/>
+      <c r="BS58" s="40" t="n"/>
+      <c r="BT58" s="40" t="n"/>
+      <c r="BU58" s="40" t="n"/>
+      <c r="BV58" s="40" t="n"/>
+      <c r="BW58" s="40" t="n"/>
+      <c r="BX58" s="40" t="n"/>
+      <c r="BY58" s="40" t="n"/>
+      <c r="BZ58" s="40" t="n"/>
+      <c r="CA58" s="40" t="n"/>
+      <c r="CB58" s="40" t="n"/>
+      <c r="CC58" s="40" t="n"/>
+      <c r="CD58" s="40" t="n"/>
+      <c r="CE58" s="40" t="n"/>
+      <c r="CF58" s="40" t="n"/>
+      <c r="CG58" s="40" t="n"/>
+      <c r="CH58" s="40" t="n"/>
+      <c r="CI58" s="40" t="n"/>
+      <c r="CJ58" s="40" t="n"/>
+      <c r="CK58" s="38" t="n"/>
+    </row>
+    <row r="59" ht="9" customHeight="1">
+      <c r="A59" s="120" t="n"/>
+      <c r="B59" s="45" t="n"/>
+      <c r="C59" s="45" t="n"/>
+      <c r="D59" s="45" t="n"/>
+      <c r="E59" s="45" t="n"/>
+      <c r="F59" s="45" t="n"/>
+      <c r="G59" s="45" t="n"/>
+      <c r="H59" s="46" t="n"/>
+      <c r="I59" s="101" t="n"/>
+      <c r="J59" s="102" t="n"/>
+      <c r="K59" s="102" t="n"/>
+      <c r="L59" s="102" t="n"/>
+      <c r="M59" s="102" t="n"/>
+      <c r="N59" s="102" t="n"/>
+      <c r="O59" s="102" t="n"/>
+      <c r="P59" s="102" t="n"/>
+      <c r="Q59" s="102" t="n"/>
+      <c r="R59" s="102" t="n"/>
+      <c r="S59" s="102" t="n"/>
+      <c r="T59" s="102" t="n"/>
+      <c r="U59" s="102" t="n"/>
+      <c r="V59" s="102" t="n"/>
+      <c r="W59" s="102" t="n"/>
+      <c r="X59" s="102" t="n"/>
+      <c r="Y59" s="102" t="n"/>
+      <c r="Z59" s="102" t="n"/>
+      <c r="AA59" s="102" t="n"/>
+      <c r="AB59" s="102" t="n"/>
+      <c r="AC59" s="102" t="n"/>
+      <c r="AD59" s="102" t="n"/>
+      <c r="AE59" s="102" t="n"/>
+      <c r="AF59" s="102" t="n"/>
+      <c r="AG59" s="102" t="n"/>
+      <c r="AH59" s="102" t="n"/>
+      <c r="AI59" s="102" t="n"/>
+      <c r="AJ59" s="102" t="n"/>
+      <c r="AK59" s="102" t="n"/>
+      <c r="AL59" s="102" t="n"/>
+      <c r="AM59" s="102" t="n"/>
+      <c r="AN59" s="102" t="n"/>
+      <c r="AO59" s="102" t="n"/>
+      <c r="AP59" s="102" t="n"/>
+      <c r="AQ59" s="102" t="n"/>
+      <c r="AR59" s="102" t="n"/>
+      <c r="AS59" s="102" t="n"/>
+      <c r="AT59" s="102" t="n"/>
+      <c r="AU59" s="102" t="n"/>
+      <c r="AV59" s="102" t="n"/>
+      <c r="AW59" s="102" t="n"/>
+      <c r="AX59" s="102" t="n"/>
+      <c r="AY59" s="102" t="n"/>
+      <c r="AZ59" s="121" t="n"/>
+      <c r="BB59" s="36" t="n"/>
+      <c r="BC59" s="40" t="n"/>
+      <c r="BD59" s="40" t="n"/>
+      <c r="BE59" s="40" t="n"/>
+      <c r="BF59" s="40" t="n"/>
+      <c r="BG59" s="40" t="n"/>
+      <c r="BH59" s="40" t="n"/>
+      <c r="BI59" s="40" t="n"/>
+      <c r="BJ59" s="40" t="n"/>
+      <c r="BK59" s="40" t="n"/>
+      <c r="BL59" s="40" t="n"/>
+      <c r="BM59" s="40" t="n"/>
+      <c r="BN59" s="40" t="n"/>
+      <c r="BO59" s="40" t="n"/>
+      <c r="BP59" s="40" t="n"/>
+      <c r="BQ59" s="40" t="n"/>
+      <c r="BR59" s="40" t="n"/>
+      <c r="BS59" s="40" t="n"/>
+      <c r="BT59" s="40" t="n"/>
+      <c r="BU59" s="40" t="n"/>
+      <c r="BV59" s="40" t="n"/>
+      <c r="BW59" s="40" t="n"/>
+      <c r="BX59" s="40" t="n"/>
+      <c r="BY59" s="40" t="n"/>
+      <c r="BZ59" s="40" t="n"/>
+      <c r="CA59" s="40" t="n"/>
+      <c r="CB59" s="40" t="n"/>
+      <c r="CC59" s="40" t="n"/>
+      <c r="CD59" s="40" t="n"/>
+      <c r="CE59" s="40" t="n"/>
+      <c r="CF59" s="40" t="n"/>
+      <c r="CG59" s="40" t="n"/>
+      <c r="CH59" s="40" t="n"/>
+      <c r="CI59" s="40" t="n"/>
+      <c r="CJ59" s="40" t="n"/>
+      <c r="CK59" s="38" t="n"/>
+    </row>
+    <row r="60" ht="9" customHeight="1">
+      <c r="A60" s="122" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="n"/>
+      <c r="C60" s="42" t="n"/>
+      <c r="D60" s="42" t="n"/>
+      <c r="E60" s="42" t="n"/>
+      <c r="F60" s="42" t="n"/>
+      <c r="G60" s="42" t="n"/>
+      <c r="H60" s="43" t="n"/>
+      <c r="I60" s="123" t="n"/>
+      <c r="J60" s="94" t="n"/>
+      <c r="K60" s="94" t="n"/>
+      <c r="L60" s="94" t="n"/>
+      <c r="M60" s="94" t="n"/>
+      <c r="N60" s="94" t="n"/>
+      <c r="O60" s="94" t="n"/>
+      <c r="P60" s="94" t="n"/>
+      <c r="Q60" s="94" t="n"/>
+      <c r="R60" s="94" t="n"/>
+      <c r="S60" s="94" t="n"/>
+      <c r="T60" s="94" t="n"/>
+      <c r="U60" s="94" t="n"/>
+      <c r="V60" s="94" t="n"/>
+      <c r="W60" s="94" t="n"/>
+      <c r="X60" s="94" t="n"/>
+      <c r="Y60" s="94" t="n"/>
+      <c r="Z60" s="94" t="n"/>
+      <c r="AA60" s="94" t="n"/>
+      <c r="AB60" s="94" t="n"/>
+      <c r="AC60" s="94" t="n"/>
+      <c r="AD60" s="94" t="n"/>
+      <c r="AE60" s="94" t="n"/>
+      <c r="AF60" s="94" t="n"/>
+      <c r="AG60" s="94" t="n"/>
+      <c r="AH60" s="94" t="n"/>
+      <c r="AI60" s="94" t="n"/>
+      <c r="AJ60" s="94" t="n"/>
+      <c r="AK60" s="94" t="n"/>
+      <c r="AL60" s="94" t="n"/>
+      <c r="AM60" s="94" t="n"/>
+      <c r="AN60" s="94" t="n"/>
+      <c r="AO60" s="94" t="n"/>
+      <c r="AP60" s="94" t="n"/>
+      <c r="AQ60" s="94" t="n"/>
+      <c r="AR60" s="94" t="n"/>
+      <c r="AS60" s="94" t="n"/>
+      <c r="AT60" s="94" t="n"/>
+      <c r="AU60" s="94" t="n"/>
+      <c r="AV60" s="94" t="n"/>
+      <c r="AW60" s="94" t="n"/>
+      <c r="AX60" s="94" t="n"/>
+      <c r="AY60" s="94" t="n"/>
+      <c r="AZ60" s="124" t="n"/>
+      <c r="BB60" s="36" t="n"/>
+      <c r="BC60" s="40" t="n"/>
+      <c r="BD60" s="40" t="n"/>
+      <c r="BE60" s="40" t="n"/>
+      <c r="BF60" s="40" t="n"/>
+      <c r="BG60" s="40" t="n"/>
+      <c r="BH60" s="40" t="n"/>
+      <c r="BI60" s="40" t="n"/>
+      <c r="BJ60" s="40" t="n"/>
+      <c r="BK60" s="40" t="n"/>
+      <c r="BL60" s="40" t="n"/>
+      <c r="BM60" s="40" t="n"/>
+      <c r="BN60" s="40" t="n"/>
+      <c r="BO60" s="40" t="n"/>
+      <c r="BP60" s="40" t="n"/>
+      <c r="BQ60" s="40" t="n"/>
+      <c r="BR60" s="40" t="n"/>
+      <c r="BS60" s="40" t="n"/>
+      <c r="BT60" s="40" t="n"/>
+      <c r="BU60" s="40" t="n"/>
+      <c r="BV60" s="40" t="n"/>
+      <c r="BW60" s="40" t="n"/>
+      <c r="BX60" s="40" t="n"/>
+      <c r="BY60" s="40" t="n"/>
+      <c r="BZ60" s="40" t="n"/>
+      <c r="CA60" s="40" t="n"/>
+      <c r="CB60" s="40" t="n"/>
+      <c r="CC60" s="40" t="n"/>
+      <c r="CD60" s="40" t="n"/>
+      <c r="CE60" s="40" t="n"/>
+      <c r="CF60" s="40" t="n"/>
+      <c r="CG60" s="40" t="n"/>
+      <c r="CH60" s="40" t="n"/>
+      <c r="CI60" s="40" t="n"/>
+      <c r="CJ60" s="40" t="n"/>
+      <c r="CK60" s="38" t="n"/>
+    </row>
+    <row r="61" ht="9" customHeight="1">
+      <c r="A61" s="137" t="n"/>
+      <c r="B61" s="138" t="n"/>
+      <c r="C61" s="138" t="n"/>
+      <c r="D61" s="138" t="n"/>
+      <c r="E61" s="138" t="n"/>
+      <c r="F61" s="138" t="n"/>
+      <c r="G61" s="138" t="n"/>
+      <c r="H61" s="139" t="n"/>
+      <c r="I61" s="140" t="n"/>
+      <c r="J61" s="141" t="n"/>
+      <c r="K61" s="141" t="n"/>
+      <c r="L61" s="141" t="n"/>
+      <c r="M61" s="141" t="n"/>
+      <c r="N61" s="141" t="n"/>
+      <c r="O61" s="141" t="n"/>
+      <c r="P61" s="141" t="n"/>
+      <c r="Q61" s="141" t="n"/>
+      <c r="R61" s="141" t="n"/>
+      <c r="S61" s="141" t="n"/>
+      <c r="T61" s="141" t="n"/>
+      <c r="U61" s="141" t="n"/>
+      <c r="V61" s="141" t="n"/>
+      <c r="W61" s="141" t="n"/>
+      <c r="X61" s="141" t="n"/>
+      <c r="Y61" s="141" t="n"/>
+      <c r="Z61" s="141" t="n"/>
+      <c r="AA61" s="141" t="n"/>
+      <c r="AB61" s="141" t="n"/>
+      <c r="AC61" s="141" t="n"/>
+      <c r="AD61" s="141" t="n"/>
+      <c r="AE61" s="141" t="n"/>
+      <c r="AF61" s="141" t="n"/>
+      <c r="AG61" s="141" t="n"/>
+      <c r="AH61" s="141" t="n"/>
+      <c r="AI61" s="141" t="n"/>
+      <c r="AJ61" s="141" t="n"/>
+      <c r="AK61" s="141" t="n"/>
+      <c r="AL61" s="141" t="n"/>
+      <c r="AM61" s="141" t="n"/>
+      <c r="AN61" s="141" t="n"/>
+      <c r="AO61" s="141" t="n"/>
+      <c r="AP61" s="141" t="n"/>
+      <c r="AQ61" s="141" t="n"/>
+      <c r="AR61" s="141" t="n"/>
+      <c r="AS61" s="141" t="n"/>
+      <c r="AT61" s="141" t="n"/>
+      <c r="AU61" s="141" t="n"/>
+      <c r="AV61" s="141" t="n"/>
+      <c r="AW61" s="141" t="n"/>
+      <c r="AX61" s="141" t="n"/>
+      <c r="AY61" s="141" t="n"/>
+      <c r="AZ61" s="142" t="n"/>
+      <c r="BB61" s="143" t="n"/>
+      <c r="BC61" s="144" t="n"/>
+      <c r="BD61" s="144" t="n"/>
+      <c r="BE61" s="144" t="n"/>
+      <c r="BF61" s="144" t="n"/>
+      <c r="BG61" s="144" t="n"/>
+      <c r="BH61" s="144" t="n"/>
+      <c r="BI61" s="144" t="n"/>
+      <c r="BJ61" s="144" t="n"/>
+      <c r="BK61" s="144" t="n"/>
+      <c r="BL61" s="144" t="n"/>
+      <c r="BM61" s="144" t="n"/>
+      <c r="BN61" s="144" t="n"/>
+      <c r="BO61" s="144" t="n"/>
+      <c r="BP61" s="144" t="n"/>
+      <c r="BQ61" s="144" t="n"/>
+      <c r="BR61" s="144" t="n"/>
+      <c r="BS61" s="144" t="n"/>
+      <c r="BT61" s="144" t="n"/>
+      <c r="BU61" s="144" t="n"/>
+      <c r="BV61" s="144" t="n"/>
+      <c r="BW61" s="144" t="n"/>
+      <c r="BX61" s="144" t="n"/>
+      <c r="BY61" s="144" t="n"/>
+      <c r="BZ61" s="144" t="n"/>
+      <c r="CA61" s="144" t="n"/>
+      <c r="CB61" s="144" t="n"/>
+      <c r="CC61" s="144" t="n"/>
+      <c r="CD61" s="144" t="n"/>
+      <c r="CE61" s="144" t="n"/>
+      <c r="CF61" s="144" t="n"/>
+      <c r="CG61" s="144" t="n"/>
+      <c r="CH61" s="144" t="n"/>
+      <c r="CI61" s="144" t="n"/>
+      <c r="CJ61" s="144" t="n"/>
+      <c r="CK61" s="145" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="133">
+  <mergeCells count="145">
     <mergeCell ref="AI32:AJ33"/>
     <mergeCell ref="AU50:AZ51"/>
     <mergeCell ref="BB6:CK7"/>
     <mergeCell ref="U20:Z21"/>
+    <mergeCell ref="A56:H59"/>
     <mergeCell ref="I22:AZ23"/>
     <mergeCell ref="AG16:AZ17"/>
-    <mergeCell ref="AU52:AZ53"/>
     <mergeCell ref="I36:X37"/>
     <mergeCell ref="A22:H23"/>
     <mergeCell ref="AU42:AZ43"/>
     <mergeCell ref="A20:H21"/>
-    <mergeCell ref="I52:X53"/>
+    <mergeCell ref="I52:O53"/>
     <mergeCell ref="A38:B39"/>
     <mergeCell ref="I24:L25"/>
     <mergeCell ref="AU44:AZ45"/>
+    <mergeCell ref="R58:V59"/>
     <mergeCell ref="Y50:AH51"/>
-    <mergeCell ref="A52:B53"/>
-    <mergeCell ref="C54:H55"/>
     <mergeCell ref="AK50:AT51"/>
     <mergeCell ref="A40:B41"/>
+    <mergeCell ref="AB56:AJ57"/>
     <mergeCell ref="AK44:AT45"/>
     <mergeCell ref="AI34:AJ35"/>
-    <mergeCell ref="Y52:AH53"/>
     <mergeCell ref="AK34:AT35"/>
     <mergeCell ref="I10:L11"/>
     <mergeCell ref="AU30:AZ31"/>
@@ -5980,59 +6695,65 @@
     <mergeCell ref="C40:H41"/>
     <mergeCell ref="S24:X25"/>
     <mergeCell ref="AK36:AT37"/>
+    <mergeCell ref="AV52:AZ53"/>
+    <mergeCell ref="A54:H55"/>
     <mergeCell ref="A50:B51"/>
     <mergeCell ref="Y42:AH43"/>
+    <mergeCell ref="I54:AZ55"/>
     <mergeCell ref="AK42:AT43"/>
     <mergeCell ref="I46:X47"/>
     <mergeCell ref="I40:X41"/>
     <mergeCell ref="C32:H33"/>
     <mergeCell ref="AU32:AZ33"/>
+    <mergeCell ref="P52:W53"/>
+    <mergeCell ref="AK56:AS57"/>
     <mergeCell ref="A12:H15"/>
     <mergeCell ref="AG24:AX25"/>
     <mergeCell ref="A32:B33"/>
     <mergeCell ref="C34:H35"/>
     <mergeCell ref="A8:H9"/>
-    <mergeCell ref="Y54:AH55"/>
+    <mergeCell ref="AK58:AQ59"/>
     <mergeCell ref="AI46:AJ47"/>
-    <mergeCell ref="AK54:AT55"/>
     <mergeCell ref="A10:H11"/>
     <mergeCell ref="AI10:AZ11"/>
     <mergeCell ref="C42:H43"/>
     <mergeCell ref="I6:AX7"/>
     <mergeCell ref="AK38:AT39"/>
     <mergeCell ref="Y34:AH35"/>
+    <mergeCell ref="A52:H53"/>
     <mergeCell ref="O20:T21"/>
     <mergeCell ref="AI48:AJ49"/>
     <mergeCell ref="Y40:AH41"/>
+    <mergeCell ref="I60:AZ61"/>
     <mergeCell ref="C50:H51"/>
     <mergeCell ref="C44:H45"/>
     <mergeCell ref="AK40:AT41"/>
     <mergeCell ref="AI38:AJ39"/>
     <mergeCell ref="O16:AF17"/>
     <mergeCell ref="AU34:AZ35"/>
+    <mergeCell ref="N56:U57"/>
     <mergeCell ref="C36:H37"/>
     <mergeCell ref="AU36:AZ37"/>
     <mergeCell ref="M12:AJ13"/>
-    <mergeCell ref="AK52:AT53"/>
     <mergeCell ref="A6:H7"/>
-    <mergeCell ref="AU54:AZ55"/>
     <mergeCell ref="Y38:AH39"/>
+    <mergeCell ref="AT56:AZ57"/>
     <mergeCell ref="BR3:CK4"/>
     <mergeCell ref="AA20:AZ21"/>
+    <mergeCell ref="AD58:AJ59"/>
     <mergeCell ref="BL3:BQ4"/>
     <mergeCell ref="C48:H49"/>
-    <mergeCell ref="I54:X55"/>
     <mergeCell ref="AU46:AZ47"/>
     <mergeCell ref="I32:X33"/>
     <mergeCell ref="AI50:AJ51"/>
     <mergeCell ref="C38:H39"/>
     <mergeCell ref="I30:AJ31"/>
     <mergeCell ref="A42:B43"/>
-    <mergeCell ref="AI52:AJ53"/>
     <mergeCell ref="I12:L13"/>
     <mergeCell ref="AK30:AT31"/>
     <mergeCell ref="AY6:AZ7"/>
     <mergeCell ref="A44:B45"/>
+    <mergeCell ref="AR58:AZ59"/>
     <mergeCell ref="A34:B35"/>
     <mergeCell ref="I14:L15"/>
     <mergeCell ref="AO12:AZ13"/>
@@ -6040,23 +6761,25 @@
     <mergeCell ref="A48:B49"/>
     <mergeCell ref="A30:B31"/>
     <mergeCell ref="I42:X43"/>
+    <mergeCell ref="W58:AC59"/>
     <mergeCell ref="AK46:AT47"/>
     <mergeCell ref="A24:H25"/>
     <mergeCell ref="I34:X35"/>
     <mergeCell ref="M14:AZ15"/>
-    <mergeCell ref="A54:B55"/>
+    <mergeCell ref="A60:H61"/>
     <mergeCell ref="Y48:AH49"/>
     <mergeCell ref="I50:X51"/>
     <mergeCell ref="I44:X45"/>
-    <mergeCell ref="C52:H53"/>
     <mergeCell ref="AK48:AT49"/>
     <mergeCell ref="A16:H19"/>
     <mergeCell ref="AI40:AJ41"/>
     <mergeCell ref="AY24:AZ25"/>
-    <mergeCell ref="AI54:AJ55"/>
     <mergeCell ref="AK32:AT33"/>
+    <mergeCell ref="V56:AA57"/>
+    <mergeCell ref="I56:M57"/>
     <mergeCell ref="A46:B47"/>
     <mergeCell ref="A28:AZ29"/>
+    <mergeCell ref="AN52:AR53"/>
     <mergeCell ref="AE24:AF25"/>
     <mergeCell ref="Y24:AD25"/>
     <mergeCell ref="C30:H31"/>
@@ -6069,21 +6792,26 @@
     <mergeCell ref="AG18:AZ19"/>
     <mergeCell ref="I16:N17"/>
     <mergeCell ref="AU38:AZ39"/>
+    <mergeCell ref="AE52:AM53"/>
+    <mergeCell ref="I58:L59"/>
     <mergeCell ref="AI42:AJ43"/>
     <mergeCell ref="I48:X49"/>
     <mergeCell ref="I18:N19"/>
     <mergeCell ref="AU40:AZ41"/>
+    <mergeCell ref="M58:Q59"/>
     <mergeCell ref="AI44:AJ45"/>
     <mergeCell ref="Y46:AH47"/>
     <mergeCell ref="I38:X39"/>
+    <mergeCell ref="AS52:AU53"/>
     <mergeCell ref="Y32:AH33"/>
     <mergeCell ref="A36:B37"/>
     <mergeCell ref="M24:R25"/>
+    <mergeCell ref="X52:AD53"/>
     <mergeCell ref="AI36:AJ37"/>
     <mergeCell ref="AK12:AN13"/>
     <mergeCell ref="I20:N21"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:CK55">
+  <conditionalFormatting sqref="A1:CK61">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(A1,1)="■"</formula>
     </cfRule>
@@ -6110,7 +6838,7 @@
     <dataValidation sqref="Y24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□その他,■その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="M10 M14 AI10 AK32 AK34 AK36 AK38 AK40 AK42 AK44 AK46 AK48 AK50 AK52 AK54 AU32 AU34 AU36 AU38 AU40 AU42 AU44 AU46 AU48 AU50 AU52 AU54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
+    <dataValidation sqref="M10 M14 AI10 AK32 AK34 AK36 AK38 AK40 AK42 AK44 AK46 AK48 AK50 AU32 AU34 AU36 AU38 AU40 AU42 AU44 AU46 AU48 AU50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>

--- a/住宅改修_現地調査アセスメントシート.xlsx
+++ b/住宅改修_現地調査アセスメントシート.xlsx
@@ -2644,13 +2644,17 @@
       <c r="V20" s="7" t="n"/>
       <c r="W20" s="7" t="n"/>
       <c r="X20" s="7" t="n"/>
-      <c r="Y20" s="89" t="n"/>
+      <c r="Y20" s="88" t="inlineStr">
+        <is>
+          <t>□生保</t>
+        </is>
+      </c>
       <c r="Z20" s="7" t="n"/>
       <c r="AA20" s="7" t="n"/>
       <c r="AB20" s="7" t="n"/>
       <c r="AC20" s="7" t="n"/>
       <c r="AD20" s="7" t="n"/>
-      <c r="AE20" s="7" t="n"/>
+      <c r="AE20" s="89" t="n"/>
       <c r="AF20" s="7" t="n"/>
       <c r="AG20" s="7" t="n"/>
       <c r="AH20" s="37" t="n"/>
@@ -6716,7 +6720,7 @@
       <c r="CK61" s="134" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="174">
+  <mergeCells count="175">
     <mergeCell ref="M50:AH51"/>
     <mergeCell ref="S20:X21"/>
     <mergeCell ref="BG50:BT51"/>
@@ -6828,12 +6832,14 @@
     <mergeCell ref="A44:B45"/>
     <mergeCell ref="G14:J15"/>
     <mergeCell ref="A16:F19"/>
+    <mergeCell ref="Y20:AD21"/>
     <mergeCell ref="Y12:AB13"/>
     <mergeCell ref="A40:H41"/>
     <mergeCell ref="AG6:AH7"/>
     <mergeCell ref="A48:B49"/>
     <mergeCell ref="F28:L29"/>
     <mergeCell ref="AE28:AH29"/>
+    <mergeCell ref="AE20:AH21"/>
     <mergeCell ref="AL56:AQ57"/>
     <mergeCell ref="C48:L49"/>
     <mergeCell ref="M42:AH43"/>
@@ -6860,7 +6866,6 @@
     <mergeCell ref="AC24:AF25"/>
     <mergeCell ref="G6:AF7"/>
     <mergeCell ref="AL60:AQ61"/>
-    <mergeCell ref="Y20:AH21"/>
     <mergeCell ref="G10:J11"/>
     <mergeCell ref="K24:P25"/>
     <mergeCell ref="M54:AH55"/>
@@ -6897,7 +6902,7 @@
       <formula>LEFT(A1,1)="■"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="G20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□1割,■1割"</formula1>
     </dataValidation>
@@ -6906,6 +6911,9 @@
     </dataValidation>
     <dataValidation sqref="S20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□3割,■3割"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"□生保,■生保"</formula1>
     </dataValidation>
     <dataValidation sqref="G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□なし,■なし"</formula1>

--- a/住宅改修_現地調査アセスメントシート.xlsx
+++ b/住宅改修_現地調査アセスメントシート.xlsx
@@ -385,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -558,6 +558,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -571,10 +576,16 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4145,42 +4156,46 @@
       <c r="C36" s="67" t="n"/>
       <c r="D36" s="67" t="n"/>
       <c r="E36" s="67" t="n"/>
-      <c r="F36" s="67" t="n"/>
-      <c r="G36" s="100" t="inlineStr">
+      <c r="F36" s="100" t="inlineStr">
         <is>
           <t>車いす付属品</t>
         </is>
       </c>
+      <c r="G36" s="67" t="n"/>
       <c r="H36" s="67" t="n"/>
       <c r="I36" s="67" t="n"/>
       <c r="J36" s="67" t="n"/>
       <c r="K36" s="67" t="n"/>
       <c r="L36" s="67" t="n"/>
       <c r="M36" s="67" t="n"/>
-      <c r="N36" s="67" t="n"/>
+      <c r="N36" s="100" t="inlineStr">
+        <is>
+          <t>特殊寝台</t>
+        </is>
+      </c>
       <c r="O36" s="67" t="n"/>
       <c r="P36" s="67" t="n"/>
-      <c r="Q36" s="100" t="inlineStr">
-        <is>
-          <t>特殊寝台</t>
-        </is>
-      </c>
+      <c r="Q36" s="67" t="n"/>
       <c r="R36" s="67" t="n"/>
       <c r="S36" s="67" t="n"/>
-      <c r="T36" s="67" t="n"/>
+      <c r="T36" s="100" t="inlineStr">
+        <is>
+          <t>特殊寝台付属品</t>
+        </is>
+      </c>
       <c r="U36" s="67" t="n"/>
       <c r="V36" s="67" t="n"/>
       <c r="W36" s="67" t="n"/>
-      <c r="X36" s="100" t="inlineStr">
-        <is>
-          <t>特殊寝台付属品</t>
-        </is>
-      </c>
+      <c r="X36" s="67" t="n"/>
       <c r="Y36" s="67" t="n"/>
       <c r="Z36" s="67" t="n"/>
       <c r="AA36" s="67" t="n"/>
       <c r="AB36" s="67" t="n"/>
-      <c r="AC36" s="67" t="n"/>
+      <c r="AC36" s="100" t="inlineStr">
+        <is>
+          <t>特価ベッド</t>
+        </is>
+      </c>
       <c r="AD36" s="67" t="n"/>
       <c r="AE36" s="67" t="n"/>
       <c r="AF36" s="67" t="n"/>
@@ -4772,16 +4787,21 @@
       <c r="J42" s="50" t="n"/>
       <c r="K42" s="50" t="n"/>
       <c r="L42" s="51" t="n"/>
-      <c r="M42" s="49" t="inlineStr">
+      <c r="M42" s="114" t="inlineStr">
+        <is>
+          <t>単位数
+（試算用）</t>
+        </is>
+      </c>
+      <c r="N42" s="115" t="n"/>
+      <c r="O42" s="115" t="n"/>
+      <c r="P42" s="115" t="n"/>
+      <c r="Q42" s="116" t="n"/>
+      <c r="R42" s="49" t="inlineStr">
         <is>
           <t>商品名</t>
         </is>
       </c>
-      <c r="N42" s="50" t="n"/>
-      <c r="O42" s="50" t="n"/>
-      <c r="P42" s="50" t="n"/>
-      <c r="Q42" s="50" t="n"/>
-      <c r="R42" s="50" t="n"/>
       <c r="S42" s="50" t="n"/>
       <c r="T42" s="50" t="n"/>
       <c r="U42" s="50" t="n"/>
@@ -4798,19 +4818,19 @@
       <c r="AF42" s="50" t="n"/>
       <c r="AG42" s="50" t="n"/>
       <c r="AH42" s="112" t="n"/>
-      <c r="AJ42" s="114" t="inlineStr">
+      <c r="AJ42" s="117" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="AK42" s="115" t="n"/>
+      <c r="AK42" s="118" t="n"/>
       <c r="AL42" s="6" t="n"/>
       <c r="AM42" s="7" t="n"/>
       <c r="AN42" s="7" t="n"/>
       <c r="AO42" s="7" t="n"/>
       <c r="AP42" s="7" t="n"/>
       <c r="AQ42" s="8" t="n"/>
-      <c r="AR42" s="116" t="inlineStr">
+      <c r="AR42" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -4843,12 +4863,12 @@
       <c r="BR42" s="67" t="n"/>
       <c r="BS42" s="67" t="n"/>
       <c r="BT42" s="67" t="n"/>
-      <c r="BU42" s="117" t="inlineStr">
+      <c r="BU42" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV42" s="118" t="n"/>
+      <c r="BV42" s="121" t="n"/>
       <c r="BW42" s="7" t="n"/>
       <c r="BX42" s="7" t="n"/>
       <c r="BY42" s="7" t="n"/>
@@ -4858,7 +4878,7 @@
       <c r="CC42" s="7" t="n"/>
       <c r="CD42" s="7" t="n"/>
       <c r="CE42" s="8" t="n"/>
-      <c r="CF42" s="118" t="n"/>
+      <c r="CF42" s="121" t="n"/>
       <c r="CG42" s="7" t="n"/>
       <c r="CH42" s="7" t="n"/>
       <c r="CI42" s="7" t="n"/>
@@ -4878,12 +4898,12 @@
       <c r="J43" s="27" t="n"/>
       <c r="K43" s="27" t="n"/>
       <c r="L43" s="28" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="27" t="n"/>
-      <c r="O43" s="27" t="n"/>
-      <c r="P43" s="27" t="n"/>
-      <c r="Q43" s="27" t="n"/>
-      <c r="R43" s="27" t="n"/>
+      <c r="M43" s="122" t="n"/>
+      <c r="N43" s="123" t="n"/>
+      <c r="O43" s="123" t="n"/>
+      <c r="P43" s="123" t="n"/>
+      <c r="Q43" s="124" t="n"/>
+      <c r="R43" s="55" t="n"/>
       <c r="S43" s="27" t="n"/>
       <c r="T43" s="27" t="n"/>
       <c r="U43" s="27" t="n"/>
@@ -4900,8 +4920,8 @@
       <c r="AF43" s="27" t="n"/>
       <c r="AG43" s="27" t="n"/>
       <c r="AH43" s="113" t="n"/>
-      <c r="AJ43" s="119" t="n"/>
-      <c r="AK43" s="120" t="n"/>
+      <c r="AJ43" s="125" t="n"/>
+      <c r="AK43" s="126" t="n"/>
       <c r="AL43" s="13" t="n"/>
       <c r="AM43" s="14" t="n"/>
       <c r="AN43" s="14" t="n"/>
@@ -4937,7 +4957,7 @@
       <c r="BR43" s="76" t="n"/>
       <c r="BS43" s="76" t="n"/>
       <c r="BT43" s="76" t="n"/>
-      <c r="BU43" s="121" t="n"/>
+      <c r="BU43" s="127" t="n"/>
       <c r="BV43" s="13" t="n"/>
       <c r="BW43" s="14" t="n"/>
       <c r="BX43" s="14" t="n"/>
@@ -4971,13 +4991,13 @@
       <c r="I44" s="67" t="n"/>
       <c r="J44" s="67" t="n"/>
       <c r="K44" s="67" t="n"/>
-      <c r="L44" s="122" t="n"/>
-      <c r="M44" s="102" t="n"/>
+      <c r="L44" s="128" t="n"/>
+      <c r="M44" s="129" t="n"/>
       <c r="N44" s="67" t="n"/>
       <c r="O44" s="67" t="n"/>
       <c r="P44" s="67" t="n"/>
-      <c r="Q44" s="67" t="n"/>
-      <c r="R44" s="67" t="n"/>
+      <c r="Q44" s="128" t="n"/>
+      <c r="R44" s="102" t="n"/>
       <c r="S44" s="67" t="n"/>
       <c r="T44" s="67" t="n"/>
       <c r="U44" s="67" t="n"/>
@@ -4994,19 +5014,19 @@
       <c r="AF44" s="67" t="n"/>
       <c r="AG44" s="67" t="n"/>
       <c r="AH44" s="68" t="n"/>
-      <c r="AJ44" s="114" t="inlineStr">
+      <c r="AJ44" s="117" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="AK44" s="115" t="n"/>
+      <c r="AK44" s="118" t="n"/>
       <c r="AL44" s="6" t="n"/>
       <c r="AM44" s="7" t="n"/>
       <c r="AN44" s="7" t="n"/>
       <c r="AO44" s="7" t="n"/>
       <c r="AP44" s="7" t="n"/>
       <c r="AQ44" s="8" t="n"/>
-      <c r="AR44" s="116" t="inlineStr">
+      <c r="AR44" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -5039,12 +5059,12 @@
       <c r="BR44" s="67" t="n"/>
       <c r="BS44" s="67" t="n"/>
       <c r="BT44" s="67" t="n"/>
-      <c r="BU44" s="117" t="inlineStr">
+      <c r="BU44" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV44" s="118" t="n"/>
+      <c r="BV44" s="121" t="n"/>
       <c r="BW44" s="7" t="n"/>
       <c r="BX44" s="7" t="n"/>
       <c r="BY44" s="7" t="n"/>
@@ -5054,7 +5074,7 @@
       <c r="CC44" s="7" t="n"/>
       <c r="CD44" s="7" t="n"/>
       <c r="CE44" s="8" t="n"/>
-      <c r="CF44" s="118" t="n"/>
+      <c r="CF44" s="121" t="n"/>
       <c r="CG44" s="7" t="n"/>
       <c r="CH44" s="7" t="n"/>
       <c r="CI44" s="7" t="n"/>
@@ -5073,13 +5093,13 @@
       <c r="I45" s="76" t="n"/>
       <c r="J45" s="76" t="n"/>
       <c r="K45" s="76" t="n"/>
-      <c r="L45" s="121" t="n"/>
+      <c r="L45" s="127" t="n"/>
       <c r="M45" s="75" t="n"/>
       <c r="N45" s="76" t="n"/>
       <c r="O45" s="76" t="n"/>
       <c r="P45" s="76" t="n"/>
-      <c r="Q45" s="76" t="n"/>
-      <c r="R45" s="76" t="n"/>
+      <c r="Q45" s="127" t="n"/>
+      <c r="R45" s="75" t="n"/>
       <c r="S45" s="76" t="n"/>
       <c r="T45" s="76" t="n"/>
       <c r="U45" s="76" t="n"/>
@@ -5096,8 +5116,8 @@
       <c r="AF45" s="76" t="n"/>
       <c r="AG45" s="76" t="n"/>
       <c r="AH45" s="77" t="n"/>
-      <c r="AJ45" s="119" t="n"/>
-      <c r="AK45" s="120" t="n"/>
+      <c r="AJ45" s="125" t="n"/>
+      <c r="AK45" s="126" t="n"/>
       <c r="AL45" s="13" t="n"/>
       <c r="AM45" s="14" t="n"/>
       <c r="AN45" s="14" t="n"/>
@@ -5133,7 +5153,7 @@
       <c r="BR45" s="76" t="n"/>
       <c r="BS45" s="76" t="n"/>
       <c r="BT45" s="76" t="n"/>
-      <c r="BU45" s="121" t="n"/>
+      <c r="BU45" s="127" t="n"/>
       <c r="BV45" s="13" t="n"/>
       <c r="BW45" s="14" t="n"/>
       <c r="BX45" s="14" t="n"/>
@@ -5167,13 +5187,13 @@
       <c r="I46" s="67" t="n"/>
       <c r="J46" s="67" t="n"/>
       <c r="K46" s="67" t="n"/>
-      <c r="L46" s="122" t="n"/>
-      <c r="M46" s="102" t="n"/>
+      <c r="L46" s="128" t="n"/>
+      <c r="M46" s="129" t="n"/>
       <c r="N46" s="67" t="n"/>
       <c r="O46" s="67" t="n"/>
       <c r="P46" s="67" t="n"/>
-      <c r="Q46" s="67" t="n"/>
-      <c r="R46" s="67" t="n"/>
+      <c r="Q46" s="128" t="n"/>
+      <c r="R46" s="102" t="n"/>
       <c r="S46" s="67" t="n"/>
       <c r="T46" s="67" t="n"/>
       <c r="U46" s="67" t="n"/>
@@ -5190,19 +5210,19 @@
       <c r="AF46" s="67" t="n"/>
       <c r="AG46" s="67" t="n"/>
       <c r="AH46" s="68" t="n"/>
-      <c r="AJ46" s="114" t="inlineStr">
+      <c r="AJ46" s="117" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="AK46" s="115" t="n"/>
+      <c r="AK46" s="118" t="n"/>
       <c r="AL46" s="6" t="n"/>
       <c r="AM46" s="7" t="n"/>
       <c r="AN46" s="7" t="n"/>
       <c r="AO46" s="7" t="n"/>
       <c r="AP46" s="7" t="n"/>
       <c r="AQ46" s="8" t="n"/>
-      <c r="AR46" s="116" t="inlineStr">
+      <c r="AR46" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -5235,12 +5255,12 @@
       <c r="BR46" s="67" t="n"/>
       <c r="BS46" s="67" t="n"/>
       <c r="BT46" s="67" t="n"/>
-      <c r="BU46" s="117" t="inlineStr">
+      <c r="BU46" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV46" s="118" t="n"/>
+      <c r="BV46" s="121" t="n"/>
       <c r="BW46" s="7" t="n"/>
       <c r="BX46" s="7" t="n"/>
       <c r="BY46" s="7" t="n"/>
@@ -5250,7 +5270,7 @@
       <c r="CC46" s="7" t="n"/>
       <c r="CD46" s="7" t="n"/>
       <c r="CE46" s="8" t="n"/>
-      <c r="CF46" s="118" t="n"/>
+      <c r="CF46" s="121" t="n"/>
       <c r="CG46" s="7" t="n"/>
       <c r="CH46" s="7" t="n"/>
       <c r="CI46" s="7" t="n"/>
@@ -5269,13 +5289,13 @@
       <c r="I47" s="76" t="n"/>
       <c r="J47" s="76" t="n"/>
       <c r="K47" s="76" t="n"/>
-      <c r="L47" s="121" t="n"/>
+      <c r="L47" s="127" t="n"/>
       <c r="M47" s="75" t="n"/>
       <c r="N47" s="76" t="n"/>
       <c r="O47" s="76" t="n"/>
       <c r="P47" s="76" t="n"/>
-      <c r="Q47" s="76" t="n"/>
-      <c r="R47" s="76" t="n"/>
+      <c r="Q47" s="127" t="n"/>
+      <c r="R47" s="75" t="n"/>
       <c r="S47" s="76" t="n"/>
       <c r="T47" s="76" t="n"/>
       <c r="U47" s="76" t="n"/>
@@ -5292,8 +5312,8 @@
       <c r="AF47" s="76" t="n"/>
       <c r="AG47" s="76" t="n"/>
       <c r="AH47" s="77" t="n"/>
-      <c r="AJ47" s="119" t="n"/>
-      <c r="AK47" s="120" t="n"/>
+      <c r="AJ47" s="125" t="n"/>
+      <c r="AK47" s="126" t="n"/>
       <c r="AL47" s="13" t="n"/>
       <c r="AM47" s="14" t="n"/>
       <c r="AN47" s="14" t="n"/>
@@ -5329,7 +5349,7 @@
       <c r="BR47" s="76" t="n"/>
       <c r="BS47" s="76" t="n"/>
       <c r="BT47" s="76" t="n"/>
-      <c r="BU47" s="121" t="n"/>
+      <c r="BU47" s="127" t="n"/>
       <c r="BV47" s="13" t="n"/>
       <c r="BW47" s="14" t="n"/>
       <c r="BX47" s="14" t="n"/>
@@ -5363,13 +5383,13 @@
       <c r="I48" s="67" t="n"/>
       <c r="J48" s="67" t="n"/>
       <c r="K48" s="67" t="n"/>
-      <c r="L48" s="122" t="n"/>
-      <c r="M48" s="102" t="n"/>
+      <c r="L48" s="128" t="n"/>
+      <c r="M48" s="129" t="n"/>
       <c r="N48" s="67" t="n"/>
       <c r="O48" s="67" t="n"/>
       <c r="P48" s="67" t="n"/>
-      <c r="Q48" s="67" t="n"/>
-      <c r="R48" s="67" t="n"/>
+      <c r="Q48" s="128" t="n"/>
+      <c r="R48" s="102" t="n"/>
       <c r="S48" s="67" t="n"/>
       <c r="T48" s="67" t="n"/>
       <c r="U48" s="67" t="n"/>
@@ -5386,19 +5406,19 @@
       <c r="AF48" s="67" t="n"/>
       <c r="AG48" s="67" t="n"/>
       <c r="AH48" s="68" t="n"/>
-      <c r="AJ48" s="114" t="inlineStr">
+      <c r="AJ48" s="117" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="AK48" s="115" t="n"/>
+      <c r="AK48" s="118" t="n"/>
       <c r="AL48" s="6" t="n"/>
       <c r="AM48" s="7" t="n"/>
       <c r="AN48" s="7" t="n"/>
       <c r="AO48" s="7" t="n"/>
       <c r="AP48" s="7" t="n"/>
       <c r="AQ48" s="8" t="n"/>
-      <c r="AR48" s="116" t="inlineStr">
+      <c r="AR48" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -5431,12 +5451,12 @@
       <c r="BR48" s="67" t="n"/>
       <c r="BS48" s="67" t="n"/>
       <c r="BT48" s="67" t="n"/>
-      <c r="BU48" s="117" t="inlineStr">
+      <c r="BU48" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV48" s="118" t="n"/>
+      <c r="BV48" s="121" t="n"/>
       <c r="BW48" s="7" t="n"/>
       <c r="BX48" s="7" t="n"/>
       <c r="BY48" s="7" t="n"/>
@@ -5446,7 +5466,7 @@
       <c r="CC48" s="7" t="n"/>
       <c r="CD48" s="7" t="n"/>
       <c r="CE48" s="8" t="n"/>
-      <c r="CF48" s="118" t="n"/>
+      <c r="CF48" s="121" t="n"/>
       <c r="CG48" s="7" t="n"/>
       <c r="CH48" s="7" t="n"/>
       <c r="CI48" s="7" t="n"/>
@@ -5465,13 +5485,13 @@
       <c r="I49" s="76" t="n"/>
       <c r="J49" s="76" t="n"/>
       <c r="K49" s="76" t="n"/>
-      <c r="L49" s="121" t="n"/>
+      <c r="L49" s="127" t="n"/>
       <c r="M49" s="75" t="n"/>
       <c r="N49" s="76" t="n"/>
       <c r="O49" s="76" t="n"/>
       <c r="P49" s="76" t="n"/>
-      <c r="Q49" s="76" t="n"/>
-      <c r="R49" s="76" t="n"/>
+      <c r="Q49" s="127" t="n"/>
+      <c r="R49" s="75" t="n"/>
       <c r="S49" s="76" t="n"/>
       <c r="T49" s="76" t="n"/>
       <c r="U49" s="76" t="n"/>
@@ -5488,8 +5508,8 @@
       <c r="AF49" s="76" t="n"/>
       <c r="AG49" s="76" t="n"/>
       <c r="AH49" s="77" t="n"/>
-      <c r="AJ49" s="119" t="n"/>
-      <c r="AK49" s="120" t="n"/>
+      <c r="AJ49" s="125" t="n"/>
+      <c r="AK49" s="126" t="n"/>
       <c r="AL49" s="13" t="n"/>
       <c r="AM49" s="14" t="n"/>
       <c r="AN49" s="14" t="n"/>
@@ -5525,7 +5545,7 @@
       <c r="BR49" s="76" t="n"/>
       <c r="BS49" s="76" t="n"/>
       <c r="BT49" s="76" t="n"/>
-      <c r="BU49" s="121" t="n"/>
+      <c r="BU49" s="127" t="n"/>
       <c r="BV49" s="13" t="n"/>
       <c r="BW49" s="14" t="n"/>
       <c r="BX49" s="14" t="n"/>
@@ -5559,13 +5579,13 @@
       <c r="I50" s="67" t="n"/>
       <c r="J50" s="67" t="n"/>
       <c r="K50" s="67" t="n"/>
-      <c r="L50" s="122" t="n"/>
-      <c r="M50" s="102" t="n"/>
+      <c r="L50" s="128" t="n"/>
+      <c r="M50" s="129" t="n"/>
       <c r="N50" s="67" t="n"/>
       <c r="O50" s="67" t="n"/>
       <c r="P50" s="67" t="n"/>
-      <c r="Q50" s="67" t="n"/>
-      <c r="R50" s="67" t="n"/>
+      <c r="Q50" s="128" t="n"/>
+      <c r="R50" s="102" t="n"/>
       <c r="S50" s="67" t="n"/>
       <c r="T50" s="67" t="n"/>
       <c r="U50" s="67" t="n"/>
@@ -5582,19 +5602,19 @@
       <c r="AF50" s="67" t="n"/>
       <c r="AG50" s="67" t="n"/>
       <c r="AH50" s="68" t="n"/>
-      <c r="AJ50" s="114" t="inlineStr">
+      <c r="AJ50" s="117" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
       </c>
-      <c r="AK50" s="115" t="n"/>
+      <c r="AK50" s="118" t="n"/>
       <c r="AL50" s="6" t="n"/>
       <c r="AM50" s="7" t="n"/>
       <c r="AN50" s="7" t="n"/>
       <c r="AO50" s="7" t="n"/>
       <c r="AP50" s="7" t="n"/>
       <c r="AQ50" s="8" t="n"/>
-      <c r="AR50" s="116" t="inlineStr">
+      <c r="AR50" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -5627,12 +5647,12 @@
       <c r="BR50" s="67" t="n"/>
       <c r="BS50" s="67" t="n"/>
       <c r="BT50" s="67" t="n"/>
-      <c r="BU50" s="117" t="inlineStr">
+      <c r="BU50" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV50" s="118" t="n"/>
+      <c r="BV50" s="121" t="n"/>
       <c r="BW50" s="7" t="n"/>
       <c r="BX50" s="7" t="n"/>
       <c r="BY50" s="7" t="n"/>
@@ -5642,7 +5662,7 @@
       <c r="CC50" s="7" t="n"/>
       <c r="CD50" s="7" t="n"/>
       <c r="CE50" s="8" t="n"/>
-      <c r="CF50" s="118" t="n"/>
+      <c r="CF50" s="121" t="n"/>
       <c r="CG50" s="7" t="n"/>
       <c r="CH50" s="7" t="n"/>
       <c r="CI50" s="7" t="n"/>
@@ -5661,13 +5681,13 @@
       <c r="I51" s="76" t="n"/>
       <c r="J51" s="76" t="n"/>
       <c r="K51" s="76" t="n"/>
-      <c r="L51" s="121" t="n"/>
+      <c r="L51" s="127" t="n"/>
       <c r="M51" s="75" t="n"/>
       <c r="N51" s="76" t="n"/>
       <c r="O51" s="76" t="n"/>
       <c r="P51" s="76" t="n"/>
-      <c r="Q51" s="76" t="n"/>
-      <c r="R51" s="76" t="n"/>
+      <c r="Q51" s="127" t="n"/>
+      <c r="R51" s="75" t="n"/>
       <c r="S51" s="76" t="n"/>
       <c r="T51" s="76" t="n"/>
       <c r="U51" s="76" t="n"/>
@@ -5684,8 +5704,8 @@
       <c r="AF51" s="76" t="n"/>
       <c r="AG51" s="76" t="n"/>
       <c r="AH51" s="77" t="n"/>
-      <c r="AJ51" s="119" t="n"/>
-      <c r="AK51" s="120" t="n"/>
+      <c r="AJ51" s="125" t="n"/>
+      <c r="AK51" s="126" t="n"/>
       <c r="AL51" s="13" t="n"/>
       <c r="AM51" s="14" t="n"/>
       <c r="AN51" s="14" t="n"/>
@@ -5721,7 +5741,7 @@
       <c r="BR51" s="76" t="n"/>
       <c r="BS51" s="76" t="n"/>
       <c r="BT51" s="76" t="n"/>
-      <c r="BU51" s="121" t="n"/>
+      <c r="BU51" s="127" t="n"/>
       <c r="BV51" s="13" t="n"/>
       <c r="BW51" s="14" t="n"/>
       <c r="BX51" s="14" t="n"/>
@@ -5755,13 +5775,13 @@
       <c r="I52" s="67" t="n"/>
       <c r="J52" s="67" t="n"/>
       <c r="K52" s="67" t="n"/>
-      <c r="L52" s="122" t="n"/>
-      <c r="M52" s="102" t="n"/>
+      <c r="L52" s="128" t="n"/>
+      <c r="M52" s="129" t="n"/>
       <c r="N52" s="67" t="n"/>
       <c r="O52" s="67" t="n"/>
       <c r="P52" s="67" t="n"/>
-      <c r="Q52" s="67" t="n"/>
-      <c r="R52" s="67" t="n"/>
+      <c r="Q52" s="128" t="n"/>
+      <c r="R52" s="102" t="n"/>
       <c r="S52" s="67" t="n"/>
       <c r="T52" s="67" t="n"/>
       <c r="U52" s="67" t="n"/>
@@ -5778,19 +5798,19 @@
       <c r="AF52" s="67" t="n"/>
       <c r="AG52" s="67" t="n"/>
       <c r="AH52" s="68" t="n"/>
-      <c r="AJ52" s="114" t="inlineStr">
+      <c r="AJ52" s="117" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
       </c>
-      <c r="AK52" s="115" t="n"/>
+      <c r="AK52" s="118" t="n"/>
       <c r="AL52" s="6" t="n"/>
       <c r="AM52" s="7" t="n"/>
       <c r="AN52" s="7" t="n"/>
       <c r="AO52" s="7" t="n"/>
       <c r="AP52" s="7" t="n"/>
       <c r="AQ52" s="8" t="n"/>
-      <c r="AR52" s="116" t="inlineStr">
+      <c r="AR52" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -5823,12 +5843,12 @@
       <c r="BR52" s="67" t="n"/>
       <c r="BS52" s="67" t="n"/>
       <c r="BT52" s="67" t="n"/>
-      <c r="BU52" s="117" t="inlineStr">
+      <c r="BU52" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV52" s="118" t="n"/>
+      <c r="BV52" s="121" t="n"/>
       <c r="BW52" s="7" t="n"/>
       <c r="BX52" s="7" t="n"/>
       <c r="BY52" s="7" t="n"/>
@@ -5838,7 +5858,7 @@
       <c r="CC52" s="7" t="n"/>
       <c r="CD52" s="7" t="n"/>
       <c r="CE52" s="8" t="n"/>
-      <c r="CF52" s="118" t="n"/>
+      <c r="CF52" s="121" t="n"/>
       <c r="CG52" s="7" t="n"/>
       <c r="CH52" s="7" t="n"/>
       <c r="CI52" s="7" t="n"/>
@@ -5857,13 +5877,13 @@
       <c r="I53" s="76" t="n"/>
       <c r="J53" s="76" t="n"/>
       <c r="K53" s="76" t="n"/>
-      <c r="L53" s="121" t="n"/>
+      <c r="L53" s="127" t="n"/>
       <c r="M53" s="75" t="n"/>
       <c r="N53" s="76" t="n"/>
       <c r="O53" s="76" t="n"/>
       <c r="P53" s="76" t="n"/>
-      <c r="Q53" s="76" t="n"/>
-      <c r="R53" s="76" t="n"/>
+      <c r="Q53" s="127" t="n"/>
+      <c r="R53" s="75" t="n"/>
       <c r="S53" s="76" t="n"/>
       <c r="T53" s="76" t="n"/>
       <c r="U53" s="76" t="n"/>
@@ -5880,8 +5900,8 @@
       <c r="AF53" s="76" t="n"/>
       <c r="AG53" s="76" t="n"/>
       <c r="AH53" s="77" t="n"/>
-      <c r="AJ53" s="119" t="n"/>
-      <c r="AK53" s="120" t="n"/>
+      <c r="AJ53" s="125" t="n"/>
+      <c r="AK53" s="126" t="n"/>
       <c r="AL53" s="13" t="n"/>
       <c r="AM53" s="14" t="n"/>
       <c r="AN53" s="14" t="n"/>
@@ -5917,7 +5937,7 @@
       <c r="BR53" s="76" t="n"/>
       <c r="BS53" s="76" t="n"/>
       <c r="BT53" s="76" t="n"/>
-      <c r="BU53" s="121" t="n"/>
+      <c r="BU53" s="127" t="n"/>
       <c r="BV53" s="13" t="n"/>
       <c r="BW53" s="14" t="n"/>
       <c r="BX53" s="14" t="n"/>
@@ -5951,13 +5971,13 @@
       <c r="I54" s="67" t="n"/>
       <c r="J54" s="67" t="n"/>
       <c r="K54" s="67" t="n"/>
-      <c r="L54" s="122" t="n"/>
-      <c r="M54" s="102" t="n"/>
+      <c r="L54" s="128" t="n"/>
+      <c r="M54" s="129" t="n"/>
       <c r="N54" s="67" t="n"/>
       <c r="O54" s="67" t="n"/>
       <c r="P54" s="67" t="n"/>
-      <c r="Q54" s="67" t="n"/>
-      <c r="R54" s="67" t="n"/>
+      <c r="Q54" s="128" t="n"/>
+      <c r="R54" s="102" t="n"/>
       <c r="S54" s="67" t="n"/>
       <c r="T54" s="67" t="n"/>
       <c r="U54" s="67" t="n"/>
@@ -5974,19 +5994,19 @@
       <c r="AF54" s="67" t="n"/>
       <c r="AG54" s="67" t="n"/>
       <c r="AH54" s="68" t="n"/>
-      <c r="AJ54" s="114" t="inlineStr">
+      <c r="AJ54" s="117" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
       </c>
-      <c r="AK54" s="115" t="n"/>
+      <c r="AK54" s="118" t="n"/>
       <c r="AL54" s="6" t="n"/>
       <c r="AM54" s="7" t="n"/>
       <c r="AN54" s="7" t="n"/>
       <c r="AO54" s="7" t="n"/>
       <c r="AP54" s="7" t="n"/>
       <c r="AQ54" s="8" t="n"/>
-      <c r="AR54" s="116" t="inlineStr">
+      <c r="AR54" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -6019,12 +6039,12 @@
       <c r="BR54" s="67" t="n"/>
       <c r="BS54" s="67" t="n"/>
       <c r="BT54" s="67" t="n"/>
-      <c r="BU54" s="117" t="inlineStr">
+      <c r="BU54" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV54" s="118" t="n"/>
+      <c r="BV54" s="121" t="n"/>
       <c r="BW54" s="7" t="n"/>
       <c r="BX54" s="7" t="n"/>
       <c r="BY54" s="7" t="n"/>
@@ -6034,7 +6054,7 @@
       <c r="CC54" s="7" t="n"/>
       <c r="CD54" s="7" t="n"/>
       <c r="CE54" s="8" t="n"/>
-      <c r="CF54" s="118" t="n"/>
+      <c r="CF54" s="121" t="n"/>
       <c r="CG54" s="7" t="n"/>
       <c r="CH54" s="7" t="n"/>
       <c r="CI54" s="7" t="n"/>
@@ -6053,13 +6073,13 @@
       <c r="I55" s="76" t="n"/>
       <c r="J55" s="76" t="n"/>
       <c r="K55" s="76" t="n"/>
-      <c r="L55" s="121" t="n"/>
+      <c r="L55" s="127" t="n"/>
       <c r="M55" s="75" t="n"/>
       <c r="N55" s="76" t="n"/>
       <c r="O55" s="76" t="n"/>
       <c r="P55" s="76" t="n"/>
-      <c r="Q55" s="76" t="n"/>
-      <c r="R55" s="76" t="n"/>
+      <c r="Q55" s="127" t="n"/>
+      <c r="R55" s="75" t="n"/>
       <c r="S55" s="76" t="n"/>
       <c r="T55" s="76" t="n"/>
       <c r="U55" s="76" t="n"/>
@@ -6076,8 +6096,8 @@
       <c r="AF55" s="76" t="n"/>
       <c r="AG55" s="76" t="n"/>
       <c r="AH55" s="77" t="n"/>
-      <c r="AJ55" s="119" t="n"/>
-      <c r="AK55" s="120" t="n"/>
+      <c r="AJ55" s="125" t="n"/>
+      <c r="AK55" s="126" t="n"/>
       <c r="AL55" s="13" t="n"/>
       <c r="AM55" s="14" t="n"/>
       <c r="AN55" s="14" t="n"/>
@@ -6113,7 +6133,7 @@
       <c r="BR55" s="76" t="n"/>
       <c r="BS55" s="76" t="n"/>
       <c r="BT55" s="76" t="n"/>
-      <c r="BU55" s="121" t="n"/>
+      <c r="BU55" s="127" t="n"/>
       <c r="BV55" s="13" t="n"/>
       <c r="BW55" s="14" t="n"/>
       <c r="BX55" s="14" t="n"/>
@@ -6147,13 +6167,13 @@
       <c r="I56" s="67" t="n"/>
       <c r="J56" s="67" t="n"/>
       <c r="K56" s="67" t="n"/>
-      <c r="L56" s="122" t="n"/>
-      <c r="M56" s="102" t="n"/>
+      <c r="L56" s="128" t="n"/>
+      <c r="M56" s="129" t="n"/>
       <c r="N56" s="67" t="n"/>
       <c r="O56" s="67" t="n"/>
       <c r="P56" s="67" t="n"/>
-      <c r="Q56" s="67" t="n"/>
-      <c r="R56" s="67" t="n"/>
+      <c r="Q56" s="128" t="n"/>
+      <c r="R56" s="102" t="n"/>
       <c r="S56" s="67" t="n"/>
       <c r="T56" s="67" t="n"/>
       <c r="U56" s="67" t="n"/>
@@ -6170,19 +6190,19 @@
       <c r="AF56" s="67" t="n"/>
       <c r="AG56" s="67" t="n"/>
       <c r="AH56" s="68" t="n"/>
-      <c r="AJ56" s="114" t="inlineStr">
+      <c r="AJ56" s="117" t="inlineStr">
         <is>
           <t>⑧</t>
         </is>
       </c>
-      <c r="AK56" s="115" t="n"/>
+      <c r="AK56" s="118" t="n"/>
       <c r="AL56" s="6" t="n"/>
       <c r="AM56" s="7" t="n"/>
       <c r="AN56" s="7" t="n"/>
       <c r="AO56" s="7" t="n"/>
       <c r="AP56" s="7" t="n"/>
       <c r="AQ56" s="8" t="n"/>
-      <c r="AR56" s="116" t="inlineStr">
+      <c r="AR56" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -6215,12 +6235,12 @@
       <c r="BR56" s="67" t="n"/>
       <c r="BS56" s="67" t="n"/>
       <c r="BT56" s="67" t="n"/>
-      <c r="BU56" s="117" t="inlineStr">
+      <c r="BU56" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV56" s="118" t="n"/>
+      <c r="BV56" s="121" t="n"/>
       <c r="BW56" s="7" t="n"/>
       <c r="BX56" s="7" t="n"/>
       <c r="BY56" s="7" t="n"/>
@@ -6230,7 +6250,7 @@
       <c r="CC56" s="7" t="n"/>
       <c r="CD56" s="7" t="n"/>
       <c r="CE56" s="8" t="n"/>
-      <c r="CF56" s="118" t="n"/>
+      <c r="CF56" s="121" t="n"/>
       <c r="CG56" s="7" t="n"/>
       <c r="CH56" s="7" t="n"/>
       <c r="CI56" s="7" t="n"/>
@@ -6249,13 +6269,13 @@
       <c r="I57" s="76" t="n"/>
       <c r="J57" s="76" t="n"/>
       <c r="K57" s="76" t="n"/>
-      <c r="L57" s="121" t="n"/>
+      <c r="L57" s="127" t="n"/>
       <c r="M57" s="75" t="n"/>
       <c r="N57" s="76" t="n"/>
       <c r="O57" s="76" t="n"/>
       <c r="P57" s="76" t="n"/>
-      <c r="Q57" s="76" t="n"/>
-      <c r="R57" s="76" t="n"/>
+      <c r="Q57" s="127" t="n"/>
+      <c r="R57" s="75" t="n"/>
       <c r="S57" s="76" t="n"/>
       <c r="T57" s="76" t="n"/>
       <c r="U57" s="76" t="n"/>
@@ -6272,8 +6292,8 @@
       <c r="AF57" s="76" t="n"/>
       <c r="AG57" s="76" t="n"/>
       <c r="AH57" s="77" t="n"/>
-      <c r="AJ57" s="119" t="n"/>
-      <c r="AK57" s="120" t="n"/>
+      <c r="AJ57" s="125" t="n"/>
+      <c r="AK57" s="126" t="n"/>
       <c r="AL57" s="13" t="n"/>
       <c r="AM57" s="14" t="n"/>
       <c r="AN57" s="14" t="n"/>
@@ -6309,7 +6329,7 @@
       <c r="BR57" s="76" t="n"/>
       <c r="BS57" s="76" t="n"/>
       <c r="BT57" s="76" t="n"/>
-      <c r="BU57" s="121" t="n"/>
+      <c r="BU57" s="127" t="n"/>
       <c r="BV57" s="13" t="n"/>
       <c r="BW57" s="14" t="n"/>
       <c r="BX57" s="14" t="n"/>
@@ -6343,13 +6363,13 @@
       <c r="I58" s="67" t="n"/>
       <c r="J58" s="67" t="n"/>
       <c r="K58" s="67" t="n"/>
-      <c r="L58" s="122" t="n"/>
-      <c r="M58" s="102" t="n"/>
+      <c r="L58" s="128" t="n"/>
+      <c r="M58" s="129" t="n"/>
       <c r="N58" s="67" t="n"/>
       <c r="O58" s="67" t="n"/>
       <c r="P58" s="67" t="n"/>
-      <c r="Q58" s="67" t="n"/>
-      <c r="R58" s="67" t="n"/>
+      <c r="Q58" s="128" t="n"/>
+      <c r="R58" s="102" t="n"/>
       <c r="S58" s="67" t="n"/>
       <c r="T58" s="67" t="n"/>
       <c r="U58" s="67" t="n"/>
@@ -6366,19 +6386,19 @@
       <c r="AF58" s="67" t="n"/>
       <c r="AG58" s="67" t="n"/>
       <c r="AH58" s="68" t="n"/>
-      <c r="AJ58" s="114" t="inlineStr">
+      <c r="AJ58" s="117" t="inlineStr">
         <is>
           <t>⑨</t>
         </is>
       </c>
-      <c r="AK58" s="115" t="n"/>
+      <c r="AK58" s="118" t="n"/>
       <c r="AL58" s="6" t="n"/>
       <c r="AM58" s="7" t="n"/>
       <c r="AN58" s="7" t="n"/>
       <c r="AO58" s="7" t="n"/>
       <c r="AP58" s="7" t="n"/>
       <c r="AQ58" s="8" t="n"/>
-      <c r="AR58" s="116" t="inlineStr">
+      <c r="AR58" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -6411,12 +6431,12 @@
       <c r="BR58" s="67" t="n"/>
       <c r="BS58" s="67" t="n"/>
       <c r="BT58" s="67" t="n"/>
-      <c r="BU58" s="117" t="inlineStr">
+      <c r="BU58" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV58" s="118" t="n"/>
+      <c r="BV58" s="121" t="n"/>
       <c r="BW58" s="7" t="n"/>
       <c r="BX58" s="7" t="n"/>
       <c r="BY58" s="7" t="n"/>
@@ -6426,7 +6446,7 @@
       <c r="CC58" s="7" t="n"/>
       <c r="CD58" s="7" t="n"/>
       <c r="CE58" s="8" t="n"/>
-      <c r="CF58" s="118" t="n"/>
+      <c r="CF58" s="121" t="n"/>
       <c r="CG58" s="7" t="n"/>
       <c r="CH58" s="7" t="n"/>
       <c r="CI58" s="7" t="n"/>
@@ -6445,13 +6465,13 @@
       <c r="I59" s="76" t="n"/>
       <c r="J59" s="76" t="n"/>
       <c r="K59" s="76" t="n"/>
-      <c r="L59" s="121" t="n"/>
+      <c r="L59" s="127" t="n"/>
       <c r="M59" s="75" t="n"/>
       <c r="N59" s="76" t="n"/>
       <c r="O59" s="76" t="n"/>
       <c r="P59" s="76" t="n"/>
-      <c r="Q59" s="76" t="n"/>
-      <c r="R59" s="76" t="n"/>
+      <c r="Q59" s="127" t="n"/>
+      <c r="R59" s="75" t="n"/>
       <c r="S59" s="76" t="n"/>
       <c r="T59" s="76" t="n"/>
       <c r="U59" s="76" t="n"/>
@@ -6468,8 +6488,8 @@
       <c r="AF59" s="76" t="n"/>
       <c r="AG59" s="76" t="n"/>
       <c r="AH59" s="77" t="n"/>
-      <c r="AJ59" s="119" t="n"/>
-      <c r="AK59" s="120" t="n"/>
+      <c r="AJ59" s="125" t="n"/>
+      <c r="AK59" s="126" t="n"/>
       <c r="AL59" s="13" t="n"/>
       <c r="AM59" s="14" t="n"/>
       <c r="AN59" s="14" t="n"/>
@@ -6505,7 +6525,7 @@
       <c r="BR59" s="76" t="n"/>
       <c r="BS59" s="76" t="n"/>
       <c r="BT59" s="76" t="n"/>
-      <c r="BU59" s="121" t="n"/>
+      <c r="BU59" s="127" t="n"/>
       <c r="BV59" s="13" t="n"/>
       <c r="BW59" s="14" t="n"/>
       <c r="BX59" s="14" t="n"/>
@@ -6539,13 +6559,13 @@
       <c r="I60" s="67" t="n"/>
       <c r="J60" s="67" t="n"/>
       <c r="K60" s="67" t="n"/>
-      <c r="L60" s="122" t="n"/>
-      <c r="M60" s="102" t="n"/>
+      <c r="L60" s="128" t="n"/>
+      <c r="M60" s="129" t="n"/>
       <c r="N60" s="67" t="n"/>
       <c r="O60" s="67" t="n"/>
       <c r="P60" s="67" t="n"/>
-      <c r="Q60" s="67" t="n"/>
-      <c r="R60" s="67" t="n"/>
+      <c r="Q60" s="128" t="n"/>
+      <c r="R60" s="102" t="n"/>
       <c r="S60" s="67" t="n"/>
       <c r="T60" s="67" t="n"/>
       <c r="U60" s="67" t="n"/>
@@ -6562,19 +6582,19 @@
       <c r="AF60" s="67" t="n"/>
       <c r="AG60" s="67" t="n"/>
       <c r="AH60" s="68" t="n"/>
-      <c r="AJ60" s="114" t="inlineStr">
+      <c r="AJ60" s="117" t="inlineStr">
         <is>
           <t>⑩</t>
         </is>
       </c>
-      <c r="AK60" s="115" t="n"/>
+      <c r="AK60" s="118" t="n"/>
       <c r="AL60" s="6" t="n"/>
       <c r="AM60" s="7" t="n"/>
       <c r="AN60" s="7" t="n"/>
       <c r="AO60" s="7" t="n"/>
       <c r="AP60" s="7" t="n"/>
       <c r="AQ60" s="8" t="n"/>
-      <c r="AR60" s="116" t="inlineStr">
+      <c r="AR60" s="119" t="inlineStr">
         <is>
           <t>手すり　段差の解消　その他（</t>
         </is>
@@ -6607,12 +6627,12 @@
       <c r="BR60" s="67" t="n"/>
       <c r="BS60" s="67" t="n"/>
       <c r="BT60" s="67" t="n"/>
-      <c r="BU60" s="117" t="inlineStr">
+      <c r="BU60" s="120" t="inlineStr">
         <is>
           <t>）</t>
         </is>
       </c>
-      <c r="BV60" s="118" t="n"/>
+      <c r="BV60" s="121" t="n"/>
       <c r="BW60" s="7" t="n"/>
       <c r="BX60" s="7" t="n"/>
       <c r="BY60" s="7" t="n"/>
@@ -6622,7 +6642,7 @@
       <c r="CC60" s="7" t="n"/>
       <c r="CD60" s="7" t="n"/>
       <c r="CE60" s="8" t="n"/>
-      <c r="CF60" s="118" t="n"/>
+      <c r="CF60" s="121" t="n"/>
       <c r="CG60" s="7" t="n"/>
       <c r="CH60" s="7" t="n"/>
       <c r="CI60" s="7" t="n"/>
@@ -6630,135 +6650,139 @@
       <c r="CK60" s="37" t="n"/>
     </row>
     <row r="61" ht="9" customHeight="1">
-      <c r="A61" s="123" t="n"/>
-      <c r="B61" s="124" t="n"/>
-      <c r="C61" s="125" t="n"/>
-      <c r="D61" s="126" t="n"/>
-      <c r="E61" s="126" t="n"/>
-      <c r="F61" s="126" t="n"/>
-      <c r="G61" s="126" t="n"/>
-      <c r="H61" s="126" t="n"/>
-      <c r="I61" s="126" t="n"/>
-      <c r="J61" s="126" t="n"/>
-      <c r="K61" s="126" t="n"/>
-      <c r="L61" s="127" t="n"/>
-      <c r="M61" s="125" t="n"/>
-      <c r="N61" s="126" t="n"/>
-      <c r="O61" s="126" t="n"/>
-      <c r="P61" s="126" t="n"/>
-      <c r="Q61" s="126" t="n"/>
-      <c r="R61" s="126" t="n"/>
-      <c r="S61" s="126" t="n"/>
-      <c r="T61" s="126" t="n"/>
-      <c r="U61" s="126" t="n"/>
-      <c r="V61" s="126" t="n"/>
-      <c r="W61" s="126" t="n"/>
-      <c r="X61" s="126" t="n"/>
-      <c r="Y61" s="126" t="n"/>
-      <c r="Z61" s="126" t="n"/>
-      <c r="AA61" s="126" t="n"/>
-      <c r="AB61" s="126" t="n"/>
-      <c r="AC61" s="126" t="n"/>
-      <c r="AD61" s="126" t="n"/>
-      <c r="AE61" s="126" t="n"/>
-      <c r="AF61" s="126" t="n"/>
-      <c r="AG61" s="126" t="n"/>
-      <c r="AH61" s="128" t="n"/>
-      <c r="AJ61" s="129" t="n"/>
-      <c r="AK61" s="130" t="n"/>
-      <c r="AL61" s="131" t="n"/>
-      <c r="AM61" s="132" t="n"/>
-      <c r="AN61" s="132" t="n"/>
-      <c r="AO61" s="132" t="n"/>
-      <c r="AP61" s="132" t="n"/>
-      <c r="AQ61" s="133" t="n"/>
-      <c r="AR61" s="125" t="n"/>
-      <c r="AS61" s="126" t="n"/>
-      <c r="AT61" s="126" t="n"/>
-      <c r="AU61" s="126" t="n"/>
-      <c r="AV61" s="126" t="n"/>
-      <c r="AW61" s="126" t="n"/>
-      <c r="AX61" s="126" t="n"/>
-      <c r="AY61" s="126" t="n"/>
-      <c r="AZ61" s="126" t="n"/>
-      <c r="BA61" s="126" t="n"/>
-      <c r="BB61" s="126" t="n"/>
-      <c r="BC61" s="126" t="n"/>
-      <c r="BD61" s="126" t="n"/>
-      <c r="BE61" s="126" t="n"/>
-      <c r="BF61" s="126" t="n"/>
-      <c r="BG61" s="126" t="n"/>
-      <c r="BH61" s="126" t="n"/>
-      <c r="BI61" s="126" t="n"/>
-      <c r="BJ61" s="126" t="n"/>
-      <c r="BK61" s="126" t="n"/>
-      <c r="BL61" s="126" t="n"/>
-      <c r="BM61" s="126" t="n"/>
-      <c r="BN61" s="126" t="n"/>
-      <c r="BO61" s="126" t="n"/>
-      <c r="BP61" s="126" t="n"/>
-      <c r="BQ61" s="126" t="n"/>
-      <c r="BR61" s="126" t="n"/>
-      <c r="BS61" s="126" t="n"/>
-      <c r="BT61" s="126" t="n"/>
-      <c r="BU61" s="127" t="n"/>
-      <c r="BV61" s="131" t="n"/>
-      <c r="BW61" s="132" t="n"/>
-      <c r="BX61" s="132" t="n"/>
-      <c r="BY61" s="132" t="n"/>
-      <c r="BZ61" s="132" t="n"/>
-      <c r="CA61" s="132" t="n"/>
-      <c r="CB61" s="132" t="n"/>
-      <c r="CC61" s="132" t="n"/>
-      <c r="CD61" s="132" t="n"/>
-      <c r="CE61" s="133" t="n"/>
-      <c r="CF61" s="131" t="n"/>
-      <c r="CG61" s="132" t="n"/>
-      <c r="CH61" s="132" t="n"/>
-      <c r="CI61" s="132" t="n"/>
-      <c r="CJ61" s="132" t="n"/>
-      <c r="CK61" s="134" t="n"/>
+      <c r="A61" s="130" t="n"/>
+      <c r="B61" s="131" t="n"/>
+      <c r="C61" s="132" t="n"/>
+      <c r="D61" s="133" t="n"/>
+      <c r="E61" s="133" t="n"/>
+      <c r="F61" s="133" t="n"/>
+      <c r="G61" s="133" t="n"/>
+      <c r="H61" s="133" t="n"/>
+      <c r="I61" s="133" t="n"/>
+      <c r="J61" s="133" t="n"/>
+      <c r="K61" s="133" t="n"/>
+      <c r="L61" s="134" t="n"/>
+      <c r="M61" s="132" t="n"/>
+      <c r="N61" s="133" t="n"/>
+      <c r="O61" s="133" t="n"/>
+      <c r="P61" s="133" t="n"/>
+      <c r="Q61" s="134" t="n"/>
+      <c r="R61" s="132" t="n"/>
+      <c r="S61" s="133" t="n"/>
+      <c r="T61" s="133" t="n"/>
+      <c r="U61" s="133" t="n"/>
+      <c r="V61" s="133" t="n"/>
+      <c r="W61" s="133" t="n"/>
+      <c r="X61" s="133" t="n"/>
+      <c r="Y61" s="133" t="n"/>
+      <c r="Z61" s="133" t="n"/>
+      <c r="AA61" s="133" t="n"/>
+      <c r="AB61" s="133" t="n"/>
+      <c r="AC61" s="133" t="n"/>
+      <c r="AD61" s="133" t="n"/>
+      <c r="AE61" s="133" t="n"/>
+      <c r="AF61" s="133" t="n"/>
+      <c r="AG61" s="133" t="n"/>
+      <c r="AH61" s="135" t="n"/>
+      <c r="AJ61" s="136" t="n"/>
+      <c r="AK61" s="137" t="n"/>
+      <c r="AL61" s="138" t="n"/>
+      <c r="AM61" s="139" t="n"/>
+      <c r="AN61" s="139" t="n"/>
+      <c r="AO61" s="139" t="n"/>
+      <c r="AP61" s="139" t="n"/>
+      <c r="AQ61" s="140" t="n"/>
+      <c r="AR61" s="132" t="n"/>
+      <c r="AS61" s="133" t="n"/>
+      <c r="AT61" s="133" t="n"/>
+      <c r="AU61" s="133" t="n"/>
+      <c r="AV61" s="133" t="n"/>
+      <c r="AW61" s="133" t="n"/>
+      <c r="AX61" s="133" t="n"/>
+      <c r="AY61" s="133" t="n"/>
+      <c r="AZ61" s="133" t="n"/>
+      <c r="BA61" s="133" t="n"/>
+      <c r="BB61" s="133" t="n"/>
+      <c r="BC61" s="133" t="n"/>
+      <c r="BD61" s="133" t="n"/>
+      <c r="BE61" s="133" t="n"/>
+      <c r="BF61" s="133" t="n"/>
+      <c r="BG61" s="133" t="n"/>
+      <c r="BH61" s="133" t="n"/>
+      <c r="BI61" s="133" t="n"/>
+      <c r="BJ61" s="133" t="n"/>
+      <c r="BK61" s="133" t="n"/>
+      <c r="BL61" s="133" t="n"/>
+      <c r="BM61" s="133" t="n"/>
+      <c r="BN61" s="133" t="n"/>
+      <c r="BO61" s="133" t="n"/>
+      <c r="BP61" s="133" t="n"/>
+      <c r="BQ61" s="133" t="n"/>
+      <c r="BR61" s="133" t="n"/>
+      <c r="BS61" s="133" t="n"/>
+      <c r="BT61" s="133" t="n"/>
+      <c r="BU61" s="134" t="n"/>
+      <c r="BV61" s="138" t="n"/>
+      <c r="BW61" s="139" t="n"/>
+      <c r="BX61" s="139" t="n"/>
+      <c r="BY61" s="139" t="n"/>
+      <c r="BZ61" s="139" t="n"/>
+      <c r="CA61" s="139" t="n"/>
+      <c r="CB61" s="139" t="n"/>
+      <c r="CC61" s="139" t="n"/>
+      <c r="CD61" s="139" t="n"/>
+      <c r="CE61" s="140" t="n"/>
+      <c r="CF61" s="138" t="n"/>
+      <c r="CG61" s="139" t="n"/>
+      <c r="CH61" s="139" t="n"/>
+      <c r="CI61" s="139" t="n"/>
+      <c r="CJ61" s="139" t="n"/>
+      <c r="CK61" s="141" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="175">
-    <mergeCell ref="M50:AH51"/>
+  <mergeCells count="186">
+    <mergeCell ref="BV58:CE59"/>
     <mergeCell ref="S20:X21"/>
     <mergeCell ref="BG50:BT51"/>
-    <mergeCell ref="BV58:CE59"/>
     <mergeCell ref="BG44:BT45"/>
     <mergeCell ref="CF56:CK57"/>
     <mergeCell ref="AJ6:CK7"/>
     <mergeCell ref="AL54:AQ55"/>
     <mergeCell ref="Q40:X41"/>
     <mergeCell ref="G8:AH9"/>
+    <mergeCell ref="R42:AH43"/>
+    <mergeCell ref="R54:AH55"/>
     <mergeCell ref="BV60:CE61"/>
     <mergeCell ref="Y10:AH11"/>
     <mergeCell ref="BV50:CE51"/>
+    <mergeCell ref="M42:Q43"/>
     <mergeCell ref="AJ60:AK61"/>
     <mergeCell ref="AL46:AQ47"/>
+    <mergeCell ref="R56:AH57"/>
     <mergeCell ref="AL40:AQ41"/>
+    <mergeCell ref="R46:AH47"/>
+    <mergeCell ref="G24:J25"/>
     <mergeCell ref="CF58:CK59"/>
-    <mergeCell ref="G24:J25"/>
     <mergeCell ref="BV52:CE53"/>
     <mergeCell ref="AJ44:AK45"/>
     <mergeCell ref="CF54:CK55"/>
-    <mergeCell ref="A36:F37"/>
+    <mergeCell ref="M44:Q45"/>
     <mergeCell ref="A52:B53"/>
     <mergeCell ref="CF60:CK61"/>
     <mergeCell ref="Y16:AH17"/>
     <mergeCell ref="A12:F15"/>
     <mergeCell ref="U10:X11"/>
     <mergeCell ref="Y18:AH19"/>
+    <mergeCell ref="F36:M37"/>
     <mergeCell ref="BG48:BT49"/>
+    <mergeCell ref="R60:AH61"/>
     <mergeCell ref="AL58:AQ59"/>
     <mergeCell ref="A50:B51"/>
     <mergeCell ref="AL52:AQ53"/>
     <mergeCell ref="A8:F9"/>
     <mergeCell ref="W38:AC39"/>
     <mergeCell ref="AJ48:AK49"/>
-    <mergeCell ref="M52:AH53"/>
     <mergeCell ref="AL42:AQ43"/>
-    <mergeCell ref="G36:P37"/>
     <mergeCell ref="G16:L17"/>
     <mergeCell ref="M18:X19"/>
     <mergeCell ref="AR40:BU41"/>
@@ -6778,28 +6802,29 @@
     <mergeCell ref="M20:R21"/>
     <mergeCell ref="C56:L57"/>
     <mergeCell ref="AG24:AH25"/>
-    <mergeCell ref="M46:AH47"/>
     <mergeCell ref="AR46:BF47"/>
     <mergeCell ref="C46:L47"/>
     <mergeCell ref="CF48:CK49"/>
     <mergeCell ref="AC12:AH13"/>
-    <mergeCell ref="AR48:BF49"/>
+    <mergeCell ref="M56:Q57"/>
     <mergeCell ref="A6:F7"/>
     <mergeCell ref="A28:E29"/>
     <mergeCell ref="Y40:AH41"/>
+    <mergeCell ref="AR48:BF49"/>
     <mergeCell ref="AJ50:AK51"/>
+    <mergeCell ref="M50:Q51"/>
     <mergeCell ref="BG52:BT53"/>
     <mergeCell ref="C60:L61"/>
     <mergeCell ref="A58:B59"/>
     <mergeCell ref="Y28:AB29"/>
-    <mergeCell ref="X36:AH37"/>
+    <mergeCell ref="AJ58:AK59"/>
     <mergeCell ref="BG42:BT43"/>
     <mergeCell ref="K38:Q39"/>
     <mergeCell ref="AJ52:AK53"/>
-    <mergeCell ref="AJ58:AK59"/>
-    <mergeCell ref="Q36:W37"/>
+    <mergeCell ref="M48:Q49"/>
     <mergeCell ref="A60:B61"/>
     <mergeCell ref="AJ42:AK43"/>
+    <mergeCell ref="M54:Q55"/>
     <mergeCell ref="G22:AH23"/>
     <mergeCell ref="BR3:CK4"/>
     <mergeCell ref="BU50:BU51"/>
@@ -6811,7 +6836,6 @@
     <mergeCell ref="AR60:BF61"/>
     <mergeCell ref="M28:Q29"/>
     <mergeCell ref="C42:L43"/>
-    <mergeCell ref="M58:AH59"/>
     <mergeCell ref="BU58:BU59"/>
     <mergeCell ref="BU52:BU53"/>
     <mergeCell ref="BV54:CE55"/>
@@ -6821,9 +6845,11 @@
     <mergeCell ref="BU42:BU43"/>
     <mergeCell ref="C50:L51"/>
     <mergeCell ref="CF52:CK53"/>
+    <mergeCell ref="R50:AH51"/>
     <mergeCell ref="C44:L45"/>
     <mergeCell ref="A42:B43"/>
-    <mergeCell ref="M60:AH61"/>
+    <mergeCell ref="N36:S37"/>
+    <mergeCell ref="T36:AB37"/>
     <mergeCell ref="Q24:V25"/>
     <mergeCell ref="A1:AH4"/>
     <mergeCell ref="BV40:CE41"/>
@@ -6831,6 +6857,7 @@
     <mergeCell ref="A24:F25"/>
     <mergeCell ref="A44:B45"/>
     <mergeCell ref="G14:J15"/>
+    <mergeCell ref="M52:Q53"/>
     <mergeCell ref="A16:F19"/>
     <mergeCell ref="Y20:AD21"/>
     <mergeCell ref="Y12:AB13"/>
@@ -6842,17 +6869,17 @@
     <mergeCell ref="AE20:AH21"/>
     <mergeCell ref="AL56:AQ57"/>
     <mergeCell ref="C48:L49"/>
-    <mergeCell ref="M42:AH43"/>
+    <mergeCell ref="R48:AH49"/>
     <mergeCell ref="BU54:BU55"/>
     <mergeCell ref="K10:T11"/>
     <mergeCell ref="A54:B55"/>
     <mergeCell ref="AD38:AH39"/>
     <mergeCell ref="G20:L21"/>
+    <mergeCell ref="A36:E37"/>
     <mergeCell ref="A38:J39"/>
     <mergeCell ref="CF46:CK47"/>
-    <mergeCell ref="M44:AH45"/>
-    <mergeCell ref="M56:AH57"/>
     <mergeCell ref="BU56:BU57"/>
+    <mergeCell ref="M46:Q47"/>
     <mergeCell ref="A20:F21"/>
     <mergeCell ref="A56:B57"/>
     <mergeCell ref="K14:AH15"/>
@@ -6861,14 +6888,13 @@
     <mergeCell ref="W24:Z25"/>
     <mergeCell ref="BV42:CE43"/>
     <mergeCell ref="A46:B47"/>
-    <mergeCell ref="M48:AH49"/>
+    <mergeCell ref="AC36:AH37"/>
     <mergeCell ref="BV44:CE45"/>
     <mergeCell ref="AC24:AF25"/>
     <mergeCell ref="G6:AF7"/>
     <mergeCell ref="AL60:AQ61"/>
     <mergeCell ref="G10:J11"/>
     <mergeCell ref="K24:P25"/>
-    <mergeCell ref="M54:AH55"/>
     <mergeCell ref="BG54:BT55"/>
     <mergeCell ref="AL50:AQ51"/>
     <mergeCell ref="CF40:CK41"/>
@@ -6881,17 +6907,22 @@
     <mergeCell ref="A26:AH27"/>
     <mergeCell ref="A30:F33"/>
     <mergeCell ref="C52:L53"/>
+    <mergeCell ref="R58:AH59"/>
+    <mergeCell ref="R52:AH53"/>
     <mergeCell ref="AJ56:AK57"/>
     <mergeCell ref="AJ46:AK47"/>
     <mergeCell ref="BV48:CE49"/>
     <mergeCell ref="AJ40:AK41"/>
+    <mergeCell ref="M58:Q59"/>
     <mergeCell ref="I40:P41"/>
     <mergeCell ref="G30:AH31"/>
     <mergeCell ref="M16:X17"/>
     <mergeCell ref="BG58:BT59"/>
     <mergeCell ref="R38:V39"/>
+    <mergeCell ref="R44:AH45"/>
     <mergeCell ref="G18:L19"/>
     <mergeCell ref="G32:AH33"/>
+    <mergeCell ref="M60:Q61"/>
     <mergeCell ref="AC28:AD29"/>
     <mergeCell ref="G12:J13"/>
     <mergeCell ref="A22:F23"/>
@@ -6927,7 +6958,7 @@
     <dataValidation sqref="W24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□その他,■その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K10 K14 Y10 BV42 BV44 BV46 BV48 BV50 BV52 BV54 BV56 BV58 BV60 CF42 CF44 CF46 CF48 CF50 CF52 CF54 CF56 CF58 CF60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
+    <dataValidation sqref="K10 K14 M44 M46 M48 M50 M52 M54 M56 M58 M60 Y10 BV42 BV44 BV46 BV48 BV50 BV52 BV54 BV56 BV58 BV60 CF42 CF44 CF46 CF48 CF50 CF52 CF54 CF56 CF58 CF60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>

--- a/住宅改修_現地調査アセスメントシート.xlsx
+++ b/住宅改修_現地調査アセスメントシート.xlsx
@@ -4784,24 +4784,24 @@
       <c r="G42" s="50" t="n"/>
       <c r="H42" s="50" t="n"/>
       <c r="I42" s="50" t="n"/>
-      <c r="J42" s="50" t="n"/>
-      <c r="K42" s="50" t="n"/>
-      <c r="L42" s="51" t="n"/>
-      <c r="M42" s="114" t="inlineStr">
+      <c r="J42" s="51" t="n"/>
+      <c r="K42" s="114" t="inlineStr">
         <is>
           <t>単位数
 （試算用）</t>
         </is>
       </c>
+      <c r="L42" s="115" t="n"/>
+      <c r="M42" s="115" t="n"/>
       <c r="N42" s="115" t="n"/>
-      <c r="O42" s="115" t="n"/>
-      <c r="P42" s="115" t="n"/>
-      <c r="Q42" s="116" t="n"/>
-      <c r="R42" s="49" t="inlineStr">
+      <c r="O42" s="116" t="n"/>
+      <c r="P42" s="49" t="inlineStr">
         <is>
           <t>商品名</t>
         </is>
       </c>
+      <c r="Q42" s="50" t="n"/>
+      <c r="R42" s="50" t="n"/>
       <c r="S42" s="50" t="n"/>
       <c r="T42" s="50" t="n"/>
       <c r="U42" s="50" t="n"/>
@@ -4832,7 +4832,7 @@
       <c r="AQ42" s="8" t="n"/>
       <c r="AR42" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS42" s="67" t="n"/>
@@ -4848,8 +4848,8 @@
       <c r="BC42" s="67" t="n"/>
       <c r="BD42" s="67" t="n"/>
       <c r="BE42" s="67" t="n"/>
-      <c r="BF42" s="67" t="n"/>
-      <c r="BG42" s="94" t="n"/>
+      <c r="BF42" s="94" t="n"/>
+      <c r="BG42" s="67" t="n"/>
       <c r="BH42" s="67" t="n"/>
       <c r="BI42" s="67" t="n"/>
       <c r="BJ42" s="67" t="n"/>
@@ -4895,15 +4895,15 @@
       <c r="G43" s="27" t="n"/>
       <c r="H43" s="27" t="n"/>
       <c r="I43" s="27" t="n"/>
-      <c r="J43" s="27" t="n"/>
-      <c r="K43" s="27" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="122" t="n"/>
+      <c r="J43" s="28" t="n"/>
+      <c r="K43" s="122" t="n"/>
+      <c r="L43" s="123" t="n"/>
+      <c r="M43" s="123" t="n"/>
       <c r="N43" s="123" t="n"/>
-      <c r="O43" s="123" t="n"/>
-      <c r="P43" s="123" t="n"/>
-      <c r="Q43" s="124" t="n"/>
-      <c r="R43" s="55" t="n"/>
+      <c r="O43" s="124" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="27" t="n"/>
+      <c r="R43" s="27" t="n"/>
       <c r="S43" s="27" t="n"/>
       <c r="T43" s="27" t="n"/>
       <c r="U43" s="27" t="n"/>
@@ -4989,15 +4989,15 @@
       <c r="G44" s="67" t="n"/>
       <c r="H44" s="67" t="n"/>
       <c r="I44" s="67" t="n"/>
-      <c r="J44" s="67" t="n"/>
-      <c r="K44" s="67" t="n"/>
-      <c r="L44" s="128" t="n"/>
-      <c r="M44" s="129" t="n"/>
+      <c r="J44" s="128" t="n"/>
+      <c r="K44" s="129" t="n"/>
+      <c r="L44" s="67" t="n"/>
+      <c r="M44" s="67" t="n"/>
       <c r="N44" s="67" t="n"/>
-      <c r="O44" s="67" t="n"/>
-      <c r="P44" s="67" t="n"/>
-      <c r="Q44" s="128" t="n"/>
-      <c r="R44" s="102" t="n"/>
+      <c r="O44" s="128" t="n"/>
+      <c r="P44" s="102" t="n"/>
+      <c r="Q44" s="67" t="n"/>
+      <c r="R44" s="67" t="n"/>
       <c r="S44" s="67" t="n"/>
       <c r="T44" s="67" t="n"/>
       <c r="U44" s="67" t="n"/>
@@ -5028,7 +5028,7 @@
       <c r="AQ44" s="8" t="n"/>
       <c r="AR44" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS44" s="67" t="n"/>
@@ -5044,8 +5044,8 @@
       <c r="BC44" s="67" t="n"/>
       <c r="BD44" s="67" t="n"/>
       <c r="BE44" s="67" t="n"/>
-      <c r="BF44" s="67" t="n"/>
-      <c r="BG44" s="94" t="n"/>
+      <c r="BF44" s="94" t="n"/>
+      <c r="BG44" s="67" t="n"/>
       <c r="BH44" s="67" t="n"/>
       <c r="BI44" s="67" t="n"/>
       <c r="BJ44" s="67" t="n"/>
@@ -5091,15 +5091,15 @@
       <c r="G45" s="76" t="n"/>
       <c r="H45" s="76" t="n"/>
       <c r="I45" s="76" t="n"/>
-      <c r="J45" s="76" t="n"/>
-      <c r="K45" s="76" t="n"/>
-      <c r="L45" s="127" t="n"/>
-      <c r="M45" s="75" t="n"/>
+      <c r="J45" s="127" t="n"/>
+      <c r="K45" s="75" t="n"/>
+      <c r="L45" s="76" t="n"/>
+      <c r="M45" s="76" t="n"/>
       <c r="N45" s="76" t="n"/>
-      <c r="O45" s="76" t="n"/>
-      <c r="P45" s="76" t="n"/>
-      <c r="Q45" s="127" t="n"/>
-      <c r="R45" s="75" t="n"/>
+      <c r="O45" s="127" t="n"/>
+      <c r="P45" s="75" t="n"/>
+      <c r="Q45" s="76" t="n"/>
+      <c r="R45" s="76" t="n"/>
       <c r="S45" s="76" t="n"/>
       <c r="T45" s="76" t="n"/>
       <c r="U45" s="76" t="n"/>
@@ -5185,15 +5185,15 @@
       <c r="G46" s="67" t="n"/>
       <c r="H46" s="67" t="n"/>
       <c r="I46" s="67" t="n"/>
-      <c r="J46" s="67" t="n"/>
-      <c r="K46" s="67" t="n"/>
-      <c r="L46" s="128" t="n"/>
-      <c r="M46" s="129" t="n"/>
+      <c r="J46" s="128" t="n"/>
+      <c r="K46" s="129" t="n"/>
+      <c r="L46" s="67" t="n"/>
+      <c r="M46" s="67" t="n"/>
       <c r="N46" s="67" t="n"/>
-      <c r="O46" s="67" t="n"/>
-      <c r="P46" s="67" t="n"/>
-      <c r="Q46" s="128" t="n"/>
-      <c r="R46" s="102" t="n"/>
+      <c r="O46" s="128" t="n"/>
+      <c r="P46" s="102" t="n"/>
+      <c r="Q46" s="67" t="n"/>
+      <c r="R46" s="67" t="n"/>
       <c r="S46" s="67" t="n"/>
       <c r="T46" s="67" t="n"/>
       <c r="U46" s="67" t="n"/>
@@ -5224,7 +5224,7 @@
       <c r="AQ46" s="8" t="n"/>
       <c r="AR46" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS46" s="67" t="n"/>
@@ -5240,8 +5240,8 @@
       <c r="BC46" s="67" t="n"/>
       <c r="BD46" s="67" t="n"/>
       <c r="BE46" s="67" t="n"/>
-      <c r="BF46" s="67" t="n"/>
-      <c r="BG46" s="94" t="n"/>
+      <c r="BF46" s="94" t="n"/>
+      <c r="BG46" s="67" t="n"/>
       <c r="BH46" s="67" t="n"/>
       <c r="BI46" s="67" t="n"/>
       <c r="BJ46" s="67" t="n"/>
@@ -5287,15 +5287,15 @@
       <c r="G47" s="76" t="n"/>
       <c r="H47" s="76" t="n"/>
       <c r="I47" s="76" t="n"/>
-      <c r="J47" s="76" t="n"/>
-      <c r="K47" s="76" t="n"/>
-      <c r="L47" s="127" t="n"/>
-      <c r="M47" s="75" t="n"/>
+      <c r="J47" s="127" t="n"/>
+      <c r="K47" s="75" t="n"/>
+      <c r="L47" s="76" t="n"/>
+      <c r="M47" s="76" t="n"/>
       <c r="N47" s="76" t="n"/>
-      <c r="O47" s="76" t="n"/>
-      <c r="P47" s="76" t="n"/>
-      <c r="Q47" s="127" t="n"/>
-      <c r="R47" s="75" t="n"/>
+      <c r="O47" s="127" t="n"/>
+      <c r="P47" s="75" t="n"/>
+      <c r="Q47" s="76" t="n"/>
+      <c r="R47" s="76" t="n"/>
       <c r="S47" s="76" t="n"/>
       <c r="T47" s="76" t="n"/>
       <c r="U47" s="76" t="n"/>
@@ -5381,15 +5381,15 @@
       <c r="G48" s="67" t="n"/>
       <c r="H48" s="67" t="n"/>
       <c r="I48" s="67" t="n"/>
-      <c r="J48" s="67" t="n"/>
-      <c r="K48" s="67" t="n"/>
-      <c r="L48" s="128" t="n"/>
-      <c r="M48" s="129" t="n"/>
+      <c r="J48" s="128" t="n"/>
+      <c r="K48" s="129" t="n"/>
+      <c r="L48" s="67" t="n"/>
+      <c r="M48" s="67" t="n"/>
       <c r="N48" s="67" t="n"/>
-      <c r="O48" s="67" t="n"/>
-      <c r="P48" s="67" t="n"/>
-      <c r="Q48" s="128" t="n"/>
-      <c r="R48" s="102" t="n"/>
+      <c r="O48" s="128" t="n"/>
+      <c r="P48" s="102" t="n"/>
+      <c r="Q48" s="67" t="n"/>
+      <c r="R48" s="67" t="n"/>
       <c r="S48" s="67" t="n"/>
       <c r="T48" s="67" t="n"/>
       <c r="U48" s="67" t="n"/>
@@ -5420,7 +5420,7 @@
       <c r="AQ48" s="8" t="n"/>
       <c r="AR48" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS48" s="67" t="n"/>
@@ -5436,8 +5436,8 @@
       <c r="BC48" s="67" t="n"/>
       <c r="BD48" s="67" t="n"/>
       <c r="BE48" s="67" t="n"/>
-      <c r="BF48" s="67" t="n"/>
-      <c r="BG48" s="94" t="n"/>
+      <c r="BF48" s="94" t="n"/>
+      <c r="BG48" s="67" t="n"/>
       <c r="BH48" s="67" t="n"/>
       <c r="BI48" s="67" t="n"/>
       <c r="BJ48" s="67" t="n"/>
@@ -5483,15 +5483,15 @@
       <c r="G49" s="76" t="n"/>
       <c r="H49" s="76" t="n"/>
       <c r="I49" s="76" t="n"/>
-      <c r="J49" s="76" t="n"/>
-      <c r="K49" s="76" t="n"/>
-      <c r="L49" s="127" t="n"/>
-      <c r="M49" s="75" t="n"/>
+      <c r="J49" s="127" t="n"/>
+      <c r="K49" s="75" t="n"/>
+      <c r="L49" s="76" t="n"/>
+      <c r="M49" s="76" t="n"/>
       <c r="N49" s="76" t="n"/>
-      <c r="O49" s="76" t="n"/>
-      <c r="P49" s="76" t="n"/>
-      <c r="Q49" s="127" t="n"/>
-      <c r="R49" s="75" t="n"/>
+      <c r="O49" s="127" t="n"/>
+      <c r="P49" s="75" t="n"/>
+      <c r="Q49" s="76" t="n"/>
+      <c r="R49" s="76" t="n"/>
       <c r="S49" s="76" t="n"/>
       <c r="T49" s="76" t="n"/>
       <c r="U49" s="76" t="n"/>
@@ -5577,15 +5577,15 @@
       <c r="G50" s="67" t="n"/>
       <c r="H50" s="67" t="n"/>
       <c r="I50" s="67" t="n"/>
-      <c r="J50" s="67" t="n"/>
-      <c r="K50" s="67" t="n"/>
-      <c r="L50" s="128" t="n"/>
-      <c r="M50" s="129" t="n"/>
+      <c r="J50" s="128" t="n"/>
+      <c r="K50" s="129" t="n"/>
+      <c r="L50" s="67" t="n"/>
+      <c r="M50" s="67" t="n"/>
       <c r="N50" s="67" t="n"/>
-      <c r="O50" s="67" t="n"/>
-      <c r="P50" s="67" t="n"/>
-      <c r="Q50" s="128" t="n"/>
-      <c r="R50" s="102" t="n"/>
+      <c r="O50" s="128" t="n"/>
+      <c r="P50" s="102" t="n"/>
+      <c r="Q50" s="67" t="n"/>
+      <c r="R50" s="67" t="n"/>
       <c r="S50" s="67" t="n"/>
       <c r="T50" s="67" t="n"/>
       <c r="U50" s="67" t="n"/>
@@ -5616,7 +5616,7 @@
       <c r="AQ50" s="8" t="n"/>
       <c r="AR50" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS50" s="67" t="n"/>
@@ -5632,8 +5632,8 @@
       <c r="BC50" s="67" t="n"/>
       <c r="BD50" s="67" t="n"/>
       <c r="BE50" s="67" t="n"/>
-      <c r="BF50" s="67" t="n"/>
-      <c r="BG50" s="94" t="n"/>
+      <c r="BF50" s="94" t="n"/>
+      <c r="BG50" s="67" t="n"/>
       <c r="BH50" s="67" t="n"/>
       <c r="BI50" s="67" t="n"/>
       <c r="BJ50" s="67" t="n"/>
@@ -5679,15 +5679,15 @@
       <c r="G51" s="76" t="n"/>
       <c r="H51" s="76" t="n"/>
       <c r="I51" s="76" t="n"/>
-      <c r="J51" s="76" t="n"/>
-      <c r="K51" s="76" t="n"/>
-      <c r="L51" s="127" t="n"/>
-      <c r="M51" s="75" t="n"/>
+      <c r="J51" s="127" t="n"/>
+      <c r="K51" s="75" t="n"/>
+      <c r="L51" s="76" t="n"/>
+      <c r="M51" s="76" t="n"/>
       <c r="N51" s="76" t="n"/>
-      <c r="O51" s="76" t="n"/>
-      <c r="P51" s="76" t="n"/>
-      <c r="Q51" s="127" t="n"/>
-      <c r="R51" s="75" t="n"/>
+      <c r="O51" s="127" t="n"/>
+      <c r="P51" s="75" t="n"/>
+      <c r="Q51" s="76" t="n"/>
+      <c r="R51" s="76" t="n"/>
       <c r="S51" s="76" t="n"/>
       <c r="T51" s="76" t="n"/>
       <c r="U51" s="76" t="n"/>
@@ -5773,15 +5773,15 @@
       <c r="G52" s="67" t="n"/>
       <c r="H52" s="67" t="n"/>
       <c r="I52" s="67" t="n"/>
-      <c r="J52" s="67" t="n"/>
-      <c r="K52" s="67" t="n"/>
-      <c r="L52" s="128" t="n"/>
-      <c r="M52" s="129" t="n"/>
+      <c r="J52" s="128" t="n"/>
+      <c r="K52" s="129" t="n"/>
+      <c r="L52" s="67" t="n"/>
+      <c r="M52" s="67" t="n"/>
       <c r="N52" s="67" t="n"/>
-      <c r="O52" s="67" t="n"/>
-      <c r="P52" s="67" t="n"/>
-      <c r="Q52" s="128" t="n"/>
-      <c r="R52" s="102" t="n"/>
+      <c r="O52" s="128" t="n"/>
+      <c r="P52" s="102" t="n"/>
+      <c r="Q52" s="67" t="n"/>
+      <c r="R52" s="67" t="n"/>
       <c r="S52" s="67" t="n"/>
       <c r="T52" s="67" t="n"/>
       <c r="U52" s="67" t="n"/>
@@ -5812,7 +5812,7 @@
       <c r="AQ52" s="8" t="n"/>
       <c r="AR52" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS52" s="67" t="n"/>
@@ -5828,8 +5828,8 @@
       <c r="BC52" s="67" t="n"/>
       <c r="BD52" s="67" t="n"/>
       <c r="BE52" s="67" t="n"/>
-      <c r="BF52" s="67" t="n"/>
-      <c r="BG52" s="94" t="n"/>
+      <c r="BF52" s="94" t="n"/>
+      <c r="BG52" s="67" t="n"/>
       <c r="BH52" s="67" t="n"/>
       <c r="BI52" s="67" t="n"/>
       <c r="BJ52" s="67" t="n"/>
@@ -5875,15 +5875,15 @@
       <c r="G53" s="76" t="n"/>
       <c r="H53" s="76" t="n"/>
       <c r="I53" s="76" t="n"/>
-      <c r="J53" s="76" t="n"/>
-      <c r="K53" s="76" t="n"/>
-      <c r="L53" s="127" t="n"/>
-      <c r="M53" s="75" t="n"/>
+      <c r="J53" s="127" t="n"/>
+      <c r="K53" s="75" t="n"/>
+      <c r="L53" s="76" t="n"/>
+      <c r="M53" s="76" t="n"/>
       <c r="N53" s="76" t="n"/>
-      <c r="O53" s="76" t="n"/>
-      <c r="P53" s="76" t="n"/>
-      <c r="Q53" s="127" t="n"/>
-      <c r="R53" s="75" t="n"/>
+      <c r="O53" s="127" t="n"/>
+      <c r="P53" s="75" t="n"/>
+      <c r="Q53" s="76" t="n"/>
+      <c r="R53" s="76" t="n"/>
       <c r="S53" s="76" t="n"/>
       <c r="T53" s="76" t="n"/>
       <c r="U53" s="76" t="n"/>
@@ -5969,15 +5969,15 @@
       <c r="G54" s="67" t="n"/>
       <c r="H54" s="67" t="n"/>
       <c r="I54" s="67" t="n"/>
-      <c r="J54" s="67" t="n"/>
-      <c r="K54" s="67" t="n"/>
-      <c r="L54" s="128" t="n"/>
-      <c r="M54" s="129" t="n"/>
+      <c r="J54" s="128" t="n"/>
+      <c r="K54" s="129" t="n"/>
+      <c r="L54" s="67" t="n"/>
+      <c r="M54" s="67" t="n"/>
       <c r="N54" s="67" t="n"/>
-      <c r="O54" s="67" t="n"/>
-      <c r="P54" s="67" t="n"/>
-      <c r="Q54" s="128" t="n"/>
-      <c r="R54" s="102" t="n"/>
+      <c r="O54" s="128" t="n"/>
+      <c r="P54" s="102" t="n"/>
+      <c r="Q54" s="67" t="n"/>
+      <c r="R54" s="67" t="n"/>
       <c r="S54" s="67" t="n"/>
       <c r="T54" s="67" t="n"/>
       <c r="U54" s="67" t="n"/>
@@ -6008,7 +6008,7 @@
       <c r="AQ54" s="8" t="n"/>
       <c r="AR54" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS54" s="67" t="n"/>
@@ -6024,8 +6024,8 @@
       <c r="BC54" s="67" t="n"/>
       <c r="BD54" s="67" t="n"/>
       <c r="BE54" s="67" t="n"/>
-      <c r="BF54" s="67" t="n"/>
-      <c r="BG54" s="94" t="n"/>
+      <c r="BF54" s="94" t="n"/>
+      <c r="BG54" s="67" t="n"/>
       <c r="BH54" s="67" t="n"/>
       <c r="BI54" s="67" t="n"/>
       <c r="BJ54" s="67" t="n"/>
@@ -6071,15 +6071,15 @@
       <c r="G55" s="76" t="n"/>
       <c r="H55" s="76" t="n"/>
       <c r="I55" s="76" t="n"/>
-      <c r="J55" s="76" t="n"/>
-      <c r="K55" s="76" t="n"/>
-      <c r="L55" s="127" t="n"/>
-      <c r="M55" s="75" t="n"/>
+      <c r="J55" s="127" t="n"/>
+      <c r="K55" s="75" t="n"/>
+      <c r="L55" s="76" t="n"/>
+      <c r="M55" s="76" t="n"/>
       <c r="N55" s="76" t="n"/>
-      <c r="O55" s="76" t="n"/>
-      <c r="P55" s="76" t="n"/>
-      <c r="Q55" s="127" t="n"/>
-      <c r="R55" s="75" t="n"/>
+      <c r="O55" s="127" t="n"/>
+      <c r="P55" s="75" t="n"/>
+      <c r="Q55" s="76" t="n"/>
+      <c r="R55" s="76" t="n"/>
       <c r="S55" s="76" t="n"/>
       <c r="T55" s="76" t="n"/>
       <c r="U55" s="76" t="n"/>
@@ -6165,15 +6165,15 @@
       <c r="G56" s="67" t="n"/>
       <c r="H56" s="67" t="n"/>
       <c r="I56" s="67" t="n"/>
-      <c r="J56" s="67" t="n"/>
-      <c r="K56" s="67" t="n"/>
-      <c r="L56" s="128" t="n"/>
-      <c r="M56" s="129" t="n"/>
+      <c r="J56" s="128" t="n"/>
+      <c r="K56" s="129" t="n"/>
+      <c r="L56" s="67" t="n"/>
+      <c r="M56" s="67" t="n"/>
       <c r="N56" s="67" t="n"/>
-      <c r="O56" s="67" t="n"/>
-      <c r="P56" s="67" t="n"/>
-      <c r="Q56" s="128" t="n"/>
-      <c r="R56" s="102" t="n"/>
+      <c r="O56" s="128" t="n"/>
+      <c r="P56" s="102" t="n"/>
+      <c r="Q56" s="67" t="n"/>
+      <c r="R56" s="67" t="n"/>
       <c r="S56" s="67" t="n"/>
       <c r="T56" s="67" t="n"/>
       <c r="U56" s="67" t="n"/>
@@ -6204,7 +6204,7 @@
       <c r="AQ56" s="8" t="n"/>
       <c r="AR56" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS56" s="67" t="n"/>
@@ -6220,8 +6220,8 @@
       <c r="BC56" s="67" t="n"/>
       <c r="BD56" s="67" t="n"/>
       <c r="BE56" s="67" t="n"/>
-      <c r="BF56" s="67" t="n"/>
-      <c r="BG56" s="94" t="n"/>
+      <c r="BF56" s="94" t="n"/>
+      <c r="BG56" s="67" t="n"/>
       <c r="BH56" s="67" t="n"/>
       <c r="BI56" s="67" t="n"/>
       <c r="BJ56" s="67" t="n"/>
@@ -6267,15 +6267,15 @@
       <c r="G57" s="76" t="n"/>
       <c r="H57" s="76" t="n"/>
       <c r="I57" s="76" t="n"/>
-      <c r="J57" s="76" t="n"/>
-      <c r="K57" s="76" t="n"/>
-      <c r="L57" s="127" t="n"/>
-      <c r="M57" s="75" t="n"/>
+      <c r="J57" s="127" t="n"/>
+      <c r="K57" s="75" t="n"/>
+      <c r="L57" s="76" t="n"/>
+      <c r="M57" s="76" t="n"/>
       <c r="N57" s="76" t="n"/>
-      <c r="O57" s="76" t="n"/>
-      <c r="P57" s="76" t="n"/>
-      <c r="Q57" s="127" t="n"/>
-      <c r="R57" s="75" t="n"/>
+      <c r="O57" s="127" t="n"/>
+      <c r="P57" s="75" t="n"/>
+      <c r="Q57" s="76" t="n"/>
+      <c r="R57" s="76" t="n"/>
       <c r="S57" s="76" t="n"/>
       <c r="T57" s="76" t="n"/>
       <c r="U57" s="76" t="n"/>
@@ -6361,15 +6361,15 @@
       <c r="G58" s="67" t="n"/>
       <c r="H58" s="67" t="n"/>
       <c r="I58" s="67" t="n"/>
-      <c r="J58" s="67" t="n"/>
-      <c r="K58" s="67" t="n"/>
-      <c r="L58" s="128" t="n"/>
-      <c r="M58" s="129" t="n"/>
+      <c r="J58" s="128" t="n"/>
+      <c r="K58" s="129" t="n"/>
+      <c r="L58" s="67" t="n"/>
+      <c r="M58" s="67" t="n"/>
       <c r="N58" s="67" t="n"/>
-      <c r="O58" s="67" t="n"/>
-      <c r="P58" s="67" t="n"/>
-      <c r="Q58" s="128" t="n"/>
-      <c r="R58" s="102" t="n"/>
+      <c r="O58" s="128" t="n"/>
+      <c r="P58" s="102" t="n"/>
+      <c r="Q58" s="67" t="n"/>
+      <c r="R58" s="67" t="n"/>
       <c r="S58" s="67" t="n"/>
       <c r="T58" s="67" t="n"/>
       <c r="U58" s="67" t="n"/>
@@ -6400,7 +6400,7 @@
       <c r="AQ58" s="8" t="n"/>
       <c r="AR58" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS58" s="67" t="n"/>
@@ -6416,8 +6416,8 @@
       <c r="BC58" s="67" t="n"/>
       <c r="BD58" s="67" t="n"/>
       <c r="BE58" s="67" t="n"/>
-      <c r="BF58" s="67" t="n"/>
-      <c r="BG58" s="94" t="n"/>
+      <c r="BF58" s="94" t="n"/>
+      <c r="BG58" s="67" t="n"/>
       <c r="BH58" s="67" t="n"/>
       <c r="BI58" s="67" t="n"/>
       <c r="BJ58" s="67" t="n"/>
@@ -6463,15 +6463,15 @@
       <c r="G59" s="76" t="n"/>
       <c r="H59" s="76" t="n"/>
       <c r="I59" s="76" t="n"/>
-      <c r="J59" s="76" t="n"/>
-      <c r="K59" s="76" t="n"/>
-      <c r="L59" s="127" t="n"/>
-      <c r="M59" s="75" t="n"/>
+      <c r="J59" s="127" t="n"/>
+      <c r="K59" s="75" t="n"/>
+      <c r="L59" s="76" t="n"/>
+      <c r="M59" s="76" t="n"/>
       <c r="N59" s="76" t="n"/>
-      <c r="O59" s="76" t="n"/>
-      <c r="P59" s="76" t="n"/>
-      <c r="Q59" s="127" t="n"/>
-      <c r="R59" s="75" t="n"/>
+      <c r="O59" s="127" t="n"/>
+      <c r="P59" s="75" t="n"/>
+      <c r="Q59" s="76" t="n"/>
+      <c r="R59" s="76" t="n"/>
       <c r="S59" s="76" t="n"/>
       <c r="T59" s="76" t="n"/>
       <c r="U59" s="76" t="n"/>
@@ -6557,15 +6557,15 @@
       <c r="G60" s="67" t="n"/>
       <c r="H60" s="67" t="n"/>
       <c r="I60" s="67" t="n"/>
-      <c r="J60" s="67" t="n"/>
-      <c r="K60" s="67" t="n"/>
-      <c r="L60" s="128" t="n"/>
-      <c r="M60" s="129" t="n"/>
+      <c r="J60" s="128" t="n"/>
+      <c r="K60" s="129" t="n"/>
+      <c r="L60" s="67" t="n"/>
+      <c r="M60" s="67" t="n"/>
       <c r="N60" s="67" t="n"/>
-      <c r="O60" s="67" t="n"/>
-      <c r="P60" s="67" t="n"/>
-      <c r="Q60" s="128" t="n"/>
-      <c r="R60" s="102" t="n"/>
+      <c r="O60" s="128" t="n"/>
+      <c r="P60" s="102" t="n"/>
+      <c r="Q60" s="67" t="n"/>
+      <c r="R60" s="67" t="n"/>
       <c r="S60" s="67" t="n"/>
       <c r="T60" s="67" t="n"/>
       <c r="U60" s="67" t="n"/>
@@ -6596,7 +6596,7 @@
       <c r="AQ60" s="8" t="n"/>
       <c r="AR60" s="119" t="inlineStr">
         <is>
-          <t>手すり　段差の解消　その他（</t>
+          <t>手すり　段差の解消　備考（</t>
         </is>
       </c>
       <c r="AS60" s="67" t="n"/>
@@ -6612,8 +6612,8 @@
       <c r="BC60" s="67" t="n"/>
       <c r="BD60" s="67" t="n"/>
       <c r="BE60" s="67" t="n"/>
-      <c r="BF60" s="67" t="n"/>
-      <c r="BG60" s="94" t="n"/>
+      <c r="BF60" s="94" t="n"/>
+      <c r="BG60" s="67" t="n"/>
       <c r="BH60" s="67" t="n"/>
       <c r="BI60" s="67" t="n"/>
       <c r="BJ60" s="67" t="n"/>
@@ -6659,15 +6659,15 @@
       <c r="G61" s="133" t="n"/>
       <c r="H61" s="133" t="n"/>
       <c r="I61" s="133" t="n"/>
-      <c r="J61" s="133" t="n"/>
-      <c r="K61" s="133" t="n"/>
-      <c r="L61" s="134" t="n"/>
-      <c r="M61" s="132" t="n"/>
+      <c r="J61" s="134" t="n"/>
+      <c r="K61" s="132" t="n"/>
+      <c r="L61" s="133" t="n"/>
+      <c r="M61" s="133" t="n"/>
       <c r="N61" s="133" t="n"/>
-      <c r="O61" s="133" t="n"/>
-      <c r="P61" s="133" t="n"/>
-      <c r="Q61" s="134" t="n"/>
-      <c r="R61" s="132" t="n"/>
+      <c r="O61" s="134" t="n"/>
+      <c r="P61" s="132" t="n"/>
+      <c r="Q61" s="133" t="n"/>
+      <c r="R61" s="133" t="n"/>
       <c r="S61" s="133" t="n"/>
       <c r="T61" s="133" t="n"/>
       <c r="U61" s="133" t="n"/>
@@ -6743,110 +6743,100 @@
   <mergeCells count="186">
     <mergeCell ref="BV58:CE59"/>
     <mergeCell ref="S20:X21"/>
-    <mergeCell ref="BG50:BT51"/>
-    <mergeCell ref="BG44:BT45"/>
     <mergeCell ref="CF56:CK57"/>
     <mergeCell ref="AJ6:CK7"/>
     <mergeCell ref="AL54:AQ55"/>
+    <mergeCell ref="P44:AH45"/>
     <mergeCell ref="Q40:X41"/>
     <mergeCell ref="G8:AH9"/>
-    <mergeCell ref="R42:AH43"/>
-    <mergeCell ref="R54:AH55"/>
     <mergeCell ref="BV60:CE61"/>
     <mergeCell ref="Y10:AH11"/>
     <mergeCell ref="BV50:CE51"/>
-    <mergeCell ref="M42:Q43"/>
     <mergeCell ref="AJ60:AK61"/>
     <mergeCell ref="AL46:AQ47"/>
-    <mergeCell ref="R56:AH57"/>
+    <mergeCell ref="BF56:BT57"/>
     <mergeCell ref="AL40:AQ41"/>
-    <mergeCell ref="R46:AH47"/>
+    <mergeCell ref="CF58:CK59"/>
     <mergeCell ref="G24:J25"/>
-    <mergeCell ref="CF58:CK59"/>
+    <mergeCell ref="AR60:BE61"/>
     <mergeCell ref="BV52:CE53"/>
     <mergeCell ref="AJ44:AK45"/>
     <mergeCell ref="CF54:CK55"/>
-    <mergeCell ref="M44:Q45"/>
     <mergeCell ref="A52:B53"/>
+    <mergeCell ref="AR50:BE51"/>
+    <mergeCell ref="AR44:BE45"/>
     <mergeCell ref="CF60:CK61"/>
+    <mergeCell ref="P48:AH49"/>
     <mergeCell ref="Y16:AH17"/>
+    <mergeCell ref="K54:O55"/>
     <mergeCell ref="A12:F15"/>
     <mergeCell ref="U10:X11"/>
     <mergeCell ref="Y18:AH19"/>
     <mergeCell ref="F36:M37"/>
-    <mergeCell ref="BG48:BT49"/>
-    <mergeCell ref="R60:AH61"/>
     <mergeCell ref="AL58:AQ59"/>
     <mergeCell ref="A50:B51"/>
+    <mergeCell ref="C54:J55"/>
+    <mergeCell ref="A8:F9"/>
     <mergeCell ref="AL52:AQ53"/>
-    <mergeCell ref="A8:F9"/>
     <mergeCell ref="W38:AC39"/>
     <mergeCell ref="AJ48:AK49"/>
     <mergeCell ref="AL42:AQ43"/>
     <mergeCell ref="G16:L17"/>
     <mergeCell ref="M18:X19"/>
-    <mergeCell ref="AR40:BU41"/>
+    <mergeCell ref="C56:J57"/>
     <mergeCell ref="A10:F11"/>
     <mergeCell ref="CF42:CK43"/>
+    <mergeCell ref="AR40:BU41"/>
+    <mergeCell ref="C46:J47"/>
     <mergeCell ref="K12:X13"/>
-    <mergeCell ref="AR42:BF43"/>
+    <mergeCell ref="P60:AH61"/>
     <mergeCell ref="AL44:AQ45"/>
-    <mergeCell ref="AR54:BF55"/>
     <mergeCell ref="R28:X29"/>
+    <mergeCell ref="K58:O59"/>
     <mergeCell ref="CF50:CK51"/>
+    <mergeCell ref="K52:O53"/>
     <mergeCell ref="CF44:CK45"/>
-    <mergeCell ref="C54:L55"/>
     <mergeCell ref="BV56:CE57"/>
-    <mergeCell ref="AR56:BF57"/>
+    <mergeCell ref="P50:AH51"/>
+    <mergeCell ref="C60:J61"/>
+    <mergeCell ref="K42:O43"/>
     <mergeCell ref="BU48:BU49"/>
     <mergeCell ref="M20:R21"/>
-    <mergeCell ref="C56:L57"/>
     <mergeCell ref="AG24:AH25"/>
-    <mergeCell ref="AR46:BF47"/>
-    <mergeCell ref="C46:L47"/>
+    <mergeCell ref="P52:AH53"/>
     <mergeCell ref="CF48:CK49"/>
     <mergeCell ref="AC12:AH13"/>
-    <mergeCell ref="M56:Q57"/>
     <mergeCell ref="A6:F7"/>
     <mergeCell ref="A28:E29"/>
     <mergeCell ref="Y40:AH41"/>
-    <mergeCell ref="AR48:BF49"/>
     <mergeCell ref="AJ50:AK51"/>
-    <mergeCell ref="M50:Q51"/>
-    <mergeCell ref="BG52:BT53"/>
-    <mergeCell ref="C60:L61"/>
     <mergeCell ref="A58:B59"/>
+    <mergeCell ref="C58:J59"/>
     <mergeCell ref="Y28:AB29"/>
     <mergeCell ref="AJ58:AK59"/>
-    <mergeCell ref="BG42:BT43"/>
     <mergeCell ref="K38:Q39"/>
     <mergeCell ref="AJ52:AK53"/>
-    <mergeCell ref="M48:Q49"/>
+    <mergeCell ref="C42:J43"/>
     <mergeCell ref="A60:B61"/>
+    <mergeCell ref="AR58:BE59"/>
     <mergeCell ref="AJ42:AK43"/>
-    <mergeCell ref="M54:Q55"/>
+    <mergeCell ref="AR52:BE53"/>
+    <mergeCell ref="C50:J51"/>
+    <mergeCell ref="C44:J45"/>
     <mergeCell ref="G22:AH23"/>
     <mergeCell ref="BR3:CK4"/>
     <mergeCell ref="BU50:BU51"/>
     <mergeCell ref="A34:AH35"/>
     <mergeCell ref="AA24:AB25"/>
-    <mergeCell ref="C58:L59"/>
     <mergeCell ref="AJ38:CK39"/>
     <mergeCell ref="BL3:BQ4"/>
-    <mergeCell ref="AR60:BF61"/>
     <mergeCell ref="M28:Q29"/>
-    <mergeCell ref="C42:L43"/>
     <mergeCell ref="BU58:BU59"/>
+    <mergeCell ref="BF50:BT51"/>
     <mergeCell ref="BU52:BU53"/>
     <mergeCell ref="BV54:CE55"/>
-    <mergeCell ref="AR50:BF51"/>
-    <mergeCell ref="AR44:BF45"/>
-    <mergeCell ref="BG46:BT47"/>
     <mergeCell ref="BU42:BU43"/>
-    <mergeCell ref="C50:L51"/>
     <mergeCell ref="CF52:CK53"/>
-    <mergeCell ref="R50:AH51"/>
-    <mergeCell ref="C44:L45"/>
     <mergeCell ref="A42:B43"/>
     <mergeCell ref="N36:S37"/>
     <mergeCell ref="T36:AB37"/>
@@ -6855,22 +6845,26 @@
     <mergeCell ref="BV40:CE41"/>
     <mergeCell ref="BU44:BU45"/>
     <mergeCell ref="A24:F25"/>
+    <mergeCell ref="C48:J49"/>
     <mergeCell ref="A44:B45"/>
+    <mergeCell ref="AR42:BE43"/>
+    <mergeCell ref="AR54:BE55"/>
     <mergeCell ref="G14:J15"/>
-    <mergeCell ref="M52:Q53"/>
     <mergeCell ref="A16:F19"/>
     <mergeCell ref="Y20:AD21"/>
+    <mergeCell ref="BF46:BT47"/>
+    <mergeCell ref="AR56:BE57"/>
     <mergeCell ref="Y12:AB13"/>
     <mergeCell ref="A40:H41"/>
     <mergeCell ref="AG6:AH7"/>
     <mergeCell ref="A48:B49"/>
     <mergeCell ref="F28:L29"/>
     <mergeCell ref="AE28:AH29"/>
+    <mergeCell ref="AR46:BE47"/>
     <mergeCell ref="AE20:AH21"/>
     <mergeCell ref="AL56:AQ57"/>
-    <mergeCell ref="C48:L49"/>
-    <mergeCell ref="R48:AH49"/>
     <mergeCell ref="BU54:BU55"/>
+    <mergeCell ref="BF48:BT49"/>
     <mergeCell ref="K10:T11"/>
     <mergeCell ref="A54:B55"/>
     <mergeCell ref="AD38:AH39"/>
@@ -6878,8 +6872,9 @@
     <mergeCell ref="A36:E37"/>
     <mergeCell ref="A38:J39"/>
     <mergeCell ref="CF46:CK47"/>
+    <mergeCell ref="AR48:BE49"/>
+    <mergeCell ref="BF54:BT55"/>
     <mergeCell ref="BU56:BU57"/>
-    <mergeCell ref="M46:Q47"/>
     <mergeCell ref="A20:F21"/>
     <mergeCell ref="A56:B57"/>
     <mergeCell ref="K14:AH15"/>
@@ -6888,45 +6883,50 @@
     <mergeCell ref="W24:Z25"/>
     <mergeCell ref="BV42:CE43"/>
     <mergeCell ref="A46:B47"/>
+    <mergeCell ref="K56:O57"/>
+    <mergeCell ref="P54:AH55"/>
+    <mergeCell ref="K46:O47"/>
     <mergeCell ref="AC36:AH37"/>
+    <mergeCell ref="BF58:BT59"/>
     <mergeCell ref="BV44:CE45"/>
+    <mergeCell ref="C52:J53"/>
     <mergeCell ref="AC24:AF25"/>
     <mergeCell ref="G6:AF7"/>
     <mergeCell ref="AL60:AQ61"/>
+    <mergeCell ref="P56:AH57"/>
     <mergeCell ref="G10:J11"/>
     <mergeCell ref="K24:P25"/>
-    <mergeCell ref="BG54:BT55"/>
+    <mergeCell ref="K48:O49"/>
+    <mergeCell ref="BF60:BT61"/>
+    <mergeCell ref="P46:AH47"/>
     <mergeCell ref="AL50:AQ51"/>
     <mergeCell ref="CF40:CK41"/>
     <mergeCell ref="BU60:BU61"/>
     <mergeCell ref="AJ54:AK55"/>
-    <mergeCell ref="AR58:BF59"/>
-    <mergeCell ref="BG56:BT57"/>
-    <mergeCell ref="AR52:BF53"/>
     <mergeCell ref="BV46:CE47"/>
     <mergeCell ref="A26:AH27"/>
     <mergeCell ref="A30:F33"/>
-    <mergeCell ref="C52:L53"/>
-    <mergeCell ref="R58:AH59"/>
-    <mergeCell ref="R52:AH53"/>
+    <mergeCell ref="BF52:BT53"/>
     <mergeCell ref="AJ56:AK57"/>
     <mergeCell ref="AJ46:AK47"/>
     <mergeCell ref="BV48:CE49"/>
     <mergeCell ref="AJ40:AK41"/>
-    <mergeCell ref="M58:Q59"/>
     <mergeCell ref="I40:P41"/>
     <mergeCell ref="G30:AH31"/>
     <mergeCell ref="M16:X17"/>
-    <mergeCell ref="BG58:BT59"/>
     <mergeCell ref="R38:V39"/>
-    <mergeCell ref="R44:AH45"/>
+    <mergeCell ref="K60:O61"/>
+    <mergeCell ref="BF42:BT43"/>
     <mergeCell ref="G18:L19"/>
     <mergeCell ref="G32:AH33"/>
-    <mergeCell ref="M60:Q61"/>
+    <mergeCell ref="P58:AH59"/>
     <mergeCell ref="AC28:AD29"/>
     <mergeCell ref="G12:J13"/>
+    <mergeCell ref="K50:O51"/>
     <mergeCell ref="A22:F23"/>
-    <mergeCell ref="BG60:BT61"/>
+    <mergeCell ref="K44:O45"/>
+    <mergeCell ref="BF44:BT45"/>
+    <mergeCell ref="P42:AH43"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:CK61">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -6958,7 +6958,7 @@
     <dataValidation sqref="W24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"□その他,■その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K10 K14 M44 M46 M48 M50 M52 M54 M56 M58 M60 Y10 BV42 BV44 BV46 BV48 BV50 BV52 BV54 BV56 BV58 BV60 CF42 CF44 CF46 CF48 CF50 CF52 CF54 CF56 CF58 CF60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
+    <dataValidation sqref="K10 K14 K44 K46 K48 K50 K52 K54 K56 K58 K60 Y10 BV42 BV44 BV46 BV48 BV50 BV52 BV54 BV56 BV58 BV60 CF42 CF44 CF46 CF48 CF50 CF52 CF54 CF56 CF58 CF60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" imeMode="halfAlpha"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
